--- a/data/FRS_cleaned/Nov/Fmn G Nov/Nov 2025-G.xlsx
+++ b/data/FRS_cleaned/Nov/Fmn G Nov/Nov 2025-G.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84FE1B2-FD2B-4C14-B159-1E416B891CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{27206D68-33BE-482D-802F-57DE02E6DC52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="A Vehicle" sheetId="20" r:id="rId1"/>
@@ -5009,41 +5009,44 @@
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -5113,12 +5116,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -5208,38 +5205,41 @@
     <xf numFmtId="2" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -5601,80 +5601,80 @@
       <c r="U2" s="92"/>
     </row>
     <row r="3" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="374" t="s">
+      <c r="A3" s="375" t="s">
         <v>392</v>
       </c>
-      <c r="B3" s="374"/>
-      <c r="C3" s="374"/>
-      <c r="D3" s="374"/>
-      <c r="E3" s="374"/>
-      <c r="F3" s="374"/>
-      <c r="G3" s="374"/>
-      <c r="H3" s="374"/>
-      <c r="I3" s="374"/>
-      <c r="J3" s="374"/>
-      <c r="K3" s="374"/>
-      <c r="L3" s="374"/>
-      <c r="M3" s="374"/>
-      <c r="N3" s="374"/>
-      <c r="O3" s="374"/>
-      <c r="P3" s="374"/>
-      <c r="Q3" s="374"/>
-      <c r="R3" s="374"/>
-      <c r="S3" s="374"/>
-      <c r="T3" s="374"/>
-      <c r="U3" s="374"/>
+      <c r="B3" s="375"/>
+      <c r="C3" s="375"/>
+      <c r="D3" s="375"/>
+      <c r="E3" s="375"/>
+      <c r="F3" s="375"/>
+      <c r="G3" s="375"/>
+      <c r="H3" s="375"/>
+      <c r="I3" s="375"/>
+      <c r="J3" s="375"/>
+      <c r="K3" s="375"/>
+      <c r="L3" s="375"/>
+      <c r="M3" s="375"/>
+      <c r="N3" s="375"/>
+      <c r="O3" s="375"/>
+      <c r="P3" s="375"/>
+      <c r="Q3" s="375"/>
+      <c r="R3" s="375"/>
+      <c r="S3" s="375"/>
+      <c r="T3" s="375"/>
+      <c r="U3" s="375"/>
     </row>
     <row r="4" spans="1:21" s="19" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="375" t="s">
+      <c r="A4" s="376" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="373" t="s">
+      <c r="B4" s="374" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="39"/>
-      <c r="D4" s="375" t="s">
+      <c r="D4" s="376" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="375"/>
-      <c r="F4" s="375" t="s">
+      <c r="E4" s="376"/>
+      <c r="F4" s="376" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="375"/>
-      <c r="H4" s="375"/>
-      <c r="I4" s="375"/>
-      <c r="J4" s="375"/>
-      <c r="K4" s="375"/>
-      <c r="L4" s="375"/>
-      <c r="M4" s="375"/>
-      <c r="N4" s="373" t="s">
+      <c r="G4" s="376"/>
+      <c r="H4" s="376"/>
+      <c r="I4" s="376"/>
+      <c r="J4" s="376"/>
+      <c r="K4" s="376"/>
+      <c r="L4" s="376"/>
+      <c r="M4" s="376"/>
+      <c r="N4" s="374" t="s">
         <v>20</v>
       </c>
-      <c r="O4" s="373" t="s">
+      <c r="O4" s="374" t="s">
         <v>34</v>
       </c>
-      <c r="P4" s="375" t="s">
+      <c r="P4" s="376" t="s">
         <v>35</v>
       </c>
-      <c r="Q4" s="373" t="s">
+      <c r="Q4" s="374" t="s">
         <v>23</v>
       </c>
-      <c r="R4" s="373" t="s">
+      <c r="R4" s="374" t="s">
         <v>24</v>
       </c>
-      <c r="S4" s="373" t="s">
+      <c r="S4" s="374" t="s">
         <v>25</v>
       </c>
-      <c r="T4" s="373" t="s">
+      <c r="T4" s="374" t="s">
         <v>26</v>
       </c>
-      <c r="U4" s="373" t="s">
+      <c r="U4" s="374" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:21" s="19" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="375"/>
-      <c r="B5" s="373"/>
+      <c r="A5" s="376"/>
+      <c r="B5" s="374"/>
       <c r="C5" s="39" t="s">
         <v>612</v>
       </c>
@@ -5708,14 +5708,14 @@
       <c r="M5" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="N5" s="373"/>
-      <c r="O5" s="373"/>
-      <c r="P5" s="375"/>
-      <c r="Q5" s="373"/>
-      <c r="R5" s="373"/>
-      <c r="S5" s="373"/>
-      <c r="T5" s="373"/>
-      <c r="U5" s="373"/>
+      <c r="N5" s="374"/>
+      <c r="O5" s="374"/>
+      <c r="P5" s="376"/>
+      <c r="Q5" s="374"/>
+      <c r="R5" s="374"/>
+      <c r="S5" s="374"/>
+      <c r="T5" s="374"/>
+      <c r="U5" s="374"/>
     </row>
     <row r="6" spans="1:21" s="19" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="40" t="s">
@@ -5781,10 +5781,10 @@
       </c>
     </row>
     <row r="7" spans="1:21" s="19" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="372" t="s">
+      <c r="A7" s="373" t="s">
         <v>153</v>
       </c>
-      <c r="B7" s="372"/>
+      <c r="B7" s="373"/>
       <c r="C7" s="46"/>
       <c r="D7" s="40"/>
       <c r="E7" s="40"/>
@@ -6925,57 +6925,57 @@
       <c r="G1" s="224"/>
       <c r="H1" s="224"/>
       <c r="I1" s="224"/>
-      <c r="J1" s="425" t="s">
+      <c r="J1" s="360" t="s">
         <v>1100</v>
       </c>
-      <c r="K1" s="425"/>
-      <c r="L1" s="425"/>
+      <c r="K1" s="360"/>
+      <c r="L1" s="360"/>
     </row>
     <row r="2" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="426" t="s">
+      <c r="A2" s="361" t="s">
         <v>1101</v>
       </c>
-      <c r="B2" s="426"/>
-      <c r="C2" s="426"/>
-      <c r="D2" s="426"/>
-      <c r="E2" s="426"/>
-      <c r="F2" s="426"/>
-      <c r="G2" s="426"/>
-      <c r="H2" s="426"/>
-      <c r="I2" s="426"/>
-      <c r="J2" s="426"/>
+      <c r="B2" s="361"/>
+      <c r="C2" s="361"/>
+      <c r="D2" s="361"/>
+      <c r="E2" s="361"/>
+      <c r="F2" s="361"/>
+      <c r="G2" s="361"/>
+      <c r="H2" s="361"/>
+      <c r="I2" s="361"/>
+      <c r="J2" s="361"/>
     </row>
     <row r="3" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="395" t="s">
+      <c r="A3" s="371" t="s">
         <v>1102</v>
       </c>
-      <c r="B3" s="395" t="s">
+      <c r="B3" s="371" t="s">
         <v>1103</v>
       </c>
-      <c r="C3" s="427" t="s">
+      <c r="C3" s="362" t="s">
         <v>1112</v>
       </c>
-      <c r="D3" s="428"/>
-      <c r="E3" s="427" t="s">
+      <c r="D3" s="363"/>
+      <c r="E3" s="362" t="s">
         <v>1113</v>
       </c>
-      <c r="F3" s="429"/>
-      <c r="G3" s="429"/>
-      <c r="H3" s="429"/>
-      <c r="I3" s="428"/>
-      <c r="J3" s="430" t="s">
+      <c r="F3" s="364"/>
+      <c r="G3" s="364"/>
+      <c r="H3" s="364"/>
+      <c r="I3" s="363"/>
+      <c r="J3" s="365" t="s">
         <v>1113</v>
       </c>
-      <c r="K3" s="432" t="s">
+      <c r="K3" s="367" t="s">
         <v>1118</v>
       </c>
-      <c r="L3" s="434" t="s">
+      <c r="L3" s="369" t="s">
         <v>1104</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A4" s="396"/>
-      <c r="B4" s="396"/>
+      <c r="A4" s="372"/>
+      <c r="B4" s="372"/>
       <c r="C4" s="353" t="s">
         <v>1114</v>
       </c>
@@ -6997,9 +6997,9 @@
       <c r="I4" s="353" t="s">
         <v>1117</v>
       </c>
-      <c r="J4" s="431"/>
-      <c r="K4" s="433"/>
-      <c r="L4" s="435"/>
+      <c r="J4" s="366"/>
+      <c r="K4" s="368"/>
+      <c r="L4" s="370"/>
     </row>
     <row r="5" spans="1:12" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="72">
@@ -7217,44 +7217,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="376" t="s">
+      <c r="A1" s="377" t="s">
         <v>915</v>
       </c>
-      <c r="B1" s="377"/>
-      <c r="C1" s="377"/>
-      <c r="D1" s="378"/>
-      <c r="E1" s="377"/>
-      <c r="F1" s="377"/>
-      <c r="G1" s="377"/>
-      <c r="H1" s="377"/>
-      <c r="I1" s="377"/>
-      <c r="J1" s="377"/>
+      <c r="B1" s="378"/>
+      <c r="C1" s="378"/>
+      <c r="D1" s="379"/>
+      <c r="E1" s="378"/>
+      <c r="F1" s="378"/>
+      <c r="G1" s="378"/>
+      <c r="H1" s="378"/>
+      <c r="I1" s="378"/>
+      <c r="J1" s="378"/>
     </row>
     <row r="2" spans="1:38" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="377"/>
-      <c r="B2" s="377"/>
-      <c r="C2" s="377"/>
-      <c r="D2" s="378"/>
-      <c r="E2" s="377"/>
-      <c r="F2" s="377"/>
-      <c r="G2" s="377"/>
-      <c r="H2" s="377"/>
-      <c r="I2" s="377"/>
-      <c r="J2" s="377"/>
+      <c r="A2" s="378"/>
+      <c r="B2" s="378"/>
+      <c r="C2" s="378"/>
+      <c r="D2" s="379"/>
+      <c r="E2" s="378"/>
+      <c r="F2" s="378"/>
+      <c r="G2" s="378"/>
+      <c r="H2" s="378"/>
+      <c r="I2" s="378"/>
+      <c r="J2" s="378"/>
     </row>
     <row r="3" spans="1:38" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="377" t="s">
+      <c r="A3" s="378" t="s">
         <v>1099</v>
       </c>
-      <c r="B3" s="377"/>
-      <c r="C3" s="377"/>
-      <c r="D3" s="378"/>
-      <c r="E3" s="377"/>
-      <c r="F3" s="377"/>
-      <c r="G3" s="377"/>
-      <c r="H3" s="377"/>
-      <c r="I3" s="377"/>
-      <c r="J3" s="377"/>
+      <c r="B3" s="378"/>
+      <c r="C3" s="378"/>
+      <c r="D3" s="379"/>
+      <c r="E3" s="378"/>
+      <c r="F3" s="378"/>
+      <c r="G3" s="378"/>
+      <c r="H3" s="378"/>
+      <c r="I3" s="378"/>
+      <c r="J3" s="378"/>
     </row>
     <row r="4" spans="1:38" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="244" t="s">
@@ -7263,14 +7263,14 @@
       <c r="B4" s="293" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="380" t="s">
+      <c r="C4" s="381" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="381"/>
-      <c r="E4" s="379"/>
-      <c r="F4" s="379"/>
-      <c r="G4" s="379"/>
-      <c r="H4" s="379"/>
+      <c r="D4" s="382"/>
+      <c r="E4" s="380"/>
+      <c r="F4" s="380"/>
+      <c r="G4" s="380"/>
+      <c r="H4" s="380"/>
       <c r="I4" s="164" t="s">
         <v>35</v>
       </c>
@@ -8566,10 +8566,10 @@
       <c r="J74" s="284"/>
     </row>
     <row r="75" spans="1:10" s="3" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="382" t="s">
+      <c r="A75" s="383" t="s">
         <v>926</v>
       </c>
-      <c r="B75" s="383"/>
+      <c r="B75" s="384"/>
       <c r="C75" s="215"/>
       <c r="D75" s="246"/>
       <c r="E75" s="246"/>
@@ -9668,10 +9668,10 @@
       <c r="M139" s="14"/>
     </row>
     <row r="140" spans="1:13" s="95" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="376" t="s">
+      <c r="A140" s="377" t="s">
         <v>289</v>
       </c>
-      <c r="B140" s="376"/>
+      <c r="B140" s="377"/>
       <c r="C140" s="189">
         <f>SUM(C8:C139)</f>
         <v>142</v>
@@ -9775,18 +9775,18 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="385" t="s">
+      <c r="A2" s="386" t="s">
         <v>911</v>
       </c>
-      <c r="B2" s="385"/>
-      <c r="C2" s="385"/>
-      <c r="D2" s="385"/>
-      <c r="E2" s="385"/>
-      <c r="F2" s="385"/>
-      <c r="G2" s="385"/>
-      <c r="H2" s="385"/>
-      <c r="I2" s="385"/>
-      <c r="J2" s="385"/>
+      <c r="B2" s="386"/>
+      <c r="C2" s="386"/>
+      <c r="D2" s="386"/>
+      <c r="E2" s="386"/>
+      <c r="F2" s="386"/>
+      <c r="G2" s="386"/>
+      <c r="H2" s="386"/>
+      <c r="I2" s="386"/>
+      <c r="J2" s="386"/>
     </row>
     <row r="3" spans="1:13" s="6" customFormat="1" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A3" s="79" t="s">
@@ -9799,9 +9799,9 @@
         <v>19</v>
       </c>
       <c r="D3" s="106"/>
-      <c r="E3" s="386"/>
-      <c r="F3" s="386"/>
-      <c r="G3" s="386"/>
+      <c r="E3" s="387"/>
+      <c r="F3" s="387"/>
+      <c r="G3" s="387"/>
       <c r="H3" s="79" t="s">
         <v>20</v>
       </c>
@@ -9873,18 +9873,18 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="382" t="s">
+      <c r="A6" s="383" t="s">
         <v>747</v>
       </c>
-      <c r="B6" s="383"/>
-      <c r="C6" s="383"/>
-      <c r="D6" s="383"/>
-      <c r="E6" s="383"/>
-      <c r="F6" s="383"/>
-      <c r="G6" s="383"/>
-      <c r="H6" s="383"/>
-      <c r="I6" s="383"/>
-      <c r="J6" s="387"/>
+      <c r="B6" s="384"/>
+      <c r="C6" s="384"/>
+      <c r="D6" s="384"/>
+      <c r="E6" s="384"/>
+      <c r="F6" s="384"/>
+      <c r="G6" s="384"/>
+      <c r="H6" s="384"/>
+      <c r="I6" s="384"/>
+      <c r="J6" s="388"/>
     </row>
     <row r="7" spans="1:13" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="247" t="s">
@@ -13613,10 +13613,10 @@
       <c r="J235" s="123"/>
     </row>
     <row r="236" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="380" t="s">
+      <c r="A236" s="381" t="s">
         <v>289</v>
       </c>
-      <c r="B236" s="384"/>
+      <c r="B236" s="385"/>
       <c r="C236" s="164">
         <f>SUM(C8:C235)</f>
         <v>54</v>
@@ -13736,85 +13736,85 @@
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="388" t="s">
+      <c r="A2" s="389" t="s">
         <v>82</v>
       </c>
-      <c r="B2" s="388"/>
-      <c r="C2" s="388"/>
-      <c r="D2" s="388"/>
-      <c r="E2" s="388"/>
-      <c r="F2" s="388"/>
-      <c r="G2" s="388"/>
-      <c r="H2" s="388"/>
-      <c r="I2" s="388"/>
-      <c r="J2" s="388"/>
-      <c r="K2" s="388"/>
-      <c r="L2" s="388"/>
-      <c r="M2" s="388"/>
-      <c r="N2" s="388"/>
-      <c r="O2" s="388"/>
-      <c r="P2" s="388"/>
-      <c r="Q2" s="388"/>
-      <c r="R2" s="388"/>
-      <c r="S2" s="388"/>
-      <c r="T2" s="388"/>
+      <c r="B2" s="389"/>
+      <c r="C2" s="389"/>
+      <c r="D2" s="389"/>
+      <c r="E2" s="389"/>
+      <c r="F2" s="389"/>
+      <c r="G2" s="389"/>
+      <c r="H2" s="389"/>
+      <c r="I2" s="389"/>
+      <c r="J2" s="389"/>
+      <c r="K2" s="389"/>
+      <c r="L2" s="389"/>
+      <c r="M2" s="389"/>
+      <c r="N2" s="389"/>
+      <c r="O2" s="389"/>
+      <c r="P2" s="389"/>
+      <c r="Q2" s="389"/>
+      <c r="R2" s="389"/>
+      <c r="S2" s="389"/>
+      <c r="T2" s="389"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="37"/>
       <c r="B3" s="100"/>
-      <c r="R3" s="389"/>
-      <c r="S3" s="390"/>
-      <c r="T3" s="390"/>
+      <c r="R3" s="390"/>
+      <c r="S3" s="391"/>
+      <c r="T3" s="391"/>
     </row>
     <row r="4" spans="1:20" s="101" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="391" t="s">
+      <c r="A4" s="392" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="392" t="s">
+      <c r="B4" s="393" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="393" t="s">
+      <c r="C4" s="394" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="394"/>
-      <c r="E4" s="391" t="s">
+      <c r="D4" s="395"/>
+      <c r="E4" s="392" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="391"/>
-      <c r="G4" s="391"/>
-      <c r="H4" s="391"/>
-      <c r="I4" s="391"/>
-      <c r="J4" s="391"/>
-      <c r="K4" s="391"/>
-      <c r="L4" s="391"/>
-      <c r="M4" s="395" t="s">
+      <c r="F4" s="392"/>
+      <c r="G4" s="392"/>
+      <c r="H4" s="392"/>
+      <c r="I4" s="392"/>
+      <c r="J4" s="392"/>
+      <c r="K4" s="392"/>
+      <c r="L4" s="392"/>
+      <c r="M4" s="371" t="s">
         <v>20</v>
       </c>
-      <c r="N4" s="395" t="s">
+      <c r="N4" s="371" t="s">
         <v>34</v>
       </c>
-      <c r="O4" s="397" t="s">
+      <c r="O4" s="396" t="s">
         <v>35</v>
       </c>
-      <c r="P4" s="392" t="s">
+      <c r="P4" s="393" t="s">
         <v>23</v>
       </c>
-      <c r="Q4" s="392" t="s">
+      <c r="Q4" s="393" t="s">
         <v>24</v>
       </c>
-      <c r="R4" s="392" t="s">
+      <c r="R4" s="393" t="s">
         <v>25</v>
       </c>
-      <c r="S4" s="392" t="s">
+      <c r="S4" s="393" t="s">
         <v>26</v>
       </c>
-      <c r="T4" s="399" t="s">
+      <c r="T4" s="398" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:20" s="101" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="391"/>
-      <c r="B5" s="392"/>
+      <c r="A5" s="392"/>
+      <c r="B5" s="393"/>
       <c r="C5" s="250" t="s">
         <v>27</v>
       </c>
@@ -13845,14 +13845,14 @@
       <c r="L5" s="211" t="s">
         <v>30</v>
       </c>
-      <c r="M5" s="396"/>
-      <c r="N5" s="396"/>
-      <c r="O5" s="398"/>
-      <c r="P5" s="392"/>
-      <c r="Q5" s="392"/>
-      <c r="R5" s="392"/>
-      <c r="S5" s="392"/>
-      <c r="T5" s="379"/>
+      <c r="M5" s="372"/>
+      <c r="N5" s="372"/>
+      <c r="O5" s="397"/>
+      <c r="P5" s="393"/>
+      <c r="Q5" s="393"/>
+      <c r="R5" s="393"/>
+      <c r="S5" s="393"/>
+      <c r="T5" s="380"/>
     </row>
     <row r="6" spans="1:20" s="101" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="211" t="s">
@@ -14510,10 +14510,10 @@
       </c>
     </row>
     <row r="28" spans="1:20" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="376" t="s">
+      <c r="A28" s="377" t="s">
         <v>289</v>
       </c>
-      <c r="B28" s="376"/>
+      <c r="B28" s="377"/>
       <c r="C28" s="211">
         <f>SUM(C26:C27)</f>
         <v>60</v>
@@ -14660,72 +14660,72 @@
       </c>
     </row>
     <row r="2" spans="1:20" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A2" s="400" t="s">
+      <c r="A2" s="399" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="400"/>
-      <c r="C2" s="400"/>
-      <c r="D2" s="400"/>
-      <c r="E2" s="400"/>
-      <c r="F2" s="400"/>
-      <c r="G2" s="400"/>
-      <c r="H2" s="400"/>
-      <c r="I2" s="400"/>
-      <c r="J2" s="400"/>
-      <c r="K2" s="400"/>
-      <c r="L2" s="400"/>
-      <c r="M2" s="400"/>
-      <c r="N2" s="400"/>
-      <c r="O2" s="400"/>
-      <c r="P2" s="400"/>
-      <c r="Q2" s="400"/>
+      <c r="B2" s="399"/>
+      <c r="C2" s="399"/>
+      <c r="D2" s="399"/>
+      <c r="E2" s="399"/>
+      <c r="F2" s="399"/>
+      <c r="G2" s="399"/>
+      <c r="H2" s="399"/>
+      <c r="I2" s="399"/>
+      <c r="J2" s="399"/>
+      <c r="K2" s="399"/>
+      <c r="L2" s="399"/>
+      <c r="M2" s="399"/>
+      <c r="N2" s="399"/>
+      <c r="O2" s="399"/>
+      <c r="P2" s="399"/>
+      <c r="Q2" s="399"/>
     </row>
     <row r="3" spans="1:20" s="101" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="397" t="s">
+      <c r="A3" s="396" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="399" t="s">
+      <c r="B3" s="398" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="391" t="s">
+      <c r="C3" s="392" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="391"/>
-      <c r="E3" s="391" t="s">
+      <c r="D3" s="392"/>
+      <c r="E3" s="392" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="391"/>
-      <c r="G3" s="391"/>
-      <c r="H3" s="391"/>
-      <c r="I3" s="391"/>
-      <c r="J3" s="399" t="s">
+      <c r="F3" s="392"/>
+      <c r="G3" s="392"/>
+      <c r="H3" s="392"/>
+      <c r="I3" s="392"/>
+      <c r="J3" s="398" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="399" t="s">
+      <c r="K3" s="398" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="399" t="s">
+      <c r="L3" s="398" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="399" t="s">
+      <c r="M3" s="398" t="s">
         <v>23</v>
       </c>
-      <c r="N3" s="399" t="s">
+      <c r="N3" s="398" t="s">
         <v>24</v>
       </c>
-      <c r="O3" s="399" t="s">
+      <c r="O3" s="398" t="s">
         <v>25</v>
       </c>
-      <c r="P3" s="399" t="s">
+      <c r="P3" s="398" t="s">
         <v>26</v>
       </c>
-      <c r="Q3" s="399" t="s">
+      <c r="Q3" s="398" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:20" s="101" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="398"/>
-      <c r="B4" s="399"/>
+      <c r="A4" s="397"/>
+      <c r="B4" s="398"/>
       <c r="C4" s="276" t="s">
         <v>27</v>
       </c>
@@ -14747,14 +14747,14 @@
       <c r="I4" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="399"/>
-      <c r="K4" s="399"/>
-      <c r="L4" s="399"/>
-      <c r="M4" s="399"/>
-      <c r="N4" s="399"/>
-      <c r="O4" s="399"/>
-      <c r="P4" s="399"/>
-      <c r="Q4" s="379"/>
+      <c r="J4" s="398"/>
+      <c r="K4" s="398"/>
+      <c r="L4" s="398"/>
+      <c r="M4" s="398"/>
+      <c r="N4" s="398"/>
+      <c r="O4" s="398"/>
+      <c r="P4" s="398"/>
+      <c r="Q4" s="380"/>
       <c r="T4" s="101" t="s">
         <v>282</v>
       </c>
@@ -16717,74 +16717,74 @@
       </c>
     </row>
     <row r="2" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="404" t="s">
+      <c r="A2" s="403" t="s">
         <v>587</v>
       </c>
-      <c r="B2" s="404"/>
-      <c r="C2" s="404"/>
-      <c r="D2" s="404"/>
-      <c r="E2" s="404"/>
-      <c r="F2" s="404"/>
-      <c r="G2" s="404"/>
-      <c r="H2" s="404"/>
-      <c r="I2" s="404"/>
-      <c r="J2" s="404"/>
-      <c r="K2" s="404"/>
-      <c r="L2" s="404"/>
-      <c r="M2" s="404"/>
-      <c r="N2" s="404"/>
-      <c r="O2" s="404"/>
-      <c r="P2" s="404"/>
-      <c r="Q2" s="404"/>
-      <c r="R2" s="404"/>
+      <c r="B2" s="403"/>
+      <c r="C2" s="403"/>
+      <c r="D2" s="403"/>
+      <c r="E2" s="403"/>
+      <c r="F2" s="403"/>
+      <c r="G2" s="403"/>
+      <c r="H2" s="403"/>
+      <c r="I2" s="403"/>
+      <c r="J2" s="403"/>
+      <c r="K2" s="403"/>
+      <c r="L2" s="403"/>
+      <c r="M2" s="403"/>
+      <c r="N2" s="403"/>
+      <c r="O2" s="403"/>
+      <c r="P2" s="403"/>
+      <c r="Q2" s="403"/>
+      <c r="R2" s="403"/>
     </row>
     <row r="3" spans="1:18" s="95" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="379" t="s">
+      <c r="A3" s="380" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="399" t="s">
+      <c r="B3" s="398" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="379" t="s">
+      <c r="C3" s="380" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="379"/>
-      <c r="E3" s="379" t="s">
+      <c r="D3" s="380"/>
+      <c r="E3" s="380" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="379"/>
-      <c r="G3" s="379"/>
-      <c r="H3" s="379"/>
-      <c r="I3" s="379"/>
-      <c r="J3" s="379"/>
-      <c r="K3" s="399" t="s">
+      <c r="F3" s="380"/>
+      <c r="G3" s="380"/>
+      <c r="H3" s="380"/>
+      <c r="I3" s="380"/>
+      <c r="J3" s="380"/>
+      <c r="K3" s="398" t="s">
         <v>20</v>
       </c>
-      <c r="L3" s="399" t="s">
+      <c r="L3" s="398" t="s">
         <v>34</v>
       </c>
-      <c r="M3" s="399" t="s">
+      <c r="M3" s="398" t="s">
         <v>586</v>
       </c>
-      <c r="N3" s="399" t="s">
+      <c r="N3" s="398" t="s">
         <v>23</v>
       </c>
-      <c r="O3" s="399" t="s">
+      <c r="O3" s="398" t="s">
         <v>24</v>
       </c>
-      <c r="P3" s="399" t="s">
+      <c r="P3" s="398" t="s">
         <v>25</v>
       </c>
-      <c r="Q3" s="399" t="s">
+      <c r="Q3" s="398" t="s">
         <v>26</v>
       </c>
-      <c r="R3" s="399" t="s">
+      <c r="R3" s="398" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:18" s="95" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="379"/>
-      <c r="B4" s="399"/>
+      <c r="A4" s="380"/>
+      <c r="B4" s="398"/>
       <c r="C4" s="244" t="s">
         <v>27</v>
       </c>
@@ -16809,14 +16809,14 @@
       <c r="J4" s="164" t="s">
         <v>30</v>
       </c>
-      <c r="K4" s="399"/>
-      <c r="L4" s="399"/>
-      <c r="M4" s="379"/>
-      <c r="N4" s="399"/>
-      <c r="O4" s="399"/>
-      <c r="P4" s="399"/>
-      <c r="Q4" s="399"/>
-      <c r="R4" s="379"/>
+      <c r="K4" s="398"/>
+      <c r="L4" s="398"/>
+      <c r="M4" s="380"/>
+      <c r="N4" s="398"/>
+      <c r="O4" s="398"/>
+      <c r="P4" s="398"/>
+      <c r="Q4" s="398"/>
+      <c r="R4" s="380"/>
     </row>
     <row r="5" spans="1:18" s="3" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -16879,22 +16879,22 @@
         <v>584</v>
       </c>
       <c r="B6" s="60"/>
-      <c r="C6" s="401"/>
-      <c r="D6" s="402"/>
-      <c r="E6" s="402"/>
-      <c r="F6" s="402"/>
-      <c r="G6" s="402"/>
-      <c r="H6" s="402"/>
-      <c r="I6" s="402"/>
-      <c r="J6" s="402"/>
-      <c r="K6" s="402"/>
-      <c r="L6" s="402"/>
-      <c r="M6" s="402"/>
-      <c r="N6" s="402"/>
-      <c r="O6" s="402"/>
-      <c r="P6" s="402"/>
-      <c r="Q6" s="402"/>
-      <c r="R6" s="403"/>
+      <c r="C6" s="400"/>
+      <c r="D6" s="401"/>
+      <c r="E6" s="401"/>
+      <c r="F6" s="401"/>
+      <c r="G6" s="401"/>
+      <c r="H6" s="401"/>
+      <c r="I6" s="401"/>
+      <c r="J6" s="401"/>
+      <c r="K6" s="401"/>
+      <c r="L6" s="401"/>
+      <c r="M6" s="401"/>
+      <c r="N6" s="401"/>
+      <c r="O6" s="401"/>
+      <c r="P6" s="401"/>
+      <c r="Q6" s="401"/>
+      <c r="R6" s="402"/>
     </row>
     <row r="7" spans="1:18" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
@@ -22533,24 +22533,24 @@
       </c>
     </row>
     <row r="2" spans="1:16" s="138" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="400" t="s">
+      <c r="A2" s="399" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="400"/>
-      <c r="C2" s="400"/>
-      <c r="D2" s="400"/>
-      <c r="E2" s="400"/>
-      <c r="F2" s="400"/>
-      <c r="G2" s="400"/>
-      <c r="H2" s="400"/>
-      <c r="I2" s="400"/>
-      <c r="J2" s="400"/>
-      <c r="K2" s="400"/>
-      <c r="L2" s="400"/>
-      <c r="M2" s="400"/>
-      <c r="N2" s="400"/>
-      <c r="O2" s="400"/>
-      <c r="P2" s="400"/>
+      <c r="B2" s="399"/>
+      <c r="C2" s="399"/>
+      <c r="D2" s="399"/>
+      <c r="E2" s="399"/>
+      <c r="F2" s="399"/>
+      <c r="G2" s="399"/>
+      <c r="H2" s="399"/>
+      <c r="I2" s="399"/>
+      <c r="J2" s="399"/>
+      <c r="K2" s="399"/>
+      <c r="L2" s="399"/>
+      <c r="M2" s="399"/>
+      <c r="N2" s="399"/>
+      <c r="O2" s="399"/>
+      <c r="P2" s="399"/>
     </row>
     <row r="3" spans="1:16" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="107" t="s">
@@ -24481,10 +24481,10 @@
       <c r="A85" s="108">
         <v>31</v>
       </c>
-      <c r="B85" s="408" t="s">
+      <c r="B85" s="407" t="s">
         <v>226</v>
       </c>
-      <c r="C85" s="409"/>
+      <c r="C85" s="408"/>
       <c r="D85" s="51"/>
       <c r="E85" s="51"/>
       <c r="F85" s="51"/>
@@ -25458,10 +25458,10 @@
       <c r="A123" s="1">
         <v>67</v>
       </c>
-      <c r="B123" s="412" t="s">
+      <c r="B123" s="411" t="s">
         <v>257</v>
       </c>
-      <c r="C123" s="413"/>
+      <c r="C123" s="412"/>
       <c r="D123" s="51"/>
       <c r="E123" s="51"/>
       <c r="F123" s="51"/>
@@ -26308,10 +26308,10 @@
       <c r="A160" s="1">
         <v>104</v>
       </c>
-      <c r="B160" s="410" t="s">
+      <c r="B160" s="409" t="s">
         <v>928</v>
       </c>
-      <c r="C160" s="411"/>
+      <c r="C160" s="410"/>
       <c r="D160" s="51"/>
       <c r="E160" s="51"/>
       <c r="F160" s="51"/>
@@ -26484,10 +26484,10 @@
       <c r="A168" s="1">
         <v>112</v>
       </c>
-      <c r="B168" s="414" t="s">
+      <c r="B168" s="413" t="s">
         <v>957</v>
       </c>
-      <c r="C168" s="415"/>
+      <c r="C168" s="414"/>
       <c r="D168" s="52"/>
       <c r="E168" s="51"/>
       <c r="F168" s="51"/>
@@ -26506,10 +26506,10 @@
       <c r="A169" s="282">
         <v>113</v>
       </c>
-      <c r="B169" s="416" t="s">
+      <c r="B169" s="415" t="s">
         <v>960</v>
       </c>
-      <c r="C169" s="417"/>
+      <c r="C169" s="416"/>
       <c r="D169" s="52"/>
       <c r="E169" s="52"/>
       <c r="F169" s="51"/>
@@ -26528,10 +26528,10 @@
       <c r="A170" s="282">
         <v>114</v>
       </c>
-      <c r="B170" s="416" t="s">
+      <c r="B170" s="415" t="s">
         <v>959</v>
       </c>
-      <c r="C170" s="417"/>
+      <c r="C170" s="416"/>
       <c r="D170" s="52"/>
       <c r="E170" s="52"/>
       <c r="F170" s="51"/>
@@ -26547,11 +26547,11 @@
       <c r="P170" s="56"/>
     </row>
     <row r="171" spans="1:16" s="36" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="405" t="s">
+      <c r="A171" s="404" t="s">
         <v>596</v>
       </c>
-      <c r="B171" s="406"/>
-      <c r="C171" s="407"/>
+      <c r="B171" s="405"/>
+      <c r="C171" s="406"/>
       <c r="D171" s="217">
         <f>SUBTOTAL(9,D72:D131)</f>
         <v>103</v>
@@ -26656,79 +26656,79 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2927" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="R1" s="420" t="s">
+      <c r="R1" s="419" t="s">
         <v>655</v>
       </c>
-      <c r="S1" s="420"/>
-      <c r="T1" s="420"/>
+      <c r="S1" s="419"/>
+      <c r="T1" s="419"/>
     </row>
     <row r="2" spans="1:2927" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="385" t="s">
+      <c r="A2" s="386" t="s">
         <v>660</v>
       </c>
-      <c r="B2" s="385"/>
-      <c r="C2" s="385"/>
-      <c r="D2" s="385"/>
-      <c r="E2" s="385"/>
-      <c r="F2" s="385"/>
-      <c r="G2" s="385"/>
-      <c r="H2" s="385"/>
-      <c r="I2" s="385"/>
-      <c r="J2" s="385"/>
-      <c r="K2" s="385"/>
-      <c r="L2" s="385"/>
-      <c r="M2" s="385"/>
-      <c r="N2" s="385"/>
-      <c r="O2" s="385"/>
-      <c r="P2" s="385"/>
-      <c r="Q2" s="385"/>
-      <c r="R2" s="385"/>
-      <c r="S2" s="385"/>
-      <c r="T2" s="385"/>
+      <c r="B2" s="386"/>
+      <c r="C2" s="386"/>
+      <c r="D2" s="386"/>
+      <c r="E2" s="386"/>
+      <c r="F2" s="386"/>
+      <c r="G2" s="386"/>
+      <c r="H2" s="386"/>
+      <c r="I2" s="386"/>
+      <c r="J2" s="386"/>
+      <c r="K2" s="386"/>
+      <c r="L2" s="386"/>
+      <c r="M2" s="386"/>
+      <c r="N2" s="386"/>
+      <c r="O2" s="386"/>
+      <c r="P2" s="386"/>
+      <c r="Q2" s="386"/>
+      <c r="R2" s="386"/>
+      <c r="S2" s="386"/>
+      <c r="T2" s="386"/>
     </row>
     <row r="3" spans="1:2927" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="399" t="s">
+      <c r="A3" s="398" t="s">
         <v>291</v>
       </c>
-      <c r="B3" s="421" t="s">
+      <c r="B3" s="420" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="379" t="s">
+      <c r="C3" s="380" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="379"/>
-      <c r="E3" s="379" t="s">
+      <c r="D3" s="380"/>
+      <c r="E3" s="380" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="379"/>
-      <c r="G3" s="379"/>
-      <c r="H3" s="379"/>
-      <c r="I3" s="379"/>
-      <c r="J3" s="379"/>
-      <c r="K3" s="379"/>
-      <c r="L3" s="379"/>
-      <c r="M3" s="422" t="s">
+      <c r="F3" s="380"/>
+      <c r="G3" s="380"/>
+      <c r="H3" s="380"/>
+      <c r="I3" s="380"/>
+      <c r="J3" s="380"/>
+      <c r="K3" s="380"/>
+      <c r="L3" s="380"/>
+      <c r="M3" s="421" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="422" t="s">
+      <c r="N3" s="421" t="s">
         <v>292</v>
       </c>
-      <c r="O3" s="379" t="s">
+      <c r="O3" s="380" t="s">
         <v>35</v>
       </c>
-      <c r="P3" s="424" t="s">
+      <c r="P3" s="423" t="s">
         <v>23</v>
       </c>
-      <c r="Q3" s="424" t="s">
+      <c r="Q3" s="423" t="s">
         <v>24</v>
       </c>
-      <c r="R3" s="424" t="s">
+      <c r="R3" s="423" t="s">
         <v>25</v>
       </c>
-      <c r="S3" s="424" t="s">
+      <c r="S3" s="423" t="s">
         <v>26</v>
       </c>
-      <c r="T3" s="399" t="s">
+      <c r="T3" s="398" t="s">
         <v>961</v>
       </c>
       <c r="U3" s="6"/>
@@ -29640,8 +29640,8 @@
       <c r="DHO3" s="6"/>
     </row>
     <row r="4" spans="1:2927" s="1" customFormat="1" ht="31.2" x14ac:dyDescent="0.25">
-      <c r="A4" s="399"/>
-      <c r="B4" s="421"/>
+      <c r="A4" s="398"/>
+      <c r="B4" s="420"/>
       <c r="C4" s="244" t="s">
         <v>27</v>
       </c>
@@ -29672,14 +29672,14 @@
       <c r="L4" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="M4" s="423"/>
-      <c r="N4" s="423"/>
-      <c r="O4" s="379"/>
-      <c r="P4" s="424"/>
-      <c r="Q4" s="424"/>
-      <c r="R4" s="424"/>
-      <c r="S4" s="424"/>
-      <c r="T4" s="379"/>
+      <c r="M4" s="422"/>
+      <c r="N4" s="422"/>
+      <c r="O4" s="380"/>
+      <c r="P4" s="423"/>
+      <c r="Q4" s="423"/>
+      <c r="R4" s="423"/>
+      <c r="S4" s="423"/>
+      <c r="T4" s="380"/>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
       <c r="W4" s="6"/>
@@ -35558,12 +35558,12 @@
       <c r="DHO5" s="6"/>
     </row>
     <row r="6" spans="1:2927" s="3" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="418" t="s">
+      <c r="A6" s="417" t="s">
         <v>627</v>
       </c>
-      <c r="B6" s="419"/>
-      <c r="C6" s="419"/>
-      <c r="D6" s="419"/>
+      <c r="B6" s="418"/>
+      <c r="C6" s="418"/>
+      <c r="D6" s="418"/>
       <c r="E6" s="205"/>
       <c r="F6" s="205"/>
       <c r="G6" s="205"/>
@@ -68365,10 +68365,10 @@
       <c r="T37" s="108"/>
     </row>
     <row r="38" spans="1:20" s="101" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="376" t="s">
+      <c r="A38" s="377" t="s">
         <v>289</v>
       </c>
-      <c r="B38" s="376"/>
+      <c r="B38" s="377"/>
       <c r="C38" s="164"/>
       <c r="D38" s="164"/>
       <c r="E38" s="164"/>
@@ -68473,48 +68473,48 @@
       <c r="J2" s="222"/>
     </row>
     <row r="3" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="360" t="s">
+      <c r="A3" s="432" t="s">
         <v>939</v>
       </c>
-      <c r="B3" s="360"/>
-      <c r="C3" s="360"/>
-      <c r="D3" s="360"/>
-      <c r="E3" s="360"/>
-      <c r="F3" s="360"/>
-      <c r="G3" s="360"/>
-      <c r="H3" s="360"/>
-      <c r="I3" s="360"/>
-      <c r="J3" s="360"/>
+      <c r="B3" s="432"/>
+      <c r="C3" s="432"/>
+      <c r="D3" s="432"/>
+      <c r="E3" s="432"/>
+      <c r="F3" s="432"/>
+      <c r="G3" s="432"/>
+      <c r="H3" s="432"/>
+      <c r="I3" s="432"/>
+      <c r="J3" s="432"/>
     </row>
     <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="361" t="s">
+      <c r="A4" s="429" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="361" t="s">
+      <c r="B4" s="429" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="362" t="s">
+      <c r="C4" s="433" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="362"/>
-      <c r="E4" s="362" t="s">
+      <c r="D4" s="433"/>
+      <c r="E4" s="433" t="s">
         <v>940</v>
       </c>
-      <c r="F4" s="362"/>
-      <c r="G4" s="362"/>
-      <c r="H4" s="361" t="s">
+      <c r="F4" s="433"/>
+      <c r="G4" s="433"/>
+      <c r="H4" s="429" t="s">
         <v>941</v>
       </c>
-      <c r="I4" s="363" t="s">
+      <c r="I4" s="434" t="s">
         <v>942</v>
       </c>
-      <c r="J4" s="364" t="s">
+      <c r="J4" s="435" t="s">
         <v>962</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="361"/>
-      <c r="B5" s="361"/>
+      <c r="A5" s="429"/>
+      <c r="B5" s="429"/>
       <c r="C5" s="227" t="s">
         <v>27</v>
       </c>
@@ -68530,15 +68530,15 @@
       <c r="G5" s="226" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="361"/>
-      <c r="I5" s="363"/>
-      <c r="J5" s="364"/>
+      <c r="H5" s="429"/>
+      <c r="I5" s="434"/>
+      <c r="J5" s="435"/>
     </row>
     <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="366" t="s">
+      <c r="A6" s="425" t="s">
         <v>1049</v>
       </c>
-      <c r="B6" s="367"/>
+      <c r="B6" s="426"/>
       <c r="C6" s="227"/>
       <c r="D6" s="227"/>
       <c r="E6" s="226"/>
@@ -69959,10 +69959,10 @@
       <c r="J93" s="328"/>
     </row>
     <row r="94" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="361" t="s">
+      <c r="A94" s="429" t="s">
         <v>1047</v>
       </c>
-      <c r="B94" s="361"/>
+      <c r="B94" s="429"/>
       <c r="C94" s="229"/>
       <c r="D94" s="229"/>
       <c r="E94" s="229"/>
@@ -69989,10 +69989,10 @@
       <c r="J95" s="229"/>
     </row>
     <row r="96" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="370" t="s">
+      <c r="A96" s="430" t="s">
         <v>596</v>
       </c>
-      <c r="B96" s="371"/>
+      <c r="B96" s="431"/>
       <c r="C96" s="304"/>
       <c r="D96" s="304"/>
       <c r="E96" s="304"/>
@@ -70003,18 +70003,18 @@
       <c r="J96" s="304"/>
     </row>
     <row r="97" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="365" t="s">
+      <c r="A97" s="424" t="s">
         <v>1050</v>
       </c>
-      <c r="B97" s="365"/>
-      <c r="C97" s="365"/>
-      <c r="D97" s="365"/>
-      <c r="E97" s="365"/>
-      <c r="F97" s="365"/>
-      <c r="G97" s="365"/>
-      <c r="H97" s="365"/>
-      <c r="I97" s="365"/>
-      <c r="J97" s="365"/>
+      <c r="B97" s="424"/>
+      <c r="C97" s="424"/>
+      <c r="D97" s="424"/>
+      <c r="E97" s="424"/>
+      <c r="F97" s="424"/>
+      <c r="G97" s="424"/>
+      <c r="H97" s="424"/>
+      <c r="I97" s="424"/>
+      <c r="J97" s="424"/>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="327">
@@ -70423,10 +70423,10 @@
       <c r="J122" s="229"/>
     </row>
     <row r="123" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="368" t="s">
+      <c r="A123" s="427" t="s">
         <v>596</v>
       </c>
-      <c r="B123" s="369"/>
+      <c r="B123" s="428"/>
       <c r="C123" s="229"/>
       <c r="D123" s="229"/>
       <c r="E123" s="229"/>
@@ -70445,11 +70445,6 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="13">
-    <mergeCell ref="A97:J97"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A123:B123"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="A96:B96"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B4:B5"/>
@@ -70458,6 +70453,11 @@
     <mergeCell ref="H4:H5"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
+    <mergeCell ref="A97:J97"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A123:B123"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="A96:B96"/>
   </mergeCells>
   <conditionalFormatting sqref="D1">
     <cfRule type="iconSet" priority="2">

--- a/data/FRS_cleaned/Nov/Fmn G Nov/Nov 2025-G.xlsx
+++ b/data/FRS_cleaned/Nov/Fmn G Nov/Nov 2025-G.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{27206D68-33BE-482D-802F-57DE02E6DC52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9DD6BE3-553E-47CA-8DB8-DDD92DBE784E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="A Vehicle" sheetId="20" r:id="rId1"/>
@@ -45,17 +45,6 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <fileRecoveryPr autoRecover="0"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -5009,45 +4998,6 @@
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -5116,6 +5066,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -5205,6 +5161,21 @@
     <xf numFmtId="2" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -5220,26 +5191,44 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -5601,80 +5590,80 @@
       <c r="U2" s="92"/>
     </row>
     <row r="3" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="375" t="s">
+      <c r="A3" s="362" t="s">
         <v>392</v>
       </c>
-      <c r="B3" s="375"/>
-      <c r="C3" s="375"/>
-      <c r="D3" s="375"/>
-      <c r="E3" s="375"/>
-      <c r="F3" s="375"/>
-      <c r="G3" s="375"/>
-      <c r="H3" s="375"/>
-      <c r="I3" s="375"/>
-      <c r="J3" s="375"/>
-      <c r="K3" s="375"/>
-      <c r="L3" s="375"/>
-      <c r="M3" s="375"/>
-      <c r="N3" s="375"/>
-      <c r="O3" s="375"/>
-      <c r="P3" s="375"/>
-      <c r="Q3" s="375"/>
-      <c r="R3" s="375"/>
-      <c r="S3" s="375"/>
-      <c r="T3" s="375"/>
-      <c r="U3" s="375"/>
+      <c r="B3" s="362"/>
+      <c r="C3" s="362"/>
+      <c r="D3" s="362"/>
+      <c r="E3" s="362"/>
+      <c r="F3" s="362"/>
+      <c r="G3" s="362"/>
+      <c r="H3" s="362"/>
+      <c r="I3" s="362"/>
+      <c r="J3" s="362"/>
+      <c r="K3" s="362"/>
+      <c r="L3" s="362"/>
+      <c r="M3" s="362"/>
+      <c r="N3" s="362"/>
+      <c r="O3" s="362"/>
+      <c r="P3" s="362"/>
+      <c r="Q3" s="362"/>
+      <c r="R3" s="362"/>
+      <c r="S3" s="362"/>
+      <c r="T3" s="362"/>
+      <c r="U3" s="362"/>
     </row>
     <row r="4" spans="1:21" s="19" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="376" t="s">
+      <c r="A4" s="363" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="374" t="s">
+      <c r="B4" s="361" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="39"/>
-      <c r="D4" s="376" t="s">
+      <c r="D4" s="363" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="376"/>
-      <c r="F4" s="376" t="s">
+      <c r="E4" s="363"/>
+      <c r="F4" s="363" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="376"/>
-      <c r="H4" s="376"/>
-      <c r="I4" s="376"/>
-      <c r="J4" s="376"/>
-      <c r="K4" s="376"/>
-      <c r="L4" s="376"/>
-      <c r="M4" s="376"/>
-      <c r="N4" s="374" t="s">
+      <c r="G4" s="363"/>
+      <c r="H4" s="363"/>
+      <c r="I4" s="363"/>
+      <c r="J4" s="363"/>
+      <c r="K4" s="363"/>
+      <c r="L4" s="363"/>
+      <c r="M4" s="363"/>
+      <c r="N4" s="361" t="s">
         <v>20</v>
       </c>
-      <c r="O4" s="374" t="s">
+      <c r="O4" s="361" t="s">
         <v>34</v>
       </c>
-      <c r="P4" s="376" t="s">
+      <c r="P4" s="363" t="s">
         <v>35</v>
       </c>
-      <c r="Q4" s="374" t="s">
+      <c r="Q4" s="361" t="s">
         <v>23</v>
       </c>
-      <c r="R4" s="374" t="s">
+      <c r="R4" s="361" t="s">
         <v>24</v>
       </c>
-      <c r="S4" s="374" t="s">
+      <c r="S4" s="361" t="s">
         <v>25</v>
       </c>
-      <c r="T4" s="374" t="s">
+      <c r="T4" s="361" t="s">
         <v>26</v>
       </c>
-      <c r="U4" s="374" t="s">
+      <c r="U4" s="361" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:21" s="19" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="376"/>
-      <c r="B5" s="374"/>
+      <c r="A5" s="363"/>
+      <c r="B5" s="361"/>
       <c r="C5" s="39" t="s">
         <v>612</v>
       </c>
@@ -5708,14 +5697,14 @@
       <c r="M5" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="N5" s="374"/>
-      <c r="O5" s="374"/>
-      <c r="P5" s="376"/>
-      <c r="Q5" s="374"/>
-      <c r="R5" s="374"/>
-      <c r="S5" s="374"/>
-      <c r="T5" s="374"/>
-      <c r="U5" s="374"/>
+      <c r="N5" s="361"/>
+      <c r="O5" s="361"/>
+      <c r="P5" s="363"/>
+      <c r="Q5" s="361"/>
+      <c r="R5" s="361"/>
+      <c r="S5" s="361"/>
+      <c r="T5" s="361"/>
+      <c r="U5" s="361"/>
     </row>
     <row r="6" spans="1:21" s="19" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="40" t="s">
@@ -5781,10 +5770,10 @@
       </c>
     </row>
     <row r="7" spans="1:21" s="19" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="373" t="s">
+      <c r="A7" s="360" t="s">
         <v>153</v>
       </c>
-      <c r="B7" s="373"/>
+      <c r="B7" s="360"/>
       <c r="C7" s="46"/>
       <c r="D7" s="40"/>
       <c r="E7" s="40"/>
@@ -6925,57 +6914,57 @@
       <c r="G1" s="224"/>
       <c r="H1" s="224"/>
       <c r="I1" s="224"/>
-      <c r="J1" s="360" t="s">
+      <c r="J1" s="425" t="s">
         <v>1100</v>
       </c>
-      <c r="K1" s="360"/>
-      <c r="L1" s="360"/>
+      <c r="K1" s="425"/>
+      <c r="L1" s="425"/>
     </row>
     <row r="2" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="361" t="s">
+      <c r="A2" s="426" t="s">
         <v>1101</v>
       </c>
-      <c r="B2" s="361"/>
-      <c r="C2" s="361"/>
-      <c r="D2" s="361"/>
-      <c r="E2" s="361"/>
-      <c r="F2" s="361"/>
-      <c r="G2" s="361"/>
-      <c r="H2" s="361"/>
-      <c r="I2" s="361"/>
-      <c r="J2" s="361"/>
+      <c r="B2" s="426"/>
+      <c r="C2" s="426"/>
+      <c r="D2" s="426"/>
+      <c r="E2" s="426"/>
+      <c r="F2" s="426"/>
+      <c r="G2" s="426"/>
+      <c r="H2" s="426"/>
+      <c r="I2" s="426"/>
+      <c r="J2" s="426"/>
     </row>
     <row r="3" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="371" t="s">
+      <c r="A3" s="383" t="s">
         <v>1102</v>
       </c>
-      <c r="B3" s="371" t="s">
+      <c r="B3" s="383" t="s">
         <v>1103</v>
       </c>
-      <c r="C3" s="362" t="s">
+      <c r="C3" s="427" t="s">
         <v>1112</v>
       </c>
-      <c r="D3" s="363"/>
-      <c r="E3" s="362" t="s">
+      <c r="D3" s="428"/>
+      <c r="E3" s="427" t="s">
         <v>1113</v>
       </c>
-      <c r="F3" s="364"/>
-      <c r="G3" s="364"/>
-      <c r="H3" s="364"/>
-      <c r="I3" s="363"/>
-      <c r="J3" s="365" t="s">
+      <c r="F3" s="429"/>
+      <c r="G3" s="429"/>
+      <c r="H3" s="429"/>
+      <c r="I3" s="428"/>
+      <c r="J3" s="430" t="s">
         <v>1113</v>
       </c>
-      <c r="K3" s="367" t="s">
+      <c r="K3" s="432" t="s">
         <v>1118</v>
       </c>
-      <c r="L3" s="369" t="s">
+      <c r="L3" s="434" t="s">
         <v>1104</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A4" s="372"/>
-      <c r="B4" s="372"/>
+      <c r="A4" s="384"/>
+      <c r="B4" s="384"/>
       <c r="C4" s="353" t="s">
         <v>1114</v>
       </c>
@@ -6997,9 +6986,9 @@
       <c r="I4" s="353" t="s">
         <v>1117</v>
       </c>
-      <c r="J4" s="366"/>
-      <c r="K4" s="368"/>
-      <c r="L4" s="370"/>
+      <c r="J4" s="431"/>
+      <c r="K4" s="433"/>
+      <c r="L4" s="435"/>
     </row>
     <row r="5" spans="1:12" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="72">
@@ -7194,7 +7183,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:AL140"/>
@@ -7217,44 +7206,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="377" t="s">
+      <c r="A1" s="364" t="s">
         <v>915</v>
       </c>
-      <c r="B1" s="378"/>
-      <c r="C1" s="378"/>
-      <c r="D1" s="379"/>
-      <c r="E1" s="378"/>
-      <c r="F1" s="378"/>
-      <c r="G1" s="378"/>
-      <c r="H1" s="378"/>
-      <c r="I1" s="378"/>
-      <c r="J1" s="378"/>
+      <c r="B1" s="365"/>
+      <c r="C1" s="365"/>
+      <c r="D1" s="366"/>
+      <c r="E1" s="365"/>
+      <c r="F1" s="365"/>
+      <c r="G1" s="365"/>
+      <c r="H1" s="365"/>
+      <c r="I1" s="365"/>
+      <c r="J1" s="365"/>
     </row>
     <row r="2" spans="1:38" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="378"/>
-      <c r="B2" s="378"/>
-      <c r="C2" s="378"/>
-      <c r="D2" s="379"/>
-      <c r="E2" s="378"/>
-      <c r="F2" s="378"/>
-      <c r="G2" s="378"/>
-      <c r="H2" s="378"/>
-      <c r="I2" s="378"/>
-      <c r="J2" s="378"/>
+      <c r="A2" s="365"/>
+      <c r="B2" s="365"/>
+      <c r="C2" s="365"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="365"/>
+      <c r="F2" s="365"/>
+      <c r="G2" s="365"/>
+      <c r="H2" s="365"/>
+      <c r="I2" s="365"/>
+      <c r="J2" s="365"/>
     </row>
     <row r="3" spans="1:38" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="378" t="s">
+      <c r="A3" s="365" t="s">
         <v>1099</v>
       </c>
-      <c r="B3" s="378"/>
-      <c r="C3" s="378"/>
-      <c r="D3" s="379"/>
-      <c r="E3" s="378"/>
-      <c r="F3" s="378"/>
-      <c r="G3" s="378"/>
-      <c r="H3" s="378"/>
-      <c r="I3" s="378"/>
-      <c r="J3" s="378"/>
+      <c r="B3" s="365"/>
+      <c r="C3" s="365"/>
+      <c r="D3" s="366"/>
+      <c r="E3" s="365"/>
+      <c r="F3" s="365"/>
+      <c r="G3" s="365"/>
+      <c r="H3" s="365"/>
+      <c r="I3" s="365"/>
+      <c r="J3" s="365"/>
     </row>
     <row r="4" spans="1:38" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="244" t="s">
@@ -7263,14 +7252,14 @@
       <c r="B4" s="293" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="381" t="s">
+      <c r="C4" s="368" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="382"/>
-      <c r="E4" s="380"/>
-      <c r="F4" s="380"/>
-      <c r="G4" s="380"/>
-      <c r="H4" s="380"/>
+      <c r="D4" s="369"/>
+      <c r="E4" s="367"/>
+      <c r="F4" s="367"/>
+      <c r="G4" s="367"/>
+      <c r="H4" s="367"/>
       <c r="I4" s="164" t="s">
         <v>35</v>
       </c>
@@ -7390,7 +7379,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:38" s="3" customFormat="1" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:38" s="3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="60" t="s">
         <v>296</v>
       </c>
@@ -7472,7 +7461,7 @@
       </c>
       <c r="J10" s="292"/>
     </row>
-    <row r="11" spans="1:38" s="3" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:38" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="59">
         <v>4</v>
       </c>
@@ -7488,7 +7477,7 @@
       <c r="I11" s="1"/>
       <c r="J11" s="96"/>
     </row>
-    <row r="12" spans="1:38" s="3" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:38" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>5</v>
       </c>
@@ -7504,7 +7493,7 @@
       <c r="I12" s="1"/>
       <c r="J12" s="96"/>
     </row>
-    <row r="13" spans="1:38" s="3" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:38" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="59">
         <v>6</v>
       </c>
@@ -7520,7 +7509,7 @@
       <c r="I13" s="1"/>
       <c r="J13" s="172"/>
     </row>
-    <row r="14" spans="1:38" s="3" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:38" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>7</v>
       </c>
@@ -7536,7 +7525,7 @@
       <c r="I14" s="1"/>
       <c r="J14" s="172"/>
     </row>
-    <row r="15" spans="1:38" s="3" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:38" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="59">
         <v>8</v>
       </c>
@@ -7574,7 +7563,7 @@
       </c>
       <c r="J16" s="262"/>
     </row>
-    <row r="17" spans="1:10" s="132" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" s="132" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="59">
         <v>10</v>
       </c>
@@ -7590,7 +7579,7 @@
       <c r="I17" s="1"/>
       <c r="J17" s="77"/>
     </row>
-    <row r="18" spans="1:10" s="132" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" s="132" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="71" t="s">
         <v>696</v>
       </c>
@@ -7604,7 +7593,7 @@
       <c r="I18" s="166"/>
       <c r="J18" s="174"/>
     </row>
-    <row r="19" spans="1:10" s="3" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" s="3" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>11</v>
       </c>
@@ -7620,7 +7609,7 @@
       <c r="I19" s="1"/>
       <c r="J19" s="169"/>
     </row>
-    <row r="20" spans="1:10" s="3" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" s="3" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>12</v>
       </c>
@@ -7636,7 +7625,7 @@
       <c r="I20" s="1"/>
       <c r="J20" s="169"/>
     </row>
-    <row r="21" spans="1:10" s="3" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" s="3" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>13</v>
       </c>
@@ -7652,7 +7641,7 @@
       <c r="I21" s="1"/>
       <c r="J21" s="98"/>
     </row>
-    <row r="22" spans="1:10" s="3" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" s="3" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>14</v>
       </c>
@@ -7667,7 +7656,7 @@
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
     </row>
-    <row r="23" spans="1:10" s="3" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" s="3" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>15</v>
       </c>
@@ -7683,7 +7672,7 @@
       <c r="I23" s="1"/>
       <c r="J23" s="175"/>
     </row>
-    <row r="24" spans="1:10" s="3" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" s="3" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>16</v>
       </c>
@@ -7699,7 +7688,7 @@
       <c r="I24" s="1"/>
       <c r="J24" s="175"/>
     </row>
-    <row r="25" spans="1:10" s="258" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" s="258" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>17</v>
       </c>
@@ -7715,7 +7704,7 @@
       <c r="I25" s="1"/>
       <c r="J25" s="56"/>
     </row>
-    <row r="26" spans="1:10" s="3" customFormat="1" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>18</v>
       </c>
@@ -7755,7 +7744,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="28" spans="1:10" s="3" customFormat="1" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>20</v>
       </c>
@@ -7771,7 +7760,7 @@
       <c r="I28" s="1"/>
       <c r="J28" s="52"/>
     </row>
-    <row r="29" spans="1:10" s="257" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" s="257" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>21</v>
       </c>
@@ -7787,7 +7776,7 @@
       <c r="I29" s="1"/>
       <c r="J29" s="267"/>
     </row>
-    <row r="30" spans="1:10" s="95" customFormat="1" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" s="95" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>22</v>
       </c>
@@ -7803,7 +7792,7 @@
       <c r="I30" s="1"/>
       <c r="J30" s="96"/>
     </row>
-    <row r="31" spans="1:10" s="95" customFormat="1" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" s="95" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>23</v>
       </c>
@@ -7843,7 +7832,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="33" spans="1:10" s="95" customFormat="1" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" s="95" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>25</v>
       </c>
@@ -7859,7 +7848,7 @@
       <c r="I33" s="1"/>
       <c r="J33" s="96"/>
     </row>
-    <row r="34" spans="1:10" s="95" customFormat="1" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" s="95" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>26</v>
       </c>
@@ -7875,7 +7864,7 @@
       <c r="I34" s="1"/>
       <c r="J34" s="96"/>
     </row>
-    <row r="35" spans="1:10" s="95" customFormat="1" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" s="95" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>27</v>
       </c>
@@ -7891,7 +7880,7 @@
       <c r="I35" s="1"/>
       <c r="J35" s="96"/>
     </row>
-    <row r="36" spans="1:10" s="3" customFormat="1" ht="36.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" s="3" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>28</v>
       </c>
@@ -7907,7 +7896,7 @@
       <c r="I36" s="1"/>
       <c r="J36" s="176"/>
     </row>
-    <row r="37" spans="1:10" s="3" customFormat="1" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" s="3" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>29</v>
       </c>
@@ -7923,7 +7912,7 @@
       <c r="I37" s="1"/>
       <c r="J37" s="55"/>
     </row>
-    <row r="38" spans="1:10" s="3" customFormat="1" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" s="3" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>30</v>
       </c>
@@ -7939,7 +7928,7 @@
       <c r="I38" s="1"/>
       <c r="J38" s="237"/>
     </row>
-    <row r="39" spans="1:10" s="132" customFormat="1" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" s="132" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>31</v>
       </c>
@@ -7955,7 +7944,7 @@
       <c r="I39" s="1"/>
       <c r="J39" s="177"/>
     </row>
-    <row r="40" spans="1:10" s="259" customFormat="1" ht="41.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" s="259" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>32</v>
       </c>
@@ -7971,7 +7960,7 @@
       <c r="I40" s="1"/>
       <c r="J40" s="269"/>
     </row>
-    <row r="41" spans="1:10" s="132" customFormat="1" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" s="132" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>33</v>
       </c>
@@ -8009,7 +7998,7 @@
       </c>
       <c r="J42" s="96"/>
     </row>
-    <row r="43" spans="1:10" s="95" customFormat="1" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" s="95" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>35</v>
       </c>
@@ -8025,7 +8014,7 @@
       <c r="I43" s="1"/>
       <c r="J43" s="96"/>
     </row>
-    <row r="44" spans="1:10" s="95" customFormat="1" ht="41.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" s="95" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>36</v>
       </c>
@@ -8041,7 +8030,7 @@
       <c r="I44" s="1"/>
       <c r="J44" s="96"/>
     </row>
-    <row r="45" spans="1:10" s="95" customFormat="1" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" s="95" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>37</v>
       </c>
@@ -8057,7 +8046,7 @@
       <c r="I45" s="1"/>
       <c r="J45" s="96"/>
     </row>
-    <row r="46" spans="1:10" s="95" customFormat="1" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" s="95" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>38</v>
       </c>
@@ -8073,7 +8062,7 @@
       <c r="I46" s="1"/>
       <c r="J46" s="96"/>
     </row>
-    <row r="47" spans="1:10" s="95" customFormat="1" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" s="95" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>39</v>
       </c>
@@ -8089,7 +8078,7 @@
       <c r="I47" s="1"/>
       <c r="J47" s="96"/>
     </row>
-    <row r="48" spans="1:10" s="132" customFormat="1" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" s="132" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>40</v>
       </c>
@@ -8105,7 +8094,7 @@
       <c r="I48" s="1"/>
       <c r="J48" s="77"/>
     </row>
-    <row r="49" spans="1:10" s="3" customFormat="1" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" s="3" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>41</v>
       </c>
@@ -8193,7 +8182,7 @@
       </c>
       <c r="J52" s="306"/>
     </row>
-    <row r="53" spans="1:10" s="3" customFormat="1" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" s="3" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>45</v>
       </c>
@@ -8209,7 +8198,7 @@
       <c r="I53" s="1"/>
       <c r="J53" s="175"/>
     </row>
-    <row r="54" spans="1:10" s="3" customFormat="1" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" s="3" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>46</v>
       </c>
@@ -8225,7 +8214,7 @@
       <c r="I54" s="1"/>
       <c r="J54" s="65"/>
     </row>
-    <row r="55" spans="1:10" s="3" customFormat="1" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" s="3" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>47</v>
       </c>
@@ -8241,7 +8230,7 @@
       <c r="I55" s="1"/>
       <c r="J55" s="65"/>
     </row>
-    <row r="56" spans="1:10" s="258" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" s="258" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>48</v>
       </c>
@@ -8257,7 +8246,7 @@
       <c r="I56" s="1"/>
       <c r="J56" s="267"/>
     </row>
-    <row r="57" spans="1:10" s="258" customFormat="1" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" s="258" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>49</v>
       </c>
@@ -8273,7 +8262,7 @@
       <c r="I57" s="1"/>
       <c r="J57" s="55"/>
     </row>
-    <row r="58" spans="1:10" s="3" customFormat="1" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" s="3" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>50</v>
       </c>
@@ -8289,7 +8278,7 @@
       <c r="I58" s="1"/>
       <c r="J58" s="172"/>
     </row>
-    <row r="59" spans="1:10" s="295" customFormat="1" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" s="295" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="285">
         <v>51</v>
       </c>
@@ -8305,7 +8294,7 @@
       <c r="I59" s="285"/>
       <c r="J59" s="294"/>
     </row>
-    <row r="60" spans="1:10" s="295" customFormat="1" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" s="295" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="285">
         <v>52</v>
       </c>
@@ -8321,7 +8310,7 @@
       <c r="I60" s="285"/>
       <c r="J60" s="294"/>
     </row>
-    <row r="61" spans="1:10" s="295" customFormat="1" ht="16.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" s="295" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A61" s="285">
         <v>53</v>
       </c>
@@ -8337,7 +8326,7 @@
       <c r="I61" s="285"/>
       <c r="J61" s="296"/>
     </row>
-    <row r="62" spans="1:10" s="289" customFormat="1" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" s="289" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="285">
         <v>54</v>
       </c>
@@ -8353,7 +8342,7 @@
       <c r="I62" s="285"/>
       <c r="J62" s="288"/>
     </row>
-    <row r="63" spans="1:10" s="29" customFormat="1" ht="30.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" s="29" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="71" t="s">
         <v>727</v>
       </c>
@@ -8367,7 +8356,7 @@
       <c r="I63" s="166"/>
       <c r="J63" s="174"/>
     </row>
-    <row r="64" spans="1:10" s="253" customFormat="1" ht="30.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" s="253" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="59">
         <v>55</v>
       </c>
@@ -8383,7 +8372,7 @@
       <c r="I64" s="1"/>
       <c r="J64" s="262"/>
     </row>
-    <row r="65" spans="1:10" s="253" customFormat="1" ht="30.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" s="253" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>56</v>
       </c>
@@ -8421,7 +8410,7 @@
       </c>
       <c r="J66" s="65"/>
     </row>
-    <row r="67" spans="1:10" s="253" customFormat="1" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" s="253" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>58</v>
       </c>
@@ -8437,7 +8426,7 @@
       <c r="I67" s="1"/>
       <c r="J67" s="255"/>
     </row>
-    <row r="68" spans="1:10" s="253" customFormat="1" ht="30.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" s="253" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="59">
         <v>59</v>
       </c>
@@ -8453,7 +8442,7 @@
       <c r="I68" s="1"/>
       <c r="J68" s="263"/>
     </row>
-    <row r="69" spans="1:10" s="3" customFormat="1" ht="30.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" s="3" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>60</v>
       </c>
@@ -8469,7 +8458,7 @@
       <c r="I69" s="1"/>
       <c r="J69" s="220"/>
     </row>
-    <row r="70" spans="1:10" s="132" customFormat="1" ht="30.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" s="132" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="59">
         <v>61</v>
       </c>
@@ -8485,7 +8474,7 @@
       <c r="I70" s="1"/>
       <c r="J70" s="177"/>
     </row>
-    <row r="71" spans="1:10" s="3" customFormat="1" ht="30.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" s="3" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="71" t="s">
         <v>730</v>
       </c>
@@ -8549,7 +8538,7 @@
       </c>
       <c r="J73" s="56"/>
     </row>
-    <row r="74" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>64</v>
       </c>
@@ -8565,11 +8554,11 @@
       <c r="I74" s="1"/>
       <c r="J74" s="284"/>
     </row>
-    <row r="75" spans="1:10" s="3" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="383" t="s">
+    <row r="75" spans="1:10" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A75" s="370" t="s">
         <v>926</v>
       </c>
-      <c r="B75" s="384"/>
+      <c r="B75" s="371"/>
       <c r="C75" s="215"/>
       <c r="D75" s="246"/>
       <c r="E75" s="246"/>
@@ -8579,7 +8568,7 @@
       <c r="I75" s="246"/>
       <c r="J75" s="193"/>
     </row>
-    <row r="76" spans="1:10" s="258" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" s="258" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>65</v>
       </c>
@@ -8617,7 +8606,7 @@
       </c>
       <c r="J77" s="61"/>
     </row>
-    <row r="78" spans="1:10" s="132" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" s="132" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="71" t="s">
         <v>731</v>
       </c>
@@ -8653,7 +8642,7 @@
       </c>
       <c r="J79" s="268"/>
     </row>
-    <row r="80" spans="1:10" s="258" customFormat="1" ht="48.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" s="258" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="59">
         <v>68</v>
       </c>
@@ -8691,7 +8680,7 @@
       </c>
       <c r="J81" s="256"/>
     </row>
-    <row r="82" spans="1:10" s="3" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" s="3" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="59">
         <v>70</v>
       </c>
@@ -8707,7 +8696,7 @@
       <c r="I82" s="1"/>
       <c r="J82" s="66"/>
     </row>
-    <row r="83" spans="1:10" s="3" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" s="3" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>71</v>
       </c>
@@ -8743,7 +8732,7 @@
       </c>
       <c r="J84" s="235"/>
     </row>
-    <row r="85" spans="1:10" s="3" customFormat="1" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" s="3" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>73</v>
       </c>
@@ -8759,7 +8748,7 @@
       <c r="I85" s="1"/>
       <c r="J85" s="172"/>
     </row>
-    <row r="86" spans="1:10" s="3" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" s="3" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="59">
         <v>74</v>
       </c>
@@ -8775,7 +8764,7 @@
       <c r="I86" s="1"/>
       <c r="J86" s="172"/>
     </row>
-    <row r="87" spans="1:10" s="132" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" s="132" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>75</v>
       </c>
@@ -8791,7 +8780,7 @@
       <c r="I87" s="1"/>
       <c r="J87" s="177"/>
     </row>
-    <row r="88" spans="1:10" s="132" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" s="132" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="59">
         <v>76</v>
       </c>
@@ -8807,7 +8796,7 @@
       <c r="I88" s="1"/>
       <c r="J88" s="177"/>
     </row>
-    <row r="89" spans="1:10" s="253" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" s="253" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>77</v>
       </c>
@@ -8843,7 +8832,7 @@
       </c>
       <c r="J90" s="318"/>
     </row>
-    <row r="91" spans="1:10" s="3" customFormat="1" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" s="3" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>79</v>
       </c>
@@ -8859,7 +8848,7 @@
       <c r="I91" s="1"/>
       <c r="J91" s="179"/>
     </row>
-    <row r="92" spans="1:10" s="3" customFormat="1" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" s="3" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="59">
         <v>80</v>
       </c>
@@ -8875,7 +8864,7 @@
       <c r="I92" s="1"/>
       <c r="J92" s="97"/>
     </row>
-    <row r="93" spans="1:10" s="253" customFormat="1" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" s="253" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>81</v>
       </c>
@@ -8891,7 +8880,7 @@
       <c r="I93" s="1"/>
       <c r="J93" s="256"/>
     </row>
-    <row r="94" spans="1:10" s="3" customFormat="1" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" s="3" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="59">
         <v>82</v>
       </c>
@@ -8907,7 +8896,7 @@
       <c r="I94" s="1"/>
       <c r="J94" s="267"/>
     </row>
-    <row r="95" spans="1:10" s="3" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>83</v>
       </c>
@@ -8923,7 +8912,7 @@
       <c r="I95" s="1"/>
       <c r="J95" s="96"/>
     </row>
-    <row r="96" spans="1:10" s="3" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="59">
         <v>84</v>
       </c>
@@ -8939,7 +8928,7 @@
       <c r="I96" s="1"/>
       <c r="J96" s="96"/>
     </row>
-    <row r="97" spans="1:38" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:38" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="163" t="s">
         <v>740</v>
       </c>
@@ -8950,7 +8939,7 @@
       <c r="G97" s="180"/>
       <c r="J97" s="181"/>
     </row>
-    <row r="98" spans="1:38" s="71" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:38" s="71" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>85</v>
       </c>
@@ -8994,7 +8983,7 @@
       <c r="AK98" s="57"/>
       <c r="AL98" s="57"/>
     </row>
-    <row r="99" spans="1:38" s="258" customFormat="1" ht="55.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:38" s="258" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>86</v>
       </c>
@@ -9010,7 +8999,7 @@
       <c r="I99" s="1"/>
       <c r="J99" s="56"/>
     </row>
-    <row r="100" spans="1:38" s="3" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:38" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A100" s="71" t="s">
         <v>741</v>
       </c>
@@ -9024,7 +9013,7 @@
       <c r="I100" s="1"/>
       <c r="J100" s="174"/>
     </row>
-    <row r="101" spans="1:38" s="3" customFormat="1" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:38" s="3" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>87</v>
       </c>
@@ -9040,7 +9029,7 @@
       <c r="I101" s="1"/>
       <c r="J101" s="183"/>
     </row>
-    <row r="102" spans="1:38" s="3" customFormat="1" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:38" s="3" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>88</v>
       </c>
@@ -9056,7 +9045,7 @@
       <c r="I102" s="1"/>
       <c r="J102" s="183"/>
     </row>
-    <row r="103" spans="1:38" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:38" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>89</v>
       </c>
@@ -9072,7 +9061,7 @@
       <c r="I103" s="1"/>
       <c r="J103" s="283"/>
     </row>
-    <row r="104" spans="1:38" s="3" customFormat="1" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:38" s="3" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>90</v>
       </c>
@@ -9088,7 +9077,7 @@
       <c r="I104" s="1"/>
       <c r="J104" s="183"/>
     </row>
-    <row r="105" spans="1:38" s="3" customFormat="1" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:38" s="3" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>91</v>
       </c>
@@ -9104,7 +9093,7 @@
       <c r="I105" s="1"/>
       <c r="J105" s="183"/>
     </row>
-    <row r="106" spans="1:38" s="3" customFormat="1" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:38" s="3" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>92</v>
       </c>
@@ -9120,7 +9109,7 @@
       <c r="I106" s="1"/>
       <c r="J106" s="65"/>
     </row>
-    <row r="107" spans="1:38" s="258" customFormat="1" ht="39.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:38" s="258" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>93</v>
       </c>
@@ -9136,7 +9125,7 @@
       <c r="I107" s="1"/>
       <c r="J107" s="65"/>
     </row>
-    <row r="108" spans="1:38" s="3" customFormat="1" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:38" s="3" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>94</v>
       </c>
@@ -9152,7 +9141,7 @@
       <c r="I108" s="1"/>
       <c r="J108" s="56"/>
     </row>
-    <row r="109" spans="1:38" s="3" customFormat="1" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:38" s="3" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>95</v>
       </c>
@@ -9168,7 +9157,7 @@
       <c r="I109" s="1"/>
       <c r="J109" s="65"/>
     </row>
-    <row r="110" spans="1:38" s="3" customFormat="1" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:38" s="3" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>96</v>
       </c>
@@ -9184,7 +9173,7 @@
       <c r="I110" s="1"/>
       <c r="J110" s="97"/>
     </row>
-    <row r="111" spans="1:38" s="3" customFormat="1" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:38" s="3" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>97</v>
       </c>
@@ -9200,7 +9189,7 @@
       <c r="I111" s="1"/>
       <c r="J111" s="96"/>
     </row>
-    <row r="112" spans="1:38" s="3" customFormat="1" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:38" s="3" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>98</v>
       </c>
@@ -9216,7 +9205,7 @@
       <c r="I112" s="1"/>
       <c r="J112" s="179"/>
     </row>
-    <row r="113" spans="1:13" s="29" customFormat="1" ht="16.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" s="29" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>99</v>
       </c>
@@ -9232,7 +9221,7 @@
       <c r="I113" s="1"/>
       <c r="J113" s="290"/>
     </row>
-    <row r="114" spans="1:13" s="29" customFormat="1" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" s="29" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>100</v>
       </c>
@@ -9248,7 +9237,7 @@
       <c r="I114" s="1"/>
       <c r="J114" s="245"/>
     </row>
-    <row r="115" spans="1:13" s="29" customFormat="1" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" s="29" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>101</v>
       </c>
@@ -9264,7 +9253,7 @@
       <c r="I115" s="1"/>
       <c r="J115" s="178"/>
     </row>
-    <row r="116" spans="1:13" s="3" customFormat="1" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" s="3" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>102</v>
       </c>
@@ -9280,7 +9269,7 @@
       <c r="I116" s="1"/>
       <c r="J116" s="96"/>
     </row>
-    <row r="117" spans="1:13" s="3" customFormat="1" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" s="3" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>103</v>
       </c>
@@ -9296,7 +9285,7 @@
       <c r="I117" s="1"/>
       <c r="J117" s="172"/>
     </row>
-    <row r="118" spans="1:13" s="3" customFormat="1" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13" s="3" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>104</v>
       </c>
@@ -9312,7 +9301,7 @@
       <c r="I118" s="1"/>
       <c r="J118" s="96"/>
     </row>
-    <row r="119" spans="1:13" s="3" customFormat="1" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13" s="3" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>105</v>
       </c>
@@ -9328,7 +9317,7 @@
       <c r="I119" s="1"/>
       <c r="J119" s="172"/>
     </row>
-    <row r="120" spans="1:13" s="3" customFormat="1" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:13" s="3" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>106</v>
       </c>
@@ -9344,7 +9333,7 @@
       <c r="I120" s="1"/>
       <c r="J120" s="96"/>
     </row>
-    <row r="121" spans="1:13" s="260" customFormat="1" ht="24.9" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:13" s="260" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>107</v>
       </c>
@@ -9361,7 +9350,7 @@
       <c r="J121" s="184"/>
       <c r="M121" s="261"/>
     </row>
-    <row r="122" spans="1:13" s="12" customFormat="1" ht="24.9" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:13" s="12" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="52">
         <v>108</v>
       </c>
@@ -9378,7 +9367,7 @@
       <c r="J122" s="184"/>
       <c r="M122" s="14"/>
     </row>
-    <row r="123" spans="1:13" s="12" customFormat="1" ht="24.9" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:13" s="12" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="52">
         <v>109</v>
       </c>
@@ -9395,7 +9384,7 @@
       <c r="J123" s="184"/>
       <c r="M123" s="14"/>
     </row>
-    <row r="124" spans="1:13" s="12" customFormat="1" ht="24.9" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:13" s="12" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="52">
         <v>110</v>
       </c>
@@ -9412,7 +9401,7 @@
       <c r="J124" s="184"/>
       <c r="M124" s="14"/>
     </row>
-    <row r="125" spans="1:13" s="12" customFormat="1" ht="24.9" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:13" s="12" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="52">
         <v>111</v>
       </c>
@@ -9429,7 +9418,7 @@
       <c r="J125" s="184"/>
       <c r="M125" s="14"/>
     </row>
-    <row r="126" spans="1:13" s="12" customFormat="1" ht="24.9" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:13" s="12" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="52">
         <v>112</v>
       </c>
@@ -9446,7 +9435,7 @@
       <c r="J126" s="184"/>
       <c r="M126" s="14"/>
     </row>
-    <row r="127" spans="1:13" s="12" customFormat="1" ht="24.9" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:13" s="12" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="52">
         <v>113</v>
       </c>
@@ -9463,7 +9452,7 @@
       <c r="J127" s="184"/>
       <c r="M127" s="14"/>
     </row>
-    <row r="128" spans="1:13" s="12" customFormat="1" ht="24.9" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:13" s="12" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="52">
         <v>114</v>
       </c>
@@ -9480,7 +9469,7 @@
       <c r="J128" s="184"/>
       <c r="M128" s="14"/>
     </row>
-    <row r="129" spans="1:13" s="12" customFormat="1" ht="24.9" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:13" s="12" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="52">
         <v>115</v>
       </c>
@@ -9497,7 +9486,7 @@
       <c r="J129" s="184"/>
       <c r="M129" s="14"/>
     </row>
-    <row r="130" spans="1:13" s="12" customFormat="1" ht="24.9" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:13" s="12" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="52">
         <v>116</v>
       </c>
@@ -9514,7 +9503,7 @@
       <c r="J130" s="184"/>
       <c r="M130" s="14"/>
     </row>
-    <row r="131" spans="1:13" s="12" customFormat="1" ht="24.9" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:13" s="12" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="52">
         <v>117</v>
       </c>
@@ -9531,7 +9520,7 @@
       <c r="J131" s="184"/>
       <c r="M131" s="14"/>
     </row>
-    <row r="132" spans="1:13" s="12" customFormat="1" ht="24.9" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13" s="12" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="52">
         <v>118</v>
       </c>
@@ -9548,7 +9537,7 @@
       <c r="J132" s="184"/>
       <c r="M132" s="14"/>
     </row>
-    <row r="133" spans="1:13" s="12" customFormat="1" ht="24.9" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13" s="12" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="52">
         <v>119</v>
       </c>
@@ -9565,7 +9554,7 @@
       <c r="J133" s="184"/>
       <c r="M133" s="14"/>
     </row>
-    <row r="134" spans="1:13" s="12" customFormat="1" ht="24.9" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13" s="12" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="52">
         <v>120</v>
       </c>
@@ -9582,7 +9571,7 @@
       <c r="J134" s="184"/>
       <c r="M134" s="14"/>
     </row>
-    <row r="135" spans="1:13" s="12" customFormat="1" ht="24.9" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:13" s="12" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="52">
         <v>121</v>
       </c>
@@ -9599,7 +9588,7 @@
       <c r="J135" s="184"/>
       <c r="M135" s="14"/>
     </row>
-    <row r="136" spans="1:13" s="12" customFormat="1" ht="24.9" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:13" s="12" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="52">
         <v>122</v>
       </c>
@@ -9616,7 +9605,7 @@
       <c r="J136" s="184"/>
       <c r="M136" s="14"/>
     </row>
-    <row r="137" spans="1:13" s="12" customFormat="1" ht="24.9" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:13" s="12" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="52">
         <v>123</v>
       </c>
@@ -9633,7 +9622,7 @@
       <c r="J137" s="184"/>
       <c r="M137" s="14"/>
     </row>
-    <row r="138" spans="1:13" s="12" customFormat="1" ht="24.9" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:13" s="12" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="52">
         <v>124</v>
       </c>
@@ -9650,7 +9639,7 @@
       <c r="J138" s="184"/>
       <c r="M138" s="14"/>
     </row>
-    <row r="139" spans="1:13" s="12" customFormat="1" ht="42" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:13" s="12" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="52">
         <v>125</v>
       </c>
@@ -9668,10 +9657,10 @@
       <c r="M139" s="14"/>
     </row>
     <row r="140" spans="1:13" s="95" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="377" t="s">
+      <c r="A140" s="364" t="s">
         <v>289</v>
       </c>
-      <c r="B140" s="377"/>
+      <c r="B140" s="364"/>
       <c r="C140" s="189">
         <f>SUM(C8:C139)</f>
         <v>142</v>
@@ -9703,13 +9692,6 @@
       <c r="J140" s="110"/>
     </row>
   </sheetData>
-  <autoFilter ref="A6:J140" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <filterColumn colId="3">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
   <mergeCells count="6">
     <mergeCell ref="A140:B140"/>
     <mergeCell ref="A3:J3"/>
@@ -9739,7 +9721,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor rgb="FF147216"/>
   </sheetPr>
   <dimension ref="A1:M236"/>
@@ -9775,18 +9757,18 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="386" t="s">
+      <c r="A2" s="373" t="s">
         <v>911</v>
       </c>
-      <c r="B2" s="386"/>
-      <c r="C2" s="386"/>
-      <c r="D2" s="386"/>
-      <c r="E2" s="386"/>
-      <c r="F2" s="386"/>
-      <c r="G2" s="386"/>
-      <c r="H2" s="386"/>
-      <c r="I2" s="386"/>
-      <c r="J2" s="386"/>
+      <c r="B2" s="373"/>
+      <c r="C2" s="373"/>
+      <c r="D2" s="373"/>
+      <c r="E2" s="373"/>
+      <c r="F2" s="373"/>
+      <c r="G2" s="373"/>
+      <c r="H2" s="373"/>
+      <c r="I2" s="373"/>
+      <c r="J2" s="373"/>
     </row>
     <row r="3" spans="1:13" s="6" customFormat="1" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A3" s="79" t="s">
@@ -9799,9 +9781,9 @@
         <v>19</v>
       </c>
       <c r="D3" s="106"/>
-      <c r="E3" s="387"/>
-      <c r="F3" s="387"/>
-      <c r="G3" s="387"/>
+      <c r="E3" s="374"/>
+      <c r="F3" s="374"/>
+      <c r="G3" s="374"/>
       <c r="H3" s="79" t="s">
         <v>20</v>
       </c>
@@ -9872,21 +9854,21 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="383" t="s">
+    <row r="6" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="370" t="s">
         <v>747</v>
       </c>
-      <c r="B6" s="384"/>
-      <c r="C6" s="384"/>
-      <c r="D6" s="384"/>
-      <c r="E6" s="384"/>
-      <c r="F6" s="384"/>
-      <c r="G6" s="384"/>
-      <c r="H6" s="384"/>
-      <c r="I6" s="384"/>
-      <c r="J6" s="388"/>
-    </row>
-    <row r="7" spans="1:13" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="371"/>
+      <c r="C6" s="371"/>
+      <c r="D6" s="371"/>
+      <c r="E6" s="371"/>
+      <c r="F6" s="371"/>
+      <c r="G6" s="371"/>
+      <c r="H6" s="371"/>
+      <c r="I6" s="371"/>
+      <c r="J6" s="375"/>
+    </row>
+    <row r="7" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="247" t="s">
         <v>748</v>
       </c>
@@ -9900,7 +9882,7 @@
       <c r="I7" s="246"/>
       <c r="J7" s="193"/>
     </row>
-    <row r="8" spans="1:13" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="59">
         <v>1</v>
       </c>
@@ -9916,7 +9898,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="96"/>
     </row>
-    <row r="9" spans="1:13" s="264" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" s="264" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -9932,7 +9914,7 @@
       <c r="I9" s="1"/>
       <c r="J9" s="96"/>
     </row>
-    <row r="10" spans="1:13" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="59">
         <v>3</v>
       </c>
@@ -9948,7 +9930,7 @@
       <c r="I10" s="1"/>
       <c r="J10" s="96"/>
     </row>
-    <row r="11" spans="1:13" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>4</v>
       </c>
@@ -9964,7 +9946,7 @@
       <c r="I11" s="1"/>
       <c r="J11" s="65"/>
     </row>
-    <row r="12" spans="1:13" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>5</v>
       </c>
@@ -9980,7 +9962,7 @@
       <c r="I12" s="1"/>
       <c r="J12" s="52"/>
     </row>
-    <row r="13" spans="1:13" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="71" t="s">
         <v>333</v>
       </c>
@@ -9994,7 +9976,7 @@
       <c r="I13" s="166"/>
       <c r="J13" s="174"/>
     </row>
-    <row r="14" spans="1:13" s="264" customFormat="1" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" s="264" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="59">
         <v>6</v>
       </c>
@@ -10010,7 +9992,7 @@
       <c r="I14" s="1"/>
       <c r="J14" s="262"/>
     </row>
-    <row r="15" spans="1:13" s="264" customFormat="1" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" s="264" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="59">
         <v>7</v>
       </c>
@@ -10026,7 +10008,7 @@
       <c r="I15" s="1"/>
       <c r="J15" s="263"/>
     </row>
-    <row r="16" spans="1:13" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="71" t="s">
         <v>332</v>
       </c>
@@ -10040,7 +10022,7 @@
       <c r="I16" s="166"/>
       <c r="J16" s="174"/>
     </row>
-    <row r="17" spans="1:10" s="265" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" s="265" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>8</v>
       </c>
@@ -10078,7 +10060,7 @@
       </c>
       <c r="J18" s="313"/>
     </row>
-    <row r="19" spans="1:10" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>10</v>
       </c>
@@ -10094,7 +10076,7 @@
       <c r="I19" s="1"/>
       <c r="J19" s="52"/>
     </row>
-    <row r="20" spans="1:10" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>11</v>
       </c>
@@ -10110,7 +10092,7 @@
       <c r="I20" s="1"/>
       <c r="J20" s="65"/>
     </row>
-    <row r="21" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>12</v>
       </c>
@@ -10126,7 +10108,7 @@
       <c r="I21" s="1"/>
       <c r="J21" s="75"/>
     </row>
-    <row r="22" spans="1:10" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>13</v>
       </c>
@@ -10142,7 +10124,7 @@
       <c r="I22" s="1"/>
       <c r="J22" s="75"/>
     </row>
-    <row r="23" spans="1:10" s="266" customFormat="1" ht="37.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" s="266" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>14</v>
       </c>
@@ -10158,7 +10140,7 @@
       <c r="I23" s="1"/>
       <c r="J23" s="267"/>
     </row>
-    <row r="24" spans="1:10" s="132" customFormat="1" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" s="132" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>15</v>
       </c>
@@ -10174,7 +10156,7 @@
       <c r="I24" s="1"/>
       <c r="J24" s="65"/>
     </row>
-    <row r="25" spans="1:10" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>16</v>
       </c>
@@ -10190,7 +10172,7 @@
       <c r="I25" s="1"/>
       <c r="J25" s="186"/>
     </row>
-    <row r="26" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="71" t="s">
         <v>763</v>
       </c>
@@ -10204,7 +10186,7 @@
       <c r="I26" s="166"/>
       <c r="J26" s="174"/>
     </row>
-    <row r="27" spans="1:10" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="59">
         <v>17</v>
       </c>
@@ -10220,7 +10202,7 @@
       <c r="I27" s="1"/>
       <c r="J27" s="61"/>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>18</v>
       </c>
@@ -10236,7 +10218,7 @@
       <c r="I28" s="1"/>
       <c r="J28" s="262"/>
     </row>
-    <row r="29" spans="1:10" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>19</v>
       </c>
@@ -10252,7 +10234,7 @@
       <c r="I29" s="1"/>
       <c r="J29" s="269"/>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>20</v>
       </c>
@@ -10268,7 +10250,7 @@
       <c r="I30" s="1"/>
       <c r="J30" s="197"/>
     </row>
-    <row r="31" spans="1:10" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>21</v>
       </c>
@@ -10284,7 +10266,7 @@
       <c r="I31" s="1"/>
       <c r="J31" s="55"/>
     </row>
-    <row r="32" spans="1:10" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>22</v>
       </c>
@@ -10322,7 +10304,7 @@
       </c>
       <c r="J33" s="269"/>
     </row>
-    <row r="34" spans="1:10" s="266" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" s="266" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>24</v>
       </c>
@@ -10338,7 +10320,7 @@
       <c r="I34" s="1"/>
       <c r="J34" s="65"/>
     </row>
-    <row r="35" spans="1:10" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>25</v>
       </c>
@@ -10354,7 +10336,7 @@
       <c r="I35" s="1"/>
       <c r="J35" s="76"/>
     </row>
-    <row r="36" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="71" t="s">
         <v>334</v>
       </c>
@@ -10368,7 +10350,7 @@
       <c r="I36" s="166"/>
       <c r="J36" s="174"/>
     </row>
-    <row r="37" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="59">
         <v>26</v>
       </c>
@@ -10384,7 +10366,7 @@
       <c r="I37" s="1"/>
       <c r="J37" s="65"/>
     </row>
-    <row r="38" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="59">
         <v>27</v>
       </c>
@@ -10400,7 +10382,7 @@
       <c r="I38" s="1"/>
       <c r="J38" s="75"/>
     </row>
-    <row r="39" spans="1:10" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>28</v>
       </c>
@@ -10416,7 +10398,7 @@
       <c r="I39" s="1"/>
       <c r="J39" s="52"/>
     </row>
-    <row r="40" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A40" s="71" t="s">
         <v>775</v>
       </c>
@@ -10430,7 +10412,7 @@
       <c r="I40" s="166"/>
       <c r="J40" s="174"/>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>29</v>
       </c>
@@ -10446,7 +10428,7 @@
       <c r="I41" s="1"/>
       <c r="J41" s="52"/>
     </row>
-    <row r="42" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>30</v>
       </c>
@@ -10462,7 +10444,7 @@
       <c r="I42" s="1"/>
       <c r="J42" s="75"/>
     </row>
-    <row r="43" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>31</v>
       </c>
@@ -10478,7 +10460,7 @@
       <c r="I43" s="1"/>
       <c r="J43" s="75"/>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>32</v>
       </c>
@@ -10494,7 +10476,7 @@
       <c r="I44" s="1"/>
       <c r="J44" s="76"/>
     </row>
-    <row r="45" spans="1:10" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>33</v>
       </c>
@@ -10510,7 +10492,7 @@
       <c r="I45" s="1"/>
       <c r="J45" s="56"/>
     </row>
-    <row r="46" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>34</v>
       </c>
@@ -10526,7 +10508,7 @@
       <c r="I46" s="1"/>
       <c r="J46" s="75"/>
     </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="59">
         <v>35</v>
       </c>
@@ -10542,7 +10524,7 @@
       <c r="I47" s="1"/>
       <c r="J47" s="52"/>
     </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>36</v>
       </c>
@@ -10558,7 +10540,7 @@
       <c r="I48" s="1"/>
       <c r="J48" s="52"/>
     </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="59">
         <v>37</v>
       </c>
@@ -10574,7 +10556,7 @@
       <c r="I49" s="1"/>
       <c r="J49" s="52"/>
     </row>
-    <row r="50" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>38</v>
       </c>
@@ -10590,7 +10572,7 @@
       <c r="I50" s="1"/>
       <c r="J50" s="75"/>
     </row>
-    <row r="51" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A51" s="166" t="s">
         <v>785</v>
       </c>
@@ -10604,7 +10586,7 @@
       <c r="I51" s="166"/>
       <c r="J51" s="173"/>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>39</v>
       </c>
@@ -10620,7 +10602,7 @@
       <c r="I52" s="1"/>
       <c r="J52" s="65"/>
     </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>40</v>
       </c>
@@ -10636,7 +10618,7 @@
       <c r="I53" s="1"/>
       <c r="J53" s="52"/>
     </row>
-    <row r="54" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A54" s="166" t="s">
         <v>788</v>
       </c>
@@ -10650,7 +10632,7 @@
       <c r="I54" s="166"/>
       <c r="J54" s="173"/>
     </row>
-    <row r="55" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>41</v>
       </c>
@@ -10666,7 +10648,7 @@
       <c r="I55" s="1"/>
       <c r="J55" s="182"/>
     </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>42</v>
       </c>
@@ -10682,7 +10664,7 @@
       <c r="I56" s="1"/>
       <c r="J56" s="65"/>
     </row>
-    <row r="57" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>43</v>
       </c>
@@ -10698,7 +10680,7 @@
       <c r="I57" s="1"/>
       <c r="J57" s="75"/>
     </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>44</v>
       </c>
@@ -10714,7 +10696,7 @@
       <c r="I58" s="1"/>
       <c r="J58" s="55"/>
     </row>
-    <row r="59" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>45</v>
       </c>
@@ -10730,7 +10712,7 @@
       <c r="I59" s="1"/>
       <c r="J59" s="75"/>
     </row>
-    <row r="60" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>46</v>
       </c>
@@ -10746,7 +10728,7 @@
       <c r="I60" s="1"/>
       <c r="J60" s="75"/>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>47</v>
       </c>
@@ -10762,7 +10744,7 @@
       <c r="I61" s="1"/>
       <c r="J61" s="52"/>
     </row>
-    <row r="62" spans="1:10" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>48</v>
       </c>
@@ -10778,7 +10760,7 @@
       <c r="I62" s="1"/>
       <c r="J62" s="52"/>
     </row>
-    <row r="63" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>49</v>
       </c>
@@ -10794,7 +10776,7 @@
       <c r="I63" s="1"/>
       <c r="J63" s="75"/>
     </row>
-    <row r="64" spans="1:10" s="264" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" s="264" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>50</v>
       </c>
@@ -10810,7 +10792,7 @@
       <c r="I64" s="1"/>
       <c r="J64" s="263"/>
     </row>
-    <row r="65" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="71" t="s">
         <v>796</v>
       </c>
@@ -10824,7 +10806,7 @@
       <c r="I65" s="166"/>
       <c r="J65" s="174"/>
     </row>
-    <row r="66" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="71" t="s">
         <v>797</v>
       </c>
@@ -10838,7 +10820,7 @@
       <c r="I66" s="166"/>
       <c r="J66" s="174"/>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>51</v>
       </c>
@@ -10854,7 +10836,7 @@
       <c r="I67" s="1"/>
       <c r="J67" s="65"/>
     </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>52</v>
       </c>
@@ -10870,7 +10852,7 @@
       <c r="I68" s="1"/>
       <c r="J68" s="65"/>
     </row>
-    <row r="69" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A69" s="71" t="s">
         <v>800</v>
       </c>
@@ -10884,7 +10866,7 @@
       <c r="I69" s="166"/>
       <c r="J69" s="174"/>
     </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>53</v>
       </c>
@@ -10900,7 +10882,7 @@
       <c r="I70" s="1"/>
       <c r="J70" s="65"/>
     </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>54</v>
       </c>
@@ -10916,7 +10898,7 @@
       <c r="I71" s="1"/>
       <c r="J71" s="65"/>
     </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>55</v>
       </c>
@@ -10932,7 +10914,7 @@
       <c r="I72" s="1"/>
       <c r="J72" s="52"/>
     </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>56</v>
       </c>
@@ -10948,7 +10930,7 @@
       <c r="I73" s="1"/>
       <c r="J73" s="52"/>
     </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>57</v>
       </c>
@@ -10964,7 +10946,7 @@
       <c r="I74" s="1"/>
       <c r="J74" s="52"/>
     </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>58</v>
       </c>
@@ -10980,7 +10962,7 @@
       <c r="I75" s="1"/>
       <c r="J75" s="52"/>
     </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>59</v>
       </c>
@@ -10996,7 +10978,7 @@
       <c r="I76" s="1"/>
       <c r="J76" s="52"/>
     </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>60</v>
       </c>
@@ -11012,7 +10994,7 @@
       <c r="I77" s="1"/>
       <c r="J77" s="52"/>
     </row>
-    <row r="78" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A78" s="71" t="s">
         <v>809</v>
       </c>
@@ -11026,7 +11008,7 @@
       <c r="I78" s="166"/>
       <c r="J78" s="174"/>
     </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>61</v>
       </c>
@@ -11042,7 +11024,7 @@
       <c r="I79" s="1"/>
       <c r="J79" s="52"/>
     </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>62</v>
       </c>
@@ -11058,7 +11040,7 @@
       <c r="I80" s="1"/>
       <c r="J80" s="61"/>
     </row>
-    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>63</v>
       </c>
@@ -11074,7 +11056,7 @@
       <c r="I81" s="1"/>
       <c r="J81" s="52"/>
     </row>
-    <row r="82" spans="1:10" ht="30.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>64</v>
       </c>
@@ -11090,7 +11072,7 @@
       <c r="I82" s="1"/>
       <c r="J82" s="65"/>
     </row>
-    <row r="83" spans="1:10" s="264" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" s="264" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>65</v>
       </c>
@@ -11106,7 +11088,7 @@
       <c r="I83" s="1"/>
       <c r="J83" s="56"/>
     </row>
-    <row r="84" spans="1:10" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>66</v>
       </c>
@@ -11122,7 +11104,7 @@
       <c r="I84" s="1"/>
       <c r="J84" s="65"/>
     </row>
-    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>67</v>
       </c>
@@ -11138,7 +11120,7 @@
       <c r="I85" s="1"/>
       <c r="J85" s="52"/>
     </row>
-    <row r="86" spans="1:10" s="264" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" s="264" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>68</v>
       </c>
@@ -11154,7 +11136,7 @@
       <c r="I86" s="1"/>
       <c r="J86" s="262"/>
     </row>
-    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>69</v>
       </c>
@@ -11170,7 +11152,7 @@
       <c r="I87" s="1"/>
       <c r="J87" s="52"/>
     </row>
-    <row r="88" spans="1:10" s="264" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" s="264" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>70</v>
       </c>
@@ -11234,7 +11216,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>73</v>
       </c>
@@ -11250,7 +11232,7 @@
       <c r="I91" s="1"/>
       <c r="J91" s="52"/>
     </row>
-    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>74</v>
       </c>
@@ -11266,7 +11248,7 @@
       <c r="I92" s="1"/>
       <c r="J92" s="55"/>
     </row>
-    <row r="93" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>75</v>
       </c>
@@ -11282,7 +11264,7 @@
       <c r="I93" s="1"/>
       <c r="J93" s="52"/>
     </row>
-    <row r="94" spans="1:10" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>76</v>
       </c>
@@ -11298,7 +11280,7 @@
       <c r="I94" s="1"/>
       <c r="J94" s="55"/>
     </row>
-    <row r="95" spans="1:10" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>77</v>
       </c>
@@ -11336,7 +11318,7 @@
       </c>
       <c r="J96" s="56"/>
     </row>
-    <row r="97" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>79</v>
       </c>
@@ -11352,7 +11334,7 @@
       <c r="I97" s="1"/>
       <c r="J97" s="55"/>
     </row>
-    <row r="98" spans="1:10" s="264" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" s="264" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>80</v>
       </c>
@@ -11368,7 +11350,7 @@
       <c r="I98" s="1"/>
       <c r="J98" s="263"/>
     </row>
-    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>81</v>
       </c>
@@ -11384,7 +11366,7 @@
       <c r="I99" s="1"/>
       <c r="J99" s="52"/>
     </row>
-    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>82</v>
       </c>
@@ -11400,7 +11382,7 @@
       <c r="I100" s="1"/>
       <c r="J100" s="52"/>
     </row>
-    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>83</v>
       </c>
@@ -11440,7 +11422,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>85</v>
       </c>
@@ -11456,7 +11438,7 @@
       <c r="I103" s="1"/>
       <c r="J103" s="65"/>
     </row>
-    <row r="104" spans="1:10" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>86</v>
       </c>
@@ -11472,7 +11454,7 @@
       <c r="I104" s="1"/>
       <c r="J104" s="55"/>
     </row>
-    <row r="105" spans="1:10" s="264" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" s="264" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>87</v>
       </c>
@@ -11488,7 +11470,7 @@
       <c r="I105" s="1"/>
       <c r="J105" s="96"/>
     </row>
-    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>88</v>
       </c>
@@ -11504,7 +11486,7 @@
       <c r="I106" s="1"/>
       <c r="J106" s="52"/>
     </row>
-    <row r="107" spans="1:10" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>89</v>
       </c>
@@ -11520,7 +11502,7 @@
       <c r="I107" s="1"/>
       <c r="J107" s="55"/>
     </row>
-    <row r="108" spans="1:10" s="264" customFormat="1" ht="36.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" s="264" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>90</v>
       </c>
@@ -11536,7 +11518,7 @@
       <c r="I108" s="1"/>
       <c r="J108" s="61"/>
     </row>
-    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>91</v>
       </c>
@@ -11552,7 +11534,7 @@
       <c r="I109" s="1"/>
       <c r="J109" s="52"/>
     </row>
-    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>92</v>
       </c>
@@ -11568,7 +11550,7 @@
       <c r="I110" s="1"/>
       <c r="J110" s="52"/>
     </row>
-    <row r="111" spans="1:10" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>93</v>
       </c>
@@ -11584,7 +11566,7 @@
       <c r="I111" s="1"/>
       <c r="J111" s="52"/>
     </row>
-    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>94</v>
       </c>
@@ -11600,7 +11582,7 @@
       <c r="I112" s="1"/>
       <c r="J112" s="52"/>
     </row>
-    <row r="113" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>95</v>
       </c>
@@ -11616,7 +11598,7 @@
       <c r="I113" s="1"/>
       <c r="J113" s="55"/>
     </row>
-    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>96</v>
       </c>
@@ -11632,7 +11614,7 @@
       <c r="I114" s="1"/>
       <c r="J114" s="52"/>
     </row>
-    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>97</v>
       </c>
@@ -11648,7 +11630,7 @@
       <c r="I115" s="1"/>
       <c r="J115" s="55"/>
     </row>
-    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>98</v>
       </c>
@@ -11664,7 +11646,7 @@
       <c r="I116" s="1"/>
       <c r="J116" s="56"/>
     </row>
-    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>99</v>
       </c>
@@ -11680,7 +11662,7 @@
       <c r="I117" s="1"/>
       <c r="J117" s="52"/>
     </row>
-    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>100</v>
       </c>
@@ -11696,7 +11678,7 @@
       <c r="I118" s="1"/>
       <c r="J118" s="52"/>
     </row>
-    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>101</v>
       </c>
@@ -11712,7 +11694,7 @@
       <c r="I119" s="1"/>
       <c r="J119" s="52"/>
     </row>
-    <row r="120" spans="1:10" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>102</v>
       </c>
@@ -11728,7 +11710,7 @@
       <c r="I120" s="1"/>
       <c r="J120" s="52"/>
     </row>
-    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>103</v>
       </c>
@@ -11744,7 +11726,7 @@
       <c r="I121" s="1"/>
       <c r="J121" s="52"/>
     </row>
-    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>104</v>
       </c>
@@ -11759,7 +11741,7 @@
       <c r="H122" s="1"/>
       <c r="I122" s="1"/>
     </row>
-    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>105</v>
       </c>
@@ -11775,7 +11757,7 @@
       <c r="I123" s="1"/>
       <c r="J123" s="52"/>
     </row>
-    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>106</v>
       </c>
@@ -11791,7 +11773,7 @@
       <c r="I124" s="1"/>
       <c r="J124" s="52"/>
     </row>
-    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>107</v>
       </c>
@@ -11807,7 +11789,7 @@
       <c r="I125" s="1"/>
       <c r="J125" s="55"/>
     </row>
-    <row r="126" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A126" s="71" t="s">
         <v>925</v>
       </c>
@@ -11821,7 +11803,7 @@
       <c r="I126" s="166"/>
       <c r="J126" s="167"/>
     </row>
-    <row r="127" spans="1:10" s="3" customFormat="1" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" s="3" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="59">
         <v>108</v>
       </c>
@@ -11837,7 +11819,7 @@
       <c r="I127" s="1"/>
       <c r="J127" s="65"/>
     </row>
-    <row r="128" spans="1:10" s="3" customFormat="1" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="59">
         <v>109</v>
       </c>
@@ -11853,7 +11835,7 @@
       <c r="I128" s="1"/>
       <c r="J128" s="65"/>
     </row>
-    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="59">
         <v>110</v>
       </c>
@@ -11869,7 +11851,7 @@
       <c r="I129" s="1"/>
       <c r="J129" s="55"/>
     </row>
-    <row r="130" spans="1:10" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="59">
         <v>111</v>
       </c>
@@ -11885,7 +11867,7 @@
       <c r="I130" s="1"/>
       <c r="J130" s="177"/>
     </row>
-    <row r="131" spans="1:10" s="133" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" s="133" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A131" s="59">
         <v>112</v>
       </c>
@@ -11901,7 +11883,7 @@
       <c r="I131" s="1"/>
       <c r="J131" s="56"/>
     </row>
-    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="59">
         <v>113</v>
       </c>
@@ -11916,7 +11898,7 @@
       <c r="H132" s="1"/>
       <c r="I132" s="1"/>
     </row>
-    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="59">
         <v>114</v>
       </c>
@@ -11932,7 +11914,7 @@
       <c r="I133" s="1"/>
       <c r="J133" s="56"/>
     </row>
-    <row r="134" spans="1:10" s="132" customFormat="1" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10" s="132" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="59">
         <v>115</v>
       </c>
@@ -11948,7 +11930,7 @@
       <c r="I134" s="1"/>
       <c r="J134" s="56"/>
     </row>
-    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="59">
         <v>116</v>
       </c>
@@ -11964,7 +11946,7 @@
       <c r="I135" s="1"/>
       <c r="J135" s="52"/>
     </row>
-    <row r="136" spans="1:10" s="264" customFormat="1" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" s="264" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="59">
         <v>117</v>
       </c>
@@ -11980,7 +11962,7 @@
       <c r="I136" s="1"/>
       <c r="J136" s="61"/>
     </row>
-    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="59">
         <v>118</v>
       </c>
@@ -11996,7 +11978,7 @@
       <c r="I137" s="1"/>
       <c r="J137" s="61"/>
     </row>
-    <row r="138" spans="1:10" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="59">
         <v>119</v>
       </c>
@@ -12012,7 +11994,7 @@
       <c r="I138" s="1"/>
       <c r="J138" s="96"/>
     </row>
-    <row r="139" spans="1:10" s="264" customFormat="1" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" s="264" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="59">
         <v>120</v>
       </c>
@@ -12028,7 +12010,7 @@
       <c r="I139" s="1"/>
       <c r="J139" s="65"/>
     </row>
-    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="59">
         <v>121</v>
       </c>
@@ -12044,7 +12026,7 @@
       <c r="I140" s="1"/>
       <c r="J140" s="187"/>
     </row>
-    <row r="141" spans="1:10" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="59">
         <v>122</v>
       </c>
@@ -12082,7 +12064,7 @@
       </c>
       <c r="J142" s="96"/>
     </row>
-    <row r="143" spans="1:10" s="5" customFormat="1" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="59">
         <v>124</v>
       </c>
@@ -12098,7 +12080,7 @@
       <c r="I143" s="1"/>
       <c r="J143" s="78"/>
     </row>
-    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="59">
         <v>125</v>
       </c>
@@ -12114,7 +12096,7 @@
       <c r="I144" s="1"/>
       <c r="J144" s="65"/>
     </row>
-    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="59">
         <v>126</v>
       </c>
@@ -12130,7 +12112,7 @@
       <c r="I145" s="1"/>
       <c r="J145" s="97"/>
     </row>
-    <row r="146" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A146" s="59">
         <v>127</v>
       </c>
@@ -12146,7 +12128,7 @@
       <c r="I146" s="1"/>
       <c r="J146" s="97"/>
     </row>
-    <row r="147" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A147" s="59">
         <v>128</v>
       </c>
@@ -12162,7 +12144,7 @@
       <c r="I147" s="1"/>
       <c r="J147" s="48"/>
     </row>
-    <row r="148" spans="1:10" ht="24.9" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="59">
         <v>129</v>
       </c>
@@ -12178,7 +12160,7 @@
       <c r="I148" s="1"/>
       <c r="J148" s="55"/>
     </row>
-    <row r="149" spans="1:10" s="264" customFormat="1" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" s="264" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="59">
         <v>130</v>
       </c>
@@ -12194,7 +12176,7 @@
       <c r="I149" s="1"/>
       <c r="J149" s="262"/>
     </row>
-    <row r="150" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="59">
         <v>131</v>
       </c>
@@ -12210,7 +12192,7 @@
       <c r="I150" s="1"/>
       <c r="J150" s="65"/>
     </row>
-    <row r="151" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A151" s="59">
         <v>132</v>
       </c>
@@ -12226,7 +12208,7 @@
       <c r="I151" s="1"/>
       <c r="J151" s="188"/>
     </row>
-    <row r="152" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="59">
         <v>133</v>
       </c>
@@ -12242,7 +12224,7 @@
       <c r="I152" s="1"/>
       <c r="J152" s="52"/>
     </row>
-    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="59">
         <v>134</v>
       </c>
@@ -12258,7 +12240,7 @@
       <c r="I153" s="1"/>
       <c r="J153" s="52"/>
     </row>
-    <row r="154" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A154" s="59">
         <v>135</v>
       </c>
@@ -12274,7 +12256,7 @@
       <c r="I154" s="1"/>
       <c r="J154" s="182"/>
     </row>
-    <row r="155" spans="1:10" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="59">
         <v>136</v>
       </c>
@@ -12290,7 +12272,7 @@
       <c r="I155" s="1"/>
       <c r="J155" s="65"/>
     </row>
-    <row r="156" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A156" s="59">
         <v>137</v>
       </c>
@@ -12306,7 +12288,7 @@
       <c r="I156" s="1"/>
       <c r="J156" s="75"/>
     </row>
-    <row r="157" spans="1:10" s="264" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" s="264" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="59">
         <v>138</v>
       </c>
@@ -12322,7 +12304,7 @@
       <c r="I157" s="1"/>
       <c r="J157" s="65"/>
     </row>
-    <row r="158" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A158" s="59">
         <v>139</v>
       </c>
@@ -12338,7 +12320,7 @@
       <c r="I158" s="1"/>
       <c r="J158" s="75"/>
     </row>
-    <row r="159" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A159" s="59">
         <v>140</v>
       </c>
@@ -12354,7 +12336,7 @@
       <c r="I159" s="1"/>
       <c r="J159" s="185"/>
     </row>
-    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" s="59">
         <v>141</v>
       </c>
@@ -12370,7 +12352,7 @@
       <c r="I160" s="1"/>
       <c r="J160" s="65"/>
     </row>
-    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" s="59">
         <v>142</v>
       </c>
@@ -12386,7 +12368,7 @@
       <c r="I161" s="1"/>
       <c r="J161" s="65"/>
     </row>
-    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" s="59">
         <v>143</v>
       </c>
@@ -12402,7 +12384,7 @@
       <c r="I162" s="1"/>
       <c r="J162" s="55"/>
     </row>
-    <row r="163" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A163" s="59">
         <v>144</v>
       </c>
@@ -12418,7 +12400,7 @@
       <c r="I163" s="1"/>
       <c r="J163" s="75"/>
     </row>
-    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" s="59">
         <v>145</v>
       </c>
@@ -12434,7 +12416,7 @@
       <c r="I164" s="1"/>
       <c r="J164" s="52"/>
     </row>
-    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" s="59">
         <v>146</v>
       </c>
@@ -12450,7 +12432,7 @@
       <c r="I165" s="1"/>
       <c r="J165" s="52"/>
     </row>
-    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" s="59">
         <v>147</v>
       </c>
@@ -12466,7 +12448,7 @@
       <c r="I166" s="1"/>
       <c r="J166" s="52"/>
     </row>
-    <row r="167" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A167" s="59">
         <v>148</v>
       </c>
@@ -12482,7 +12464,7 @@
       <c r="I167" s="1"/>
       <c r="J167" s="185"/>
     </row>
-    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="59">
         <v>149</v>
       </c>
@@ -12498,7 +12480,7 @@
       <c r="I168" s="1"/>
       <c r="J168" s="65"/>
     </row>
-    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" s="59">
         <v>150</v>
       </c>
@@ -12514,7 +12496,7 @@
       <c r="I169" s="1"/>
       <c r="J169" s="65"/>
     </row>
-    <row r="170" spans="1:10" s="7" customFormat="1" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" s="7" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="59">
         <v>151</v>
       </c>
@@ -12530,7 +12512,7 @@
       <c r="I170" s="1"/>
       <c r="J170" s="75"/>
     </row>
-    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" s="59">
         <v>152</v>
       </c>
@@ -12546,7 +12528,7 @@
       <c r="I171" s="1"/>
       <c r="J171" s="52"/>
     </row>
-    <row r="172" spans="1:10" s="4" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:10" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A172" s="59">
         <v>153</v>
       </c>
@@ -12562,7 +12544,7 @@
       <c r="I172" s="1"/>
       <c r="J172" s="55"/>
     </row>
-    <row r="173" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A173" s="59">
         <v>154</v>
       </c>
@@ -12578,7 +12560,7 @@
       <c r="I173" s="1"/>
       <c r="J173" s="185"/>
     </row>
-    <row r="174" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A174" s="59">
         <v>155</v>
       </c>
@@ -12594,7 +12576,7 @@
       <c r="I174" s="1"/>
       <c r="J174" s="185"/>
     </row>
-    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" s="59">
         <v>156</v>
       </c>
@@ -12610,7 +12592,7 @@
       <c r="I175" s="1"/>
       <c r="J175" s="52"/>
     </row>
-    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" s="59">
         <v>157</v>
       </c>
@@ -12626,7 +12608,7 @@
       <c r="I176" s="1"/>
       <c r="J176" s="52"/>
     </row>
-    <row r="177" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" s="59">
         <v>158</v>
       </c>
@@ -12642,7 +12624,7 @@
       <c r="I177" s="1"/>
       <c r="J177" s="52"/>
     </row>
-    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" s="59">
         <v>159</v>
       </c>
@@ -12658,7 +12640,7 @@
       <c r="I178" s="1"/>
       <c r="J178" s="52"/>
     </row>
-    <row r="179" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A179" s="59">
         <v>160</v>
       </c>
@@ -12674,7 +12656,7 @@
       <c r="I179" s="1"/>
       <c r="J179" s="185"/>
     </row>
-    <row r="180" spans="1:10" s="266" customFormat="1" ht="30.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:10" s="266" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="59">
         <v>161</v>
       </c>
@@ -12690,7 +12672,7 @@
       <c r="I180" s="1"/>
       <c r="J180" s="56"/>
     </row>
-    <row r="181" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A181" s="59">
         <v>162</v>
       </c>
@@ -12706,7 +12688,7 @@
       <c r="I181" s="1"/>
       <c r="J181" s="123"/>
     </row>
-    <row r="182" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A182" s="59">
         <v>163</v>
       </c>
@@ -12722,7 +12704,7 @@
       <c r="I182" s="1"/>
       <c r="J182" s="185"/>
     </row>
-    <row r="183" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A183" s="59">
         <v>164</v>
       </c>
@@ -12760,7 +12742,7 @@
       </c>
       <c r="J184" s="123"/>
     </row>
-    <row r="185" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A185" s="59">
         <v>166</v>
       </c>
@@ -12798,7 +12780,7 @@
       </c>
       <c r="J186" s="123"/>
     </row>
-    <row r="187" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A187" s="59">
         <v>168</v>
       </c>
@@ -12814,7 +12796,7 @@
       <c r="I187" s="1"/>
       <c r="J187" s="185"/>
     </row>
-    <row r="188" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A188" s="59">
         <v>169</v>
       </c>
@@ -12830,7 +12812,7 @@
       <c r="I188" s="1"/>
       <c r="J188" s="185"/>
     </row>
-    <row r="189" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A189" s="59">
         <v>170</v>
       </c>
@@ -12846,7 +12828,7 @@
       <c r="I189" s="1"/>
       <c r="J189" s="185"/>
     </row>
-    <row r="190" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A190" s="59">
         <v>171</v>
       </c>
@@ -12862,7 +12844,7 @@
       <c r="I190" s="1"/>
       <c r="J190" s="123"/>
     </row>
-    <row r="191" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A191" s="59">
         <v>172</v>
       </c>
@@ -12878,7 +12860,7 @@
       <c r="I191" s="1"/>
       <c r="J191" s="185"/>
     </row>
-    <row r="192" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A192" s="59">
         <v>173</v>
       </c>
@@ -12894,7 +12876,7 @@
       <c r="I192" s="1"/>
       <c r="J192" s="185"/>
     </row>
-    <row r="193" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A193" s="59">
         <v>174</v>
       </c>
@@ -12910,7 +12892,7 @@
       <c r="I193" s="1"/>
       <c r="J193" s="185"/>
     </row>
-    <row r="194" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A194" s="59">
         <v>175</v>
       </c>
@@ -12948,7 +12930,7 @@
       </c>
       <c r="J195" s="346"/>
     </row>
-    <row r="196" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A196" s="59">
         <v>177</v>
       </c>
@@ -12964,7 +12946,7 @@
       <c r="I196" s="1"/>
       <c r="J196" s="123"/>
     </row>
-    <row r="197" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A197" s="59">
         <v>178</v>
       </c>
@@ -12980,7 +12962,7 @@
       <c r="I197" s="1"/>
       <c r="J197" s="123"/>
     </row>
-    <row r="198" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A198" s="59">
         <v>179</v>
       </c>
@@ -12996,7 +12978,7 @@
       <c r="I198" s="1"/>
       <c r="J198" s="123"/>
     </row>
-    <row r="199" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A199" s="59">
         <v>180</v>
       </c>
@@ -13012,7 +12994,7 @@
       <c r="I199" s="1"/>
       <c r="J199" s="123"/>
     </row>
-    <row r="200" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A200" s="59">
         <v>181</v>
       </c>
@@ -13028,7 +13010,7 @@
       <c r="I200" s="1"/>
       <c r="J200" s="123"/>
     </row>
-    <row r="201" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A201" s="59">
         <v>182</v>
       </c>
@@ -13044,7 +13026,7 @@
       <c r="I201" s="1"/>
       <c r="J201" s="123"/>
     </row>
-    <row r="202" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A202" s="59">
         <v>183</v>
       </c>
@@ -13060,7 +13042,7 @@
       <c r="I202" s="1"/>
       <c r="J202" s="123"/>
     </row>
-    <row r="203" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A203" s="59">
         <v>184</v>
       </c>
@@ -13076,7 +13058,7 @@
       <c r="I203" s="1"/>
       <c r="J203" s="185"/>
     </row>
-    <row r="204" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A204" s="59">
         <v>185</v>
       </c>
@@ -13092,7 +13074,7 @@
       <c r="I204" s="1"/>
       <c r="J204" s="185"/>
     </row>
-    <row r="205" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A205" s="59">
         <v>186</v>
       </c>
@@ -13108,7 +13090,7 @@
       <c r="I205" s="1"/>
       <c r="J205" s="185"/>
     </row>
-    <row r="206" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A206" s="59">
         <v>187</v>
       </c>
@@ -13124,7 +13106,7 @@
       <c r="I206" s="1"/>
       <c r="J206" s="185"/>
     </row>
-    <row r="207" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A207" s="59">
         <v>188</v>
       </c>
@@ -13140,7 +13122,7 @@
       <c r="I207" s="1"/>
       <c r="J207" s="123"/>
     </row>
-    <row r="208" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A208" s="59">
         <v>189</v>
       </c>
@@ -13156,7 +13138,7 @@
       <c r="I208" s="1"/>
       <c r="J208" s="185"/>
     </row>
-    <row r="209" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A209" s="59">
         <v>190</v>
       </c>
@@ -13172,7 +13154,7 @@
       <c r="I209" s="1"/>
       <c r="J209" s="123"/>
     </row>
-    <row r="210" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A210" s="59">
         <v>191</v>
       </c>
@@ -13188,7 +13170,7 @@
       <c r="I210" s="1"/>
       <c r="J210" s="185"/>
     </row>
-    <row r="211" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A211" s="59">
         <v>192</v>
       </c>
@@ -13204,7 +13186,7 @@
       <c r="I211" s="1"/>
       <c r="J211" s="185"/>
     </row>
-    <row r="212" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A212" s="59">
         <v>193</v>
       </c>
@@ -13220,7 +13202,7 @@
       <c r="I212" s="1"/>
       <c r="J212" s="185"/>
     </row>
-    <row r="213" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A213" s="59">
         <v>194</v>
       </c>
@@ -13236,7 +13218,7 @@
       <c r="I213" s="1"/>
       <c r="J213" s="185"/>
     </row>
-    <row r="214" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A214" s="59">
         <v>195</v>
       </c>
@@ -13252,7 +13234,7 @@
       <c r="I214" s="1"/>
       <c r="J214" s="185"/>
     </row>
-    <row r="215" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A215" s="59">
         <v>196</v>
       </c>
@@ -13268,7 +13250,7 @@
       <c r="I215" s="1"/>
       <c r="J215" s="185"/>
     </row>
-    <row r="216" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A216" s="59">
         <v>197</v>
       </c>
@@ -13284,7 +13266,7 @@
       <c r="I216" s="1"/>
       <c r="J216" s="185"/>
     </row>
-    <row r="217" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A217" s="59">
         <v>198</v>
       </c>
@@ -13300,7 +13282,7 @@
       <c r="I217" s="1"/>
       <c r="J217" s="185"/>
     </row>
-    <row r="218" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A218" s="59">
         <v>199</v>
       </c>
@@ -13316,7 +13298,7 @@
       <c r="I218" s="1"/>
       <c r="J218" s="185"/>
     </row>
-    <row r="219" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A219" s="59">
         <v>200</v>
       </c>
@@ -13332,7 +13314,7 @@
       <c r="I219" s="1"/>
       <c r="J219" s="123"/>
     </row>
-    <row r="220" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A220" s="59">
         <v>201</v>
       </c>
@@ -13348,7 +13330,7 @@
       <c r="I220" s="1"/>
       <c r="J220" s="123"/>
     </row>
-    <row r="221" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A221" s="59">
         <v>202</v>
       </c>
@@ -13364,7 +13346,7 @@
       <c r="I221" s="1"/>
       <c r="J221" s="185"/>
     </row>
-    <row r="222" spans="1:10" s="132" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:10" s="132" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="59">
         <v>203</v>
       </c>
@@ -13380,7 +13362,7 @@
       <c r="I222" s="1"/>
       <c r="J222" s="185"/>
     </row>
-    <row r="223" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A223" s="59">
         <v>204</v>
       </c>
@@ -13396,7 +13378,7 @@
       <c r="I223" s="1"/>
       <c r="J223" s="185"/>
     </row>
-    <row r="224" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A224" s="59">
         <v>205</v>
       </c>
@@ -13412,7 +13394,7 @@
       <c r="I224" s="1"/>
       <c r="J224" s="185"/>
     </row>
-    <row r="225" spans="1:10" s="132" customFormat="1" ht="30.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:10" s="132" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A225" s="59">
         <v>206</v>
       </c>
@@ -13428,7 +13410,7 @@
       <c r="I225" s="1"/>
       <c r="J225" s="185"/>
     </row>
-    <row r="226" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A226" s="59">
         <v>207</v>
       </c>
@@ -13444,7 +13426,7 @@
       <c r="I226" s="1"/>
       <c r="J226" s="185"/>
     </row>
-    <row r="227" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A227" s="59">
         <v>208</v>
       </c>
@@ -13460,7 +13442,7 @@
       <c r="I227" s="1"/>
       <c r="J227" s="123"/>
     </row>
-    <row r="228" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A228" s="59">
         <v>209</v>
       </c>
@@ -13476,7 +13458,7 @@
       <c r="I228" s="1"/>
       <c r="J228" s="123"/>
     </row>
-    <row r="229" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A229" s="59">
         <v>210</v>
       </c>
@@ -13492,7 +13474,7 @@
       <c r="I229" s="1"/>
       <c r="J229" s="123"/>
     </row>
-    <row r="230" spans="1:10" s="132" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:10" s="132" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A230" s="59">
         <v>211</v>
       </c>
@@ -13554,7 +13536,7 @@
       </c>
       <c r="J232" s="123"/>
     </row>
-    <row r="233" spans="1:10" s="266" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:10" s="266" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A233" s="59">
         <v>214</v>
       </c>
@@ -13613,10 +13595,10 @@
       <c r="J235" s="123"/>
     </row>
     <row r="236" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="381" t="s">
+      <c r="A236" s="368" t="s">
         <v>289</v>
       </c>
-      <c r="B236" s="385"/>
+      <c r="B236" s="372"/>
       <c r="C236" s="164">
         <f>SUM(C8:C235)</f>
         <v>54</v>
@@ -13648,15 +13630,6 @@
       <c r="J236" s="131"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M236" xr:uid="{00000000-0009-0000-0000-000002000000}">
-    <filterColumn colId="3">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="4" showButton="0"/>
-    <filterColumn colId="5" showButton="0"/>
-  </autoFilter>
   <mergeCells count="4">
     <mergeCell ref="A236:B236"/>
     <mergeCell ref="A2:J2"/>
@@ -13736,85 +13709,85 @@
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="389" t="s">
+      <c r="A2" s="376" t="s">
         <v>82</v>
       </c>
-      <c r="B2" s="389"/>
-      <c r="C2" s="389"/>
-      <c r="D2" s="389"/>
-      <c r="E2" s="389"/>
-      <c r="F2" s="389"/>
-      <c r="G2" s="389"/>
-      <c r="H2" s="389"/>
-      <c r="I2" s="389"/>
-      <c r="J2" s="389"/>
-      <c r="K2" s="389"/>
-      <c r="L2" s="389"/>
-      <c r="M2" s="389"/>
-      <c r="N2" s="389"/>
-      <c r="O2" s="389"/>
-      <c r="P2" s="389"/>
-      <c r="Q2" s="389"/>
-      <c r="R2" s="389"/>
-      <c r="S2" s="389"/>
-      <c r="T2" s="389"/>
+      <c r="B2" s="376"/>
+      <c r="C2" s="376"/>
+      <c r="D2" s="376"/>
+      <c r="E2" s="376"/>
+      <c r="F2" s="376"/>
+      <c r="G2" s="376"/>
+      <c r="H2" s="376"/>
+      <c r="I2" s="376"/>
+      <c r="J2" s="376"/>
+      <c r="K2" s="376"/>
+      <c r="L2" s="376"/>
+      <c r="M2" s="376"/>
+      <c r="N2" s="376"/>
+      <c r="O2" s="376"/>
+      <c r="P2" s="376"/>
+      <c r="Q2" s="376"/>
+      <c r="R2" s="376"/>
+      <c r="S2" s="376"/>
+      <c r="T2" s="376"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="37"/>
       <c r="B3" s="100"/>
-      <c r="R3" s="390"/>
-      <c r="S3" s="391"/>
-      <c r="T3" s="391"/>
+      <c r="R3" s="377"/>
+      <c r="S3" s="378"/>
+      <c r="T3" s="378"/>
     </row>
     <row r="4" spans="1:20" s="101" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="392" t="s">
+      <c r="A4" s="379" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="393" t="s">
+      <c r="B4" s="380" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="394" t="s">
+      <c r="C4" s="381" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="395"/>
-      <c r="E4" s="392" t="s">
+      <c r="D4" s="382"/>
+      <c r="E4" s="379" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="392"/>
-      <c r="G4" s="392"/>
-      <c r="H4" s="392"/>
-      <c r="I4" s="392"/>
-      <c r="J4" s="392"/>
-      <c r="K4" s="392"/>
-      <c r="L4" s="392"/>
-      <c r="M4" s="371" t="s">
+      <c r="F4" s="379"/>
+      <c r="G4" s="379"/>
+      <c r="H4" s="379"/>
+      <c r="I4" s="379"/>
+      <c r="J4" s="379"/>
+      <c r="K4" s="379"/>
+      <c r="L4" s="379"/>
+      <c r="M4" s="383" t="s">
         <v>20</v>
       </c>
-      <c r="N4" s="371" t="s">
+      <c r="N4" s="383" t="s">
         <v>34</v>
       </c>
-      <c r="O4" s="396" t="s">
+      <c r="O4" s="385" t="s">
         <v>35</v>
       </c>
-      <c r="P4" s="393" t="s">
+      <c r="P4" s="380" t="s">
         <v>23</v>
       </c>
-      <c r="Q4" s="393" t="s">
+      <c r="Q4" s="380" t="s">
         <v>24</v>
       </c>
-      <c r="R4" s="393" t="s">
+      <c r="R4" s="380" t="s">
         <v>25</v>
       </c>
-      <c r="S4" s="393" t="s">
+      <c r="S4" s="380" t="s">
         <v>26</v>
       </c>
-      <c r="T4" s="398" t="s">
+      <c r="T4" s="387" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:20" s="101" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="392"/>
-      <c r="B5" s="393"/>
+      <c r="A5" s="379"/>
+      <c r="B5" s="380"/>
       <c r="C5" s="250" t="s">
         <v>27</v>
       </c>
@@ -13845,14 +13818,14 @@
       <c r="L5" s="211" t="s">
         <v>30</v>
       </c>
-      <c r="M5" s="372"/>
-      <c r="N5" s="372"/>
-      <c r="O5" s="397"/>
-      <c r="P5" s="393"/>
-      <c r="Q5" s="393"/>
-      <c r="R5" s="393"/>
-      <c r="S5" s="393"/>
-      <c r="T5" s="380"/>
+      <c r="M5" s="384"/>
+      <c r="N5" s="384"/>
+      <c r="O5" s="386"/>
+      <c r="P5" s="380"/>
+      <c r="Q5" s="380"/>
+      <c r="R5" s="380"/>
+      <c r="S5" s="380"/>
+      <c r="T5" s="367"/>
     </row>
     <row r="6" spans="1:20" s="101" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="211" t="s">
@@ -14510,10 +14483,10 @@
       </c>
     </row>
     <row r="28" spans="1:20" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="377" t="s">
+      <c r="A28" s="364" t="s">
         <v>289</v>
       </c>
-      <c r="B28" s="377"/>
+      <c r="B28" s="364"/>
       <c r="C28" s="211">
         <f>SUM(C26:C27)</f>
         <v>60</v>
@@ -14624,7 +14597,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor rgb="FF147216"/>
   </sheetPr>
   <dimension ref="A1:T76"/>
@@ -14660,72 +14633,72 @@
       </c>
     </row>
     <row r="2" spans="1:20" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A2" s="399" t="s">
+      <c r="A2" s="388" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="399"/>
-      <c r="C2" s="399"/>
-      <c r="D2" s="399"/>
-      <c r="E2" s="399"/>
-      <c r="F2" s="399"/>
-      <c r="G2" s="399"/>
-      <c r="H2" s="399"/>
-      <c r="I2" s="399"/>
-      <c r="J2" s="399"/>
-      <c r="K2" s="399"/>
-      <c r="L2" s="399"/>
-      <c r="M2" s="399"/>
-      <c r="N2" s="399"/>
-      <c r="O2" s="399"/>
-      <c r="P2" s="399"/>
-      <c r="Q2" s="399"/>
+      <c r="B2" s="388"/>
+      <c r="C2" s="388"/>
+      <c r="D2" s="388"/>
+      <c r="E2" s="388"/>
+      <c r="F2" s="388"/>
+      <c r="G2" s="388"/>
+      <c r="H2" s="388"/>
+      <c r="I2" s="388"/>
+      <c r="J2" s="388"/>
+      <c r="K2" s="388"/>
+      <c r="L2" s="388"/>
+      <c r="M2" s="388"/>
+      <c r="N2" s="388"/>
+      <c r="O2" s="388"/>
+      <c r="P2" s="388"/>
+      <c r="Q2" s="388"/>
     </row>
     <row r="3" spans="1:20" s="101" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="396" t="s">
+      <c r="A3" s="385" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="398" t="s">
+      <c r="B3" s="387" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="392" t="s">
+      <c r="C3" s="379" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="392"/>
-      <c r="E3" s="392" t="s">
+      <c r="D3" s="379"/>
+      <c r="E3" s="379" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="392"/>
-      <c r="G3" s="392"/>
-      <c r="H3" s="392"/>
-      <c r="I3" s="392"/>
-      <c r="J3" s="398" t="s">
+      <c r="F3" s="379"/>
+      <c r="G3" s="379"/>
+      <c r="H3" s="379"/>
+      <c r="I3" s="379"/>
+      <c r="J3" s="387" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="398" t="s">
+      <c r="K3" s="387" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="398" t="s">
+      <c r="L3" s="387" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="398" t="s">
+      <c r="M3" s="387" t="s">
         <v>23</v>
       </c>
-      <c r="N3" s="398" t="s">
+      <c r="N3" s="387" t="s">
         <v>24</v>
       </c>
-      <c r="O3" s="398" t="s">
+      <c r="O3" s="387" t="s">
         <v>25</v>
       </c>
-      <c r="P3" s="398" t="s">
+      <c r="P3" s="387" t="s">
         <v>26</v>
       </c>
-      <c r="Q3" s="398" t="s">
+      <c r="Q3" s="387" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:20" s="101" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="397"/>
-      <c r="B4" s="398"/>
+      <c r="A4" s="386"/>
+      <c r="B4" s="387"/>
       <c r="C4" s="276" t="s">
         <v>27</v>
       </c>
@@ -14747,14 +14720,14 @@
       <c r="I4" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="398"/>
-      <c r="K4" s="398"/>
-      <c r="L4" s="398"/>
-      <c r="M4" s="398"/>
-      <c r="N4" s="398"/>
-      <c r="O4" s="398"/>
-      <c r="P4" s="398"/>
-      <c r="Q4" s="380"/>
+      <c r="J4" s="387"/>
+      <c r="K4" s="387"/>
+      <c r="L4" s="387"/>
+      <c r="M4" s="387"/>
+      <c r="N4" s="387"/>
+      <c r="O4" s="387"/>
+      <c r="P4" s="387"/>
+      <c r="Q4" s="367"/>
       <c r="T4" s="101" t="s">
         <v>282</v>
       </c>
@@ -14812,7 +14785,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="2" customFormat="1" ht="35.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -14838,7 +14811,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2</v>
       </c>
@@ -14861,7 +14834,7 @@
       <c r="P7" s="54"/>
       <c r="Q7" s="76"/>
     </row>
-    <row r="8" spans="1:20" s="2" customFormat="1" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" s="2" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -14887,7 +14860,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="9" spans="1:20" s="2" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>4</v>
       </c>
@@ -14910,7 +14883,7 @@
       <c r="P9" s="54"/>
       <c r="Q9" s="121"/>
     </row>
-    <row r="10" spans="1:20" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>5</v>
       </c>
@@ -14977,7 +14950,7 @@
       </c>
       <c r="Q11" s="76"/>
     </row>
-    <row r="12" spans="1:20" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>7</v>
       </c>
@@ -15000,7 +14973,7 @@
       <c r="P12" s="54"/>
       <c r="Q12" s="96"/>
     </row>
-    <row r="13" spans="1:20" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>8</v>
       </c>
@@ -15023,7 +14996,7 @@
       <c r="P13" s="54"/>
       <c r="Q13" s="122"/>
     </row>
-    <row r="14" spans="1:20" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>9</v>
       </c>
@@ -15087,7 +15060,7 @@
       </c>
       <c r="Q15" s="177"/>
     </row>
-    <row r="16" spans="1:20" s="2" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>11</v>
       </c>
@@ -15110,7 +15083,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="98"/>
     </row>
-    <row r="17" spans="1:20" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>12</v>
       </c>
@@ -15133,7 +15106,7 @@
       <c r="P17" s="54"/>
       <c r="Q17" s="96"/>
     </row>
-    <row r="18" spans="1:20" ht="42" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>13</v>
       </c>
@@ -15156,7 +15129,7 @@
       <c r="P18" s="54"/>
       <c r="Q18" s="76"/>
     </row>
-    <row r="19" spans="1:20" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>14</v>
       </c>
@@ -15179,7 +15152,7 @@
       <c r="P19" s="54"/>
       <c r="Q19" s="122"/>
     </row>
-    <row r="20" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>15</v>
       </c>
@@ -15202,7 +15175,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="123"/>
     </row>
-    <row r="21" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>16</v>
       </c>
@@ -15225,7 +15198,7 @@
       <c r="P21" s="54"/>
       <c r="Q21" s="123"/>
     </row>
-    <row r="22" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>17</v>
       </c>
@@ -15248,7 +15221,7 @@
       <c r="P22" s="54"/>
       <c r="Q22" s="76"/>
     </row>
-    <row r="23" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>18</v>
       </c>
@@ -15271,7 +15244,7 @@
       <c r="P23" s="54"/>
       <c r="Q23" s="76"/>
     </row>
-    <row r="24" spans="1:20" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>19</v>
       </c>
@@ -15306,7 +15279,7 @@
       </c>
       <c r="Q24" s="122"/>
     </row>
-    <row r="25" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>20</v>
       </c>
@@ -15425,7 +15398,7 @@
       </c>
       <c r="Q27" s="320"/>
     </row>
-    <row r="28" spans="1:20" s="2" customFormat="1" ht="35.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>23</v>
       </c>
@@ -15498,7 +15471,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="37.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>25</v>
       </c>
@@ -15562,7 +15535,7 @@
       </c>
       <c r="Q31" s="76"/>
     </row>
-    <row r="32" spans="1:20" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>27</v>
       </c>
@@ -15585,7 +15558,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="123"/>
     </row>
-    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>28</v>
       </c>
@@ -15608,7 +15581,7 @@
       <c r="P33" s="54"/>
       <c r="Q33" s="122"/>
     </row>
-    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>29</v>
       </c>
@@ -15631,7 +15604,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="122"/>
     </row>
-    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>30</v>
       </c>
@@ -15654,7 +15627,7 @@
       <c r="P35" s="54"/>
       <c r="Q35" s="122"/>
     </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>31</v>
       </c>
@@ -15677,7 +15650,7 @@
       <c r="P36" s="54"/>
       <c r="Q36" s="123"/>
     </row>
-    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>32</v>
       </c>
@@ -15700,7 +15673,7 @@
       <c r="P37" s="54"/>
       <c r="Q37" s="122"/>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>33</v>
       </c>
@@ -15723,7 +15696,7 @@
       <c r="P38" s="54"/>
       <c r="Q38" s="122"/>
     </row>
-    <row r="39" spans="1:17" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>34</v>
       </c>
@@ -15746,7 +15719,7 @@
       <c r="P39" s="54"/>
       <c r="Q39" s="76"/>
     </row>
-    <row r="40" spans="1:17" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>35</v>
       </c>
@@ -15769,7 +15742,7 @@
       <c r="P40" s="54"/>
       <c r="Q40" s="124"/>
     </row>
-    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>36</v>
       </c>
@@ -15792,7 +15765,7 @@
       <c r="P41" s="54"/>
       <c r="Q41" s="122"/>
     </row>
-    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>37</v>
       </c>
@@ -15815,7 +15788,7 @@
       <c r="P42" s="54"/>
       <c r="Q42" s="122"/>
     </row>
-    <row r="43" spans="1:17" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>38</v>
       </c>
@@ -15838,7 +15811,7 @@
       <c r="P43" s="54"/>
       <c r="Q43" s="123"/>
     </row>
-    <row r="44" spans="1:17" ht="49.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>39</v>
       </c>
@@ -15861,7 +15834,7 @@
       <c r="P44" s="54"/>
       <c r="Q44" s="76"/>
     </row>
-    <row r="45" spans="1:17" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>40</v>
       </c>
@@ -15884,7 +15857,7 @@
       <c r="P45" s="54"/>
       <c r="Q45" s="97"/>
     </row>
-    <row r="46" spans="1:17" s="2" customFormat="1" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" s="2" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>41</v>
       </c>
@@ -15907,7 +15880,7 @@
       <c r="P46" s="54"/>
       <c r="Q46" s="65"/>
     </row>
-    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>42</v>
       </c>
@@ -15930,7 +15903,7 @@
       <c r="P47" s="54"/>
       <c r="Q47" s="97"/>
     </row>
-    <row r="48" spans="1:17" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>43</v>
       </c>
@@ -15953,7 +15926,7 @@
       <c r="P48" s="54"/>
       <c r="Q48" s="122"/>
     </row>
-    <row r="49" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>44</v>
       </c>
@@ -15976,7 +15949,7 @@
       <c r="P49" s="54"/>
       <c r="Q49" s="76"/>
     </row>
-    <row r="50" spans="1:20" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>45</v>
       </c>
@@ -15999,7 +15972,7 @@
       <c r="P50" s="54"/>
       <c r="Q50" s="122"/>
     </row>
-    <row r="51" spans="1:20" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>46</v>
       </c>
@@ -16022,7 +15995,7 @@
       <c r="P51" s="54"/>
       <c r="Q51" s="122"/>
     </row>
-    <row r="52" spans="1:20" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>47</v>
       </c>
@@ -16045,7 +16018,7 @@
       <c r="P52" s="54"/>
       <c r="Q52" s="97"/>
     </row>
-    <row r="53" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>48</v>
       </c>
@@ -16068,7 +16041,7 @@
       <c r="P53" s="54"/>
       <c r="Q53" s="76"/>
     </row>
-    <row r="54" spans="1:20" s="2" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:20" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>49</v>
       </c>
@@ -16091,7 +16064,7 @@
       <c r="P54" s="54"/>
       <c r="Q54" s="96"/>
     </row>
-    <row r="55" spans="1:20" ht="15.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>50</v>
       </c>
@@ -16114,7 +16087,7 @@
       <c r="P55" s="54"/>
       <c r="Q55" s="77"/>
     </row>
-    <row r="56" spans="1:20" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>51</v>
       </c>
@@ -16137,7 +16110,7 @@
       <c r="P56" s="54"/>
       <c r="Q56" s="124"/>
     </row>
-    <row r="57" spans="1:20" ht="44.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>52</v>
       </c>
@@ -16163,7 +16136,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="58" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>53</v>
       </c>
@@ -16186,7 +16159,7 @@
       <c r="P58" s="54"/>
       <c r="Q58" s="122"/>
     </row>
-    <row r="59" spans="1:20" ht="35.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>54</v>
       </c>
@@ -16212,7 +16185,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="60" spans="1:20" s="15" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>55</v>
       </c>
@@ -16235,7 +16208,7 @@
       <c r="P60" s="308"/>
       <c r="Q60" s="122"/>
     </row>
-    <row r="61" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>56</v>
       </c>
@@ -16299,7 +16272,7 @@
       </c>
       <c r="Q62" s="122"/>
     </row>
-    <row r="63" spans="1:20" s="2" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:20" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>58</v>
       </c>
@@ -16322,7 +16295,7 @@
       <c r="P63" s="54"/>
       <c r="Q63" s="78"/>
     </row>
-    <row r="64" spans="1:20" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>59</v>
       </c>
@@ -16345,7 +16318,7 @@
       <c r="P64" s="54"/>
       <c r="Q64" s="97"/>
     </row>
-    <row r="65" spans="1:17" s="2" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>60</v>
       </c>
@@ -16368,7 +16341,7 @@
       <c r="P65" s="54"/>
       <c r="Q65" s="48"/>
     </row>
-    <row r="66" spans="1:17" s="2" customFormat="1" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" s="2" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>61</v>
       </c>
@@ -16391,7 +16364,7 @@
       <c r="P66" s="54"/>
       <c r="Q66" s="87"/>
     </row>
-    <row r="67" spans="1:17" s="2" customFormat="1" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>62</v>
       </c>
@@ -16414,7 +16387,7 @@
       <c r="P67" s="54"/>
       <c r="Q67" s="76"/>
     </row>
-    <row r="68" spans="1:17" s="2" customFormat="1" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>63</v>
       </c>
@@ -16437,7 +16410,7 @@
       <c r="P68" s="54"/>
       <c r="Q68" s="76"/>
     </row>
-    <row r="69" spans="1:17" s="2" customFormat="1" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>64</v>
       </c>
@@ -16460,7 +16433,7 @@
       <c r="P69" s="54"/>
       <c r="Q69" s="97"/>
     </row>
-    <row r="70" spans="1:17" s="2" customFormat="1" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>65</v>
       </c>
@@ -16483,7 +16456,7 @@
       <c r="P70" s="54"/>
       <c r="Q70" s="269"/>
     </row>
-    <row r="71" spans="1:17" s="2" customFormat="1" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>66</v>
       </c>
@@ -16506,7 +16479,7 @@
       <c r="P71" s="54"/>
       <c r="Q71" s="76"/>
     </row>
-    <row r="72" spans="1:17" s="2" customFormat="1" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>67</v>
       </c>
@@ -16577,7 +16550,7 @@
       </c>
       <c r="C74" s="136">
         <f>SUBTOTAL(9,C11:C73)</f>
-        <v>611</v>
+        <v>831</v>
       </c>
       <c r="D74" s="136">
         <f t="shared" ref="D74:L74" si="27">SUM(D6:D73)</f>
@@ -16621,12 +16594,12 @@
       <c r="P74" s="136"/>
       <c r="Q74" s="125"/>
     </row>
-    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="N75" s="5" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="M76" s="5" t="s">
         <v>282</v>
       </c>
@@ -16640,19 +16613,6 @@
     <protectedRange sqref="B72" name="Range1"/>
     <protectedRange sqref="B73" name="Range1_2"/>
   </protectedRanges>
-  <autoFilter ref="A5:Q76" xr:uid="{00000000-0009-0000-0000-000004000000}">
-    <filterColumn colId="3">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="15">
-      <filters blank="1">
-        <filter val="100.00%"/>
-        <filter val="98.14%"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <mergeCells count="13">
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="K3:K4"/>
@@ -16687,7 +16647,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor rgb="FF147216"/>
   </sheetPr>
   <dimension ref="A1:R1048576"/>
@@ -16717,74 +16677,74 @@
       </c>
     </row>
     <row r="2" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="403" t="s">
+      <c r="A2" s="392" t="s">
         <v>587</v>
       </c>
-      <c r="B2" s="403"/>
-      <c r="C2" s="403"/>
-      <c r="D2" s="403"/>
-      <c r="E2" s="403"/>
-      <c r="F2" s="403"/>
-      <c r="G2" s="403"/>
-      <c r="H2" s="403"/>
-      <c r="I2" s="403"/>
-      <c r="J2" s="403"/>
-      <c r="K2" s="403"/>
-      <c r="L2" s="403"/>
-      <c r="M2" s="403"/>
-      <c r="N2" s="403"/>
-      <c r="O2" s="403"/>
-      <c r="P2" s="403"/>
-      <c r="Q2" s="403"/>
-      <c r="R2" s="403"/>
+      <c r="B2" s="392"/>
+      <c r="C2" s="392"/>
+      <c r="D2" s="392"/>
+      <c r="E2" s="392"/>
+      <c r="F2" s="392"/>
+      <c r="G2" s="392"/>
+      <c r="H2" s="392"/>
+      <c r="I2" s="392"/>
+      <c r="J2" s="392"/>
+      <c r="K2" s="392"/>
+      <c r="L2" s="392"/>
+      <c r="M2" s="392"/>
+      <c r="N2" s="392"/>
+      <c r="O2" s="392"/>
+      <c r="P2" s="392"/>
+      <c r="Q2" s="392"/>
+      <c r="R2" s="392"/>
     </row>
     <row r="3" spans="1:18" s="95" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="380" t="s">
+      <c r="A3" s="367" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="398" t="s">
+      <c r="B3" s="387" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="380" t="s">
+      <c r="C3" s="367" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="380"/>
-      <c r="E3" s="380" t="s">
+      <c r="D3" s="367"/>
+      <c r="E3" s="367" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="380"/>
-      <c r="G3" s="380"/>
-      <c r="H3" s="380"/>
-      <c r="I3" s="380"/>
-      <c r="J3" s="380"/>
-      <c r="K3" s="398" t="s">
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="387" t="s">
         <v>20</v>
       </c>
-      <c r="L3" s="398" t="s">
+      <c r="L3" s="387" t="s">
         <v>34</v>
       </c>
-      <c r="M3" s="398" t="s">
+      <c r="M3" s="387" t="s">
         <v>586</v>
       </c>
-      <c r="N3" s="398" t="s">
+      <c r="N3" s="387" t="s">
         <v>23</v>
       </c>
-      <c r="O3" s="398" t="s">
+      <c r="O3" s="387" t="s">
         <v>24</v>
       </c>
-      <c r="P3" s="398" t="s">
+      <c r="P3" s="387" t="s">
         <v>25</v>
       </c>
-      <c r="Q3" s="398" t="s">
+      <c r="Q3" s="387" t="s">
         <v>26</v>
       </c>
-      <c r="R3" s="398" t="s">
+      <c r="R3" s="387" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:18" s="95" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="380"/>
-      <c r="B4" s="398"/>
+      <c r="A4" s="367"/>
+      <c r="B4" s="387"/>
       <c r="C4" s="244" t="s">
         <v>27</v>
       </c>
@@ -16809,14 +16769,14 @@
       <c r="J4" s="164" t="s">
         <v>30</v>
       </c>
-      <c r="K4" s="398"/>
-      <c r="L4" s="398"/>
-      <c r="M4" s="380"/>
-      <c r="N4" s="398"/>
-      <c r="O4" s="398"/>
-      <c r="P4" s="398"/>
-      <c r="Q4" s="398"/>
-      <c r="R4" s="380"/>
+      <c r="K4" s="387"/>
+      <c r="L4" s="387"/>
+      <c r="M4" s="367"/>
+      <c r="N4" s="387"/>
+      <c r="O4" s="387"/>
+      <c r="P4" s="387"/>
+      <c r="Q4" s="387"/>
+      <c r="R4" s="367"/>
     </row>
     <row r="5" spans="1:18" s="3" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -16874,29 +16834,29 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="95" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="95" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="60" t="s">
         <v>584</v>
       </c>
       <c r="B6" s="60"/>
-      <c r="C6" s="400"/>
-      <c r="D6" s="401"/>
-      <c r="E6" s="401"/>
-      <c r="F6" s="401"/>
-      <c r="G6" s="401"/>
-      <c r="H6" s="401"/>
-      <c r="I6" s="401"/>
-      <c r="J6" s="401"/>
-      <c r="K6" s="401"/>
-      <c r="L6" s="401"/>
-      <c r="M6" s="401"/>
-      <c r="N6" s="401"/>
-      <c r="O6" s="401"/>
-      <c r="P6" s="401"/>
-      <c r="Q6" s="401"/>
-      <c r="R6" s="402"/>
-    </row>
-    <row r="7" spans="1:18" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="389"/>
+      <c r="D6" s="390"/>
+      <c r="E6" s="390"/>
+      <c r="F6" s="390"/>
+      <c r="G6" s="390"/>
+      <c r="H6" s="390"/>
+      <c r="I6" s="390"/>
+      <c r="J6" s="390"/>
+      <c r="K6" s="390"/>
+      <c r="L6" s="390"/>
+      <c r="M6" s="390"/>
+      <c r="N6" s="390"/>
+      <c r="O6" s="390"/>
+      <c r="P6" s="390"/>
+      <c r="Q6" s="390"/>
+      <c r="R6" s="391"/>
+    </row>
+    <row r="7" spans="1:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -16920,7 +16880,7 @@
       <c r="Q7" s="54"/>
       <c r="R7" s="55"/>
     </row>
-    <row r="8" spans="1:18" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>2</v>
       </c>
@@ -16944,7 +16904,7 @@
       <c r="Q8" s="54"/>
       <c r="R8" s="55"/>
     </row>
-    <row r="9" spans="1:18" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>3</v>
       </c>
@@ -16968,7 +16928,7 @@
       <c r="Q9" s="54"/>
       <c r="R9" s="55"/>
     </row>
-    <row r="10" spans="1:18" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>4</v>
       </c>
@@ -16991,7 +16951,7 @@
       <c r="P10" s="54"/>
       <c r="Q10" s="54"/>
     </row>
-    <row r="11" spans="1:18" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>5</v>
       </c>
@@ -17015,7 +16975,7 @@
       <c r="Q11" s="54"/>
       <c r="R11" s="96"/>
     </row>
-    <row r="12" spans="1:18" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>6</v>
       </c>
@@ -17039,7 +16999,7 @@
       <c r="Q12" s="54"/>
       <c r="R12" s="74"/>
     </row>
-    <row r="13" spans="1:18" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>7</v>
       </c>
@@ -17063,7 +17023,7 @@
       <c r="Q13" s="54"/>
       <c r="R13" s="74"/>
     </row>
-    <row r="14" spans="1:18" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>8</v>
       </c>
@@ -17087,7 +17047,7 @@
       <c r="Q14" s="54"/>
       <c r="R14" s="262"/>
     </row>
-    <row r="15" spans="1:18" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>9</v>
       </c>
@@ -17203,7 +17163,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="18" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>12</v>
       </c>
@@ -17227,7 +17187,7 @@
       <c r="Q18" s="54"/>
       <c r="R18" s="55"/>
     </row>
-    <row r="19" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>13</v>
       </c>
@@ -17337,7 +17297,7 @@
       </c>
       <c r="R21" s="97"/>
     </row>
-    <row r="22" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>16</v>
       </c>
@@ -17361,7 +17321,7 @@
       <c r="Q22" s="54"/>
       <c r="R22" s="269"/>
     </row>
-    <row r="23" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>17</v>
       </c>
@@ -17385,7 +17345,7 @@
       <c r="Q23" s="54"/>
       <c r="R23" s="65"/>
     </row>
-    <row r="24" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>18</v>
       </c>
@@ -17409,7 +17369,7 @@
       <c r="Q24" s="54"/>
       <c r="R24" s="65"/>
     </row>
-    <row r="25" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>19</v>
       </c>
@@ -17433,7 +17393,7 @@
       <c r="Q25" s="54"/>
       <c r="R25" s="65"/>
     </row>
-    <row r="26" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>20</v>
       </c>
@@ -17457,7 +17417,7 @@
       <c r="Q26" s="54"/>
       <c r="R26" s="65"/>
     </row>
-    <row r="27" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>21</v>
       </c>
@@ -17481,7 +17441,7 @@
       <c r="Q27" s="54"/>
       <c r="R27" s="65"/>
     </row>
-    <row r="28" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>22</v>
       </c>
@@ -17505,7 +17465,7 @@
       <c r="Q28" s="54"/>
       <c r="R28" s="76"/>
     </row>
-    <row r="29" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>23</v>
       </c>
@@ -17529,7 +17489,7 @@
       <c r="Q29" s="54"/>
       <c r="R29" s="76"/>
     </row>
-    <row r="30" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>24</v>
       </c>
@@ -17553,7 +17513,7 @@
       <c r="Q30" s="54"/>
       <c r="R30" s="55"/>
     </row>
-    <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>25</v>
       </c>
@@ -17577,7 +17537,7 @@
       <c r="Q31" s="54"/>
       <c r="R31" s="65"/>
     </row>
-    <row r="32" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>26</v>
       </c>
@@ -17601,7 +17561,7 @@
       <c r="Q32" s="54"/>
       <c r="R32" s="55"/>
     </row>
-    <row r="33" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>27</v>
       </c>
@@ -17625,7 +17585,7 @@
       <c r="Q33" s="54"/>
       <c r="R33" s="55"/>
     </row>
-    <row r="34" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>28</v>
       </c>
@@ -17649,7 +17609,7 @@
       <c r="Q34" s="54"/>
       <c r="R34" s="55"/>
     </row>
-    <row r="35" spans="1:18" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>29</v>
       </c>
@@ -17673,7 +17633,7 @@
       <c r="Q35" s="54"/>
       <c r="R35" s="65"/>
     </row>
-    <row r="36" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>30</v>
       </c>
@@ -17697,7 +17657,7 @@
       <c r="Q36" s="54"/>
       <c r="R36" s="55"/>
     </row>
-    <row r="37" spans="1:18" ht="36.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>31</v>
       </c>
@@ -17721,7 +17681,7 @@
       <c r="Q37" s="54"/>
       <c r="R37" s="65"/>
     </row>
-    <row r="38" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>32</v>
       </c>
@@ -17745,7 +17705,7 @@
       <c r="Q38" s="54"/>
       <c r="R38" s="97"/>
     </row>
-    <row r="39" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>33</v>
       </c>
@@ -17769,7 +17729,7 @@
       <c r="Q39" s="54"/>
       <c r="R39" s="76"/>
     </row>
-    <row r="40" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>34</v>
       </c>
@@ -17793,7 +17753,7 @@
       <c r="Q40" s="54"/>
       <c r="R40" s="55"/>
     </row>
-    <row r="41" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>35</v>
       </c>
@@ -17817,7 +17777,7 @@
       <c r="Q41" s="54"/>
       <c r="R41" s="55"/>
     </row>
-    <row r="42" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>36</v>
       </c>
@@ -17841,7 +17801,7 @@
       <c r="Q42" s="54"/>
       <c r="R42" s="55"/>
     </row>
-    <row r="43" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>37</v>
       </c>
@@ -17865,7 +17825,7 @@
       <c r="Q43" s="54"/>
       <c r="R43" s="55"/>
     </row>
-    <row r="44" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>38</v>
       </c>
@@ -17889,7 +17849,7 @@
       <c r="Q44" s="54"/>
       <c r="R44" s="55"/>
     </row>
-    <row r="45" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>39</v>
       </c>
@@ -17913,7 +17873,7 @@
       <c r="Q45" s="54"/>
       <c r="R45" s="76"/>
     </row>
-    <row r="46" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>40</v>
       </c>
@@ -17937,7 +17897,7 @@
       <c r="Q46" s="54"/>
       <c r="R46" s="55"/>
     </row>
-    <row r="47" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>41</v>
       </c>
@@ -17961,7 +17921,7 @@
       <c r="Q47" s="54"/>
       <c r="R47" s="55"/>
     </row>
-    <row r="48" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>42</v>
       </c>
@@ -17985,7 +17945,7 @@
       <c r="Q48" s="54"/>
       <c r="R48" s="55"/>
     </row>
-    <row r="49" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>43</v>
       </c>
@@ -18009,7 +17969,7 @@
       <c r="Q49" s="54"/>
       <c r="R49" s="55"/>
     </row>
-    <row r="50" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>44</v>
       </c>
@@ -18033,7 +17993,7 @@
       <c r="Q50" s="54"/>
       <c r="R50" s="55"/>
     </row>
-    <row r="51" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>45</v>
       </c>
@@ -18057,7 +18017,7 @@
       <c r="Q51" s="54"/>
       <c r="R51" s="55"/>
     </row>
-    <row r="52" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>46</v>
       </c>
@@ -18081,7 +18041,7 @@
       <c r="Q52" s="54"/>
       <c r="R52" s="55"/>
     </row>
-    <row r="53" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>47</v>
       </c>
@@ -18105,7 +18065,7 @@
       <c r="Q53" s="54"/>
       <c r="R53" s="55"/>
     </row>
-    <row r="54" spans="1:18" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>48</v>
       </c>
@@ -18129,7 +18089,7 @@
       <c r="Q54" s="54"/>
       <c r="R54" s="65"/>
     </row>
-    <row r="55" spans="1:18" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>49</v>
       </c>
@@ -18153,7 +18113,7 @@
       <c r="Q55" s="54"/>
       <c r="R55" s="77"/>
     </row>
-    <row r="56" spans="1:18" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>50</v>
       </c>
@@ -18177,7 +18137,7 @@
       <c r="Q56" s="54"/>
       <c r="R56" s="77"/>
     </row>
-    <row r="57" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>51</v>
       </c>
@@ -18201,7 +18161,7 @@
       <c r="Q57" s="54"/>
       <c r="R57" s="65"/>
     </row>
-    <row r="58" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>52</v>
       </c>
@@ -18225,7 +18185,7 @@
       <c r="Q58" s="54"/>
       <c r="R58" s="65"/>
     </row>
-    <row r="59" spans="1:18" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>53</v>
       </c>
@@ -18249,7 +18209,7 @@
       <c r="Q59" s="54"/>
       <c r="R59" s="97"/>
     </row>
-    <row r="60" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>54</v>
       </c>
@@ -18273,7 +18233,7 @@
       <c r="Q60" s="54"/>
       <c r="R60" s="55"/>
     </row>
-    <row r="61" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>55</v>
       </c>
@@ -18297,7 +18257,7 @@
       <c r="Q61" s="54"/>
       <c r="R61" s="55"/>
     </row>
-    <row r="62" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>56</v>
       </c>
@@ -18321,7 +18281,7 @@
       <c r="Q62" s="54"/>
       <c r="R62" s="97"/>
     </row>
-    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>57</v>
       </c>
@@ -18345,7 +18305,7 @@
       <c r="Q63" s="54"/>
       <c r="R63" s="55"/>
     </row>
-    <row r="64" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>58</v>
       </c>
@@ -18369,7 +18329,7 @@
       <c r="Q64" s="54"/>
       <c r="R64" s="55"/>
     </row>
-    <row r="65" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>59</v>
       </c>
@@ -18393,7 +18353,7 @@
       <c r="Q65" s="54"/>
       <c r="R65" s="76"/>
     </row>
-    <row r="66" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>60</v>
       </c>
@@ -18417,7 +18377,7 @@
       <c r="Q66" s="54"/>
       <c r="R66" s="55"/>
     </row>
-    <row r="67" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>61</v>
       </c>
@@ -18441,7 +18401,7 @@
       <c r="Q67" s="54"/>
       <c r="R67" s="55"/>
     </row>
-    <row r="68" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>62</v>
       </c>
@@ -18465,7 +18425,7 @@
       <c r="Q68" s="54"/>
       <c r="R68" s="55"/>
     </row>
-    <row r="69" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>63</v>
       </c>
@@ -18489,7 +18449,7 @@
       <c r="Q69" s="54"/>
       <c r="R69" s="55"/>
     </row>
-    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>64</v>
       </c>
@@ -18513,7 +18473,7 @@
       <c r="Q70" s="54"/>
       <c r="R70" s="55"/>
     </row>
-    <row r="71" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>65</v>
       </c>
@@ -18537,7 +18497,7 @@
       <c r="Q71" s="54"/>
       <c r="R71" s="55"/>
     </row>
-    <row r="72" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>66</v>
       </c>
@@ -18561,7 +18521,7 @@
       <c r="Q72" s="54"/>
       <c r="R72" s="55"/>
     </row>
-    <row r="73" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>67</v>
       </c>
@@ -18627,7 +18587,7 @@
       </c>
       <c r="R74" s="76"/>
     </row>
-    <row r="75" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>69</v>
       </c>
@@ -18651,7 +18611,7 @@
       <c r="Q75" s="54"/>
       <c r="R75" s="262"/>
     </row>
-    <row r="76" spans="1:18" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>70</v>
       </c>
@@ -18675,7 +18635,7 @@
       <c r="Q76" s="54"/>
       <c r="R76" s="97"/>
     </row>
-    <row r="77" spans="1:18" ht="27.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>71</v>
       </c>
@@ -18741,7 +18701,7 @@
       </c>
       <c r="R78" s="65"/>
     </row>
-    <row r="79" spans="1:18" ht="27.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>73</v>
       </c>
@@ -18765,7 +18725,7 @@
       <c r="Q79" s="54"/>
       <c r="R79" s="65"/>
     </row>
-    <row r="80" spans="1:18" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>74</v>
       </c>
@@ -18789,7 +18749,7 @@
       <c r="Q80" s="54"/>
       <c r="R80" s="65"/>
     </row>
-    <row r="81" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>75</v>
       </c>
@@ -18813,7 +18773,7 @@
       <c r="Q81" s="54"/>
       <c r="R81" s="55"/>
     </row>
-    <row r="82" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>76</v>
       </c>
@@ -18837,7 +18797,7 @@
       <c r="Q82" s="54"/>
       <c r="R82" s="55"/>
     </row>
-    <row r="83" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>77</v>
       </c>
@@ -18861,7 +18821,7 @@
       <c r="Q83" s="54"/>
       <c r="R83" s="55"/>
     </row>
-    <row r="84" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:18" ht="30" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>78</v>
       </c>
@@ -18885,7 +18845,7 @@
       <c r="Q84" s="54"/>
       <c r="R84" s="55"/>
     </row>
-    <row r="85" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>79</v>
       </c>
@@ -18909,7 +18869,7 @@
       <c r="Q85" s="54"/>
       <c r="R85" s="55"/>
     </row>
-    <row r="86" spans="1:18" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>80</v>
       </c>
@@ -18933,7 +18893,7 @@
       <c r="Q86" s="54"/>
       <c r="R86" s="65"/>
     </row>
-    <row r="87" spans="1:18" ht="39.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>81</v>
       </c>
@@ -18957,7 +18917,7 @@
       <c r="Q87" s="54"/>
       <c r="R87" s="65"/>
     </row>
-    <row r="88" spans="1:18" ht="35.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:18" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>82</v>
       </c>
@@ -18981,7 +18941,7 @@
       <c r="Q88" s="54"/>
       <c r="R88" s="65"/>
     </row>
-    <row r="89" spans="1:18" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>83</v>
       </c>
@@ -19005,7 +18965,7 @@
       <c r="Q89" s="54"/>
       <c r="R89" s="76"/>
     </row>
-    <row r="90" spans="1:18" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>84</v>
       </c>
@@ -19029,7 +18989,7 @@
       <c r="Q90" s="54"/>
       <c r="R90" s="81"/>
     </row>
-    <row r="91" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>85</v>
       </c>
@@ -19053,7 +19013,7 @@
       <c r="Q91" s="54"/>
       <c r="R91" s="55"/>
     </row>
-    <row r="92" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>86</v>
       </c>
@@ -19077,7 +19037,7 @@
       <c r="Q92" s="54"/>
       <c r="R92" s="55"/>
     </row>
-    <row r="93" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>87</v>
       </c>
@@ -19101,7 +19061,7 @@
       <c r="Q93" s="54"/>
       <c r="R93" s="65"/>
     </row>
-    <row r="94" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>88</v>
       </c>
@@ -19125,7 +19085,7 @@
       <c r="Q94" s="54"/>
       <c r="R94" s="55"/>
     </row>
-    <row r="95" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>89</v>
       </c>
@@ -19149,7 +19109,7 @@
       <c r="Q95" s="54"/>
       <c r="R95" s="55"/>
     </row>
-    <row r="96" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>90</v>
       </c>
@@ -19173,7 +19133,7 @@
       <c r="Q96" s="54"/>
       <c r="R96" s="55"/>
     </row>
-    <row r="97" spans="1:18" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>91</v>
       </c>
@@ -19197,7 +19157,7 @@
       <c r="Q97" s="54"/>
       <c r="R97" s="48"/>
     </row>
-    <row r="98" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>92</v>
       </c>
@@ -19221,7 +19181,7 @@
       <c r="Q98" s="54"/>
       <c r="R98" s="55"/>
     </row>
-    <row r="99" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>93</v>
       </c>
@@ -19245,7 +19205,7 @@
       <c r="Q99" s="54"/>
       <c r="R99" s="55"/>
     </row>
-    <row r="100" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>94</v>
       </c>
@@ -19269,7 +19229,7 @@
       <c r="Q100" s="54"/>
       <c r="R100" s="97"/>
     </row>
-    <row r="101" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>95</v>
       </c>
@@ -19293,7 +19253,7 @@
       <c r="Q101" s="54"/>
       <c r="R101" s="55"/>
     </row>
-    <row r="102" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>96</v>
       </c>
@@ -19359,7 +19319,7 @@
       </c>
       <c r="R103" s="97"/>
     </row>
-    <row r="104" spans="1:18" ht="27.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>98</v>
       </c>
@@ -19425,7 +19385,7 @@
       </c>
       <c r="R105" s="96"/>
     </row>
-    <row r="106" spans="1:18" ht="39.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>100</v>
       </c>
@@ -19449,7 +19409,7 @@
       <c r="Q106" s="54"/>
       <c r="R106" s="81"/>
     </row>
-    <row r="107" spans="1:18" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>101</v>
       </c>
@@ -19473,7 +19433,7 @@
       <c r="Q107" s="54"/>
       <c r="R107" s="48"/>
     </row>
-    <row r="108" spans="1:18" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:18" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>102</v>
       </c>
@@ -19497,7 +19457,7 @@
       <c r="Q108" s="54"/>
       <c r="R108" s="65"/>
     </row>
-    <row r="109" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>103</v>
       </c>
@@ -19521,7 +19481,7 @@
       <c r="Q109" s="54"/>
       <c r="R109" s="55"/>
     </row>
-    <row r="110" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>104</v>
       </c>
@@ -19545,7 +19505,7 @@
       <c r="Q110" s="54"/>
       <c r="R110" s="55"/>
     </row>
-    <row r="111" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>105</v>
       </c>
@@ -19569,7 +19529,7 @@
       <c r="Q111" s="54"/>
       <c r="R111" s="55"/>
     </row>
-    <row r="112" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>106</v>
       </c>
@@ -19593,7 +19553,7 @@
       <c r="Q112" s="54"/>
       <c r="R112" s="55"/>
     </row>
-    <row r="113" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>107</v>
       </c>
@@ -19617,7 +19577,7 @@
       <c r="Q113" s="54"/>
       <c r="R113" s="55"/>
     </row>
-    <row r="114" spans="1:18" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>108</v>
       </c>
@@ -19641,7 +19601,7 @@
       <c r="Q114" s="54"/>
       <c r="R114" s="76"/>
     </row>
-    <row r="115" spans="1:18" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>109</v>
       </c>
@@ -19708,7 +19668,7 @@
       </c>
       <c r="R116" s="65"/>
     </row>
-    <row r="117" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>111</v>
       </c>
@@ -19732,7 +19692,7 @@
       <c r="Q117" s="54"/>
       <c r="R117" s="97"/>
     </row>
-    <row r="118" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>112</v>
       </c>
@@ -19756,7 +19716,7 @@
       <c r="Q118" s="54"/>
       <c r="R118" s="96"/>
     </row>
-    <row r="119" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>113</v>
       </c>
@@ -19780,7 +19740,7 @@
       <c r="Q119" s="54"/>
       <c r="R119" s="262"/>
     </row>
-    <row r="120" spans="1:18" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>114</v>
       </c>
@@ -19804,7 +19764,7 @@
       <c r="Q120" s="54"/>
       <c r="R120" s="74"/>
     </row>
-    <row r="121" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>115</v>
       </c>
@@ -19828,7 +19788,7 @@
       <c r="Q121" s="54"/>
       <c r="R121" s="262"/>
     </row>
-    <row r="122" spans="1:18" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>116</v>
       </c>
@@ -19852,7 +19812,7 @@
       <c r="Q122" s="54"/>
       <c r="R122" s="74"/>
     </row>
-    <row r="123" spans="1:18" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>117</v>
       </c>
@@ -19876,7 +19836,7 @@
       <c r="Q123" s="54"/>
       <c r="R123" s="74"/>
     </row>
-    <row r="124" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>118</v>
       </c>
@@ -19900,7 +19860,7 @@
       <c r="Q124" s="54"/>
       <c r="R124" s="76"/>
     </row>
-    <row r="125" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>119</v>
       </c>
@@ -19924,7 +19884,7 @@
       <c r="Q125" s="54"/>
       <c r="R125" s="55"/>
     </row>
-    <row r="126" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>120</v>
       </c>
@@ -19948,7 +19908,7 @@
       <c r="Q126" s="54"/>
       <c r="R126" s="96"/>
     </row>
-    <row r="127" spans="1:18" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>121</v>
       </c>
@@ -19972,7 +19932,7 @@
       <c r="Q127" s="54"/>
       <c r="R127" s="81"/>
     </row>
-    <row r="128" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>122</v>
       </c>
@@ -19996,7 +19956,7 @@
       <c r="Q128" s="54"/>
       <c r="R128" s="55"/>
     </row>
-    <row r="129" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>123</v>
       </c>
@@ -20020,7 +19980,7 @@
       <c r="Q129" s="54"/>
       <c r="R129" s="55"/>
     </row>
-    <row r="130" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:18" ht="30" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>124</v>
       </c>
@@ -20044,7 +20004,7 @@
       <c r="Q130" s="54"/>
       <c r="R130" s="76"/>
     </row>
-    <row r="131" spans="1:18" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>125</v>
       </c>
@@ -20068,7 +20028,7 @@
       <c r="Q131" s="54"/>
       <c r="R131" s="75"/>
     </row>
-    <row r="132" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>126</v>
       </c>
@@ -20092,7 +20052,7 @@
       <c r="Q132" s="54"/>
       <c r="R132" s="55"/>
     </row>
-    <row r="133" spans="1:18" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A133" s="71" t="s">
         <v>1071</v>
       </c>
@@ -20114,7 +20074,7 @@
       <c r="Q133" s="166"/>
       <c r="R133" s="167"/>
     </row>
-    <row r="134" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>127</v>
       </c>
@@ -20138,7 +20098,7 @@
       <c r="Q134" s="54"/>
       <c r="R134" s="96"/>
     </row>
-    <row r="135" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>128</v>
       </c>
@@ -20162,7 +20122,7 @@
       <c r="Q135" s="54"/>
       <c r="R135" s="55"/>
     </row>
-    <row r="136" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>129</v>
       </c>
@@ -20186,7 +20146,7 @@
       <c r="Q136" s="54"/>
       <c r="R136" s="55"/>
     </row>
-    <row r="137" spans="1:18" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>130</v>
       </c>
@@ -20210,7 +20170,7 @@
       <c r="Q137" s="54"/>
       <c r="R137" s="81"/>
     </row>
-    <row r="138" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>131</v>
       </c>
@@ -20234,7 +20194,7 @@
       <c r="Q138" s="54"/>
       <c r="R138" s="65"/>
     </row>
-    <row r="139" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>132</v>
       </c>
@@ -20258,7 +20218,7 @@
       <c r="Q139" s="54"/>
       <c r="R139" s="55"/>
     </row>
-    <row r="140" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>133</v>
       </c>
@@ -20282,7 +20242,7 @@
       <c r="Q140" s="54"/>
       <c r="R140" s="65"/>
     </row>
-    <row r="141" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>134</v>
       </c>
@@ -20306,7 +20266,7 @@
       <c r="Q141" s="54"/>
       <c r="R141" s="55"/>
     </row>
-    <row r="142" spans="1:18" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>135</v>
       </c>
@@ -20330,7 +20290,7 @@
       <c r="Q142" s="54"/>
       <c r="R142" s="65"/>
     </row>
-    <row r="143" spans="1:18" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>136</v>
       </c>
@@ -20354,7 +20314,7 @@
       <c r="Q143" s="54"/>
       <c r="R143" s="78"/>
     </row>
-    <row r="144" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>137</v>
       </c>
@@ -20378,7 +20338,7 @@
       <c r="Q144" s="54"/>
       <c r="R144" s="65"/>
     </row>
-    <row r="145" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>138</v>
       </c>
@@ -20402,7 +20362,7 @@
       <c r="Q145" s="54"/>
       <c r="R145" s="65"/>
     </row>
-    <row r="146" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>139</v>
       </c>
@@ -20426,7 +20386,7 @@
       <c r="Q146" s="54"/>
       <c r="R146" s="55"/>
     </row>
-    <row r="147" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>140</v>
       </c>
@@ -20450,7 +20410,7 @@
       <c r="Q147" s="54"/>
       <c r="R147" s="55"/>
     </row>
-    <row r="148" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>141</v>
       </c>
@@ -20474,7 +20434,7 @@
       <c r="Q148" s="54"/>
       <c r="R148" s="55"/>
     </row>
-    <row r="149" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>142</v>
       </c>
@@ -20498,7 +20458,7 @@
       <c r="Q149" s="54"/>
       <c r="R149" s="65"/>
     </row>
-    <row r="150" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>143</v>
       </c>
@@ -20522,7 +20482,7 @@
       <c r="Q150" s="54"/>
       <c r="R150" s="65"/>
     </row>
-    <row r="151" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>144</v>
       </c>
@@ -20546,7 +20506,7 @@
       <c r="Q151" s="54"/>
       <c r="R151" s="76"/>
     </row>
-    <row r="152" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>145</v>
       </c>
@@ -20614,7 +20574,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="154" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>147</v>
       </c>
@@ -20638,7 +20598,7 @@
       <c r="Q154" s="54"/>
       <c r="R154" s="55"/>
     </row>
-    <row r="155" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>148</v>
       </c>
@@ -20662,7 +20622,7 @@
       <c r="Q155" s="54"/>
       <c r="R155" s="55"/>
     </row>
-    <row r="156" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>149</v>
       </c>
@@ -20686,7 +20646,7 @@
       <c r="Q156" s="54"/>
       <c r="R156" s="55"/>
     </row>
-    <row r="157" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>150</v>
       </c>
@@ -20710,7 +20670,7 @@
       <c r="Q157" s="54"/>
       <c r="R157" s="55"/>
     </row>
-    <row r="158" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>151</v>
       </c>
@@ -20734,7 +20694,7 @@
       <c r="Q158" s="54"/>
       <c r="R158" s="55"/>
     </row>
-    <row r="159" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>152</v>
       </c>
@@ -20758,7 +20718,7 @@
       <c r="Q159" s="54"/>
       <c r="R159" s="55"/>
     </row>
-    <row r="160" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>153</v>
       </c>
@@ -20782,7 +20742,7 @@
       <c r="Q160" s="54"/>
       <c r="R160" s="55"/>
     </row>
-    <row r="161" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>154</v>
       </c>
@@ -20806,7 +20766,7 @@
       <c r="Q161" s="54"/>
       <c r="R161" s="76"/>
     </row>
-    <row r="162" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>155</v>
       </c>
@@ -20830,7 +20790,7 @@
       <c r="Q162" s="54"/>
       <c r="R162" s="76"/>
     </row>
-    <row r="163" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>156</v>
       </c>
@@ -20854,7 +20814,7 @@
       <c r="Q163" s="54"/>
       <c r="R163" s="55"/>
     </row>
-    <row r="164" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>157</v>
       </c>
@@ -20878,7 +20838,7 @@
       <c r="Q164" s="54"/>
       <c r="R164" s="55"/>
     </row>
-    <row r="165" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>158</v>
       </c>
@@ -20902,7 +20862,7 @@
       <c r="Q165" s="54"/>
       <c r="R165" s="55"/>
     </row>
-    <row r="166" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>159</v>
       </c>
@@ -20926,7 +20886,7 @@
       <c r="Q166" s="54"/>
       <c r="R166" s="55"/>
     </row>
-    <row r="167" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>160</v>
       </c>
@@ -20950,7 +20910,7 @@
       <c r="Q167" s="54"/>
       <c r="R167" s="55"/>
     </row>
-    <row r="168" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>161</v>
       </c>
@@ -20974,7 +20934,7 @@
       <c r="Q168" s="54"/>
       <c r="R168" s="55"/>
     </row>
-    <row r="169" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>162</v>
       </c>
@@ -20998,7 +20958,7 @@
       <c r="Q169" s="54"/>
       <c r="R169" s="55"/>
     </row>
-    <row r="170" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>163</v>
       </c>
@@ -21022,7 +20982,7 @@
       <c r="Q170" s="54"/>
       <c r="R170" s="55"/>
     </row>
-    <row r="171" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>164</v>
       </c>
@@ -21046,7 +21006,7 @@
       <c r="Q171" s="54"/>
       <c r="R171" s="55"/>
     </row>
-    <row r="172" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>165</v>
       </c>
@@ -21070,7 +21030,7 @@
       <c r="Q172" s="54"/>
       <c r="R172" s="65"/>
     </row>
-    <row r="173" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>166</v>
       </c>
@@ -21094,7 +21054,7 @@
       <c r="Q173" s="54"/>
       <c r="R173" s="65"/>
     </row>
-    <row r="174" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>167</v>
       </c>
@@ -21118,7 +21078,7 @@
       <c r="Q174" s="54"/>
       <c r="R174" s="55"/>
     </row>
-    <row r="175" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>168</v>
       </c>
@@ -21142,7 +21102,7 @@
       <c r="Q175" s="54"/>
       <c r="R175" s="76"/>
     </row>
-    <row r="176" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>169</v>
       </c>
@@ -21166,7 +21126,7 @@
       <c r="Q176" s="54"/>
       <c r="R176" s="65"/>
     </row>
-    <row r="177" spans="1:18" s="83" customFormat="1" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:18" s="83" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>170</v>
       </c>
@@ -21190,7 +21150,7 @@
       <c r="Q177" s="54"/>
       <c r="R177" s="77"/>
     </row>
-    <row r="178" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>171</v>
       </c>
@@ -21214,7 +21174,7 @@
       <c r="Q178" s="54"/>
       <c r="R178" s="55"/>
     </row>
-    <row r="179" spans="1:18" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>172</v>
       </c>
@@ -21238,7 +21198,7 @@
       <c r="Q179" s="54"/>
       <c r="R179" s="48"/>
     </row>
-    <row r="180" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>173</v>
       </c>
@@ -21262,7 +21222,7 @@
       <c r="Q180" s="54"/>
       <c r="R180" s="55"/>
     </row>
-    <row r="181" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>174</v>
       </c>
@@ -21286,7 +21246,7 @@
       <c r="Q181" s="54"/>
       <c r="R181" s="55"/>
     </row>
-    <row r="182" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>175</v>
       </c>
@@ -21310,7 +21270,7 @@
       <c r="Q182" s="54"/>
       <c r="R182" s="55"/>
     </row>
-    <row r="183" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>176</v>
       </c>
@@ -21334,7 +21294,7 @@
       <c r="Q183" s="54"/>
       <c r="R183" s="55"/>
     </row>
-    <row r="184" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>177</v>
       </c>
@@ -21358,7 +21318,7 @@
       <c r="Q184" s="54"/>
       <c r="R184" s="55"/>
     </row>
-    <row r="185" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>178</v>
       </c>
@@ -21382,7 +21342,7 @@
       <c r="Q185" s="54"/>
       <c r="R185" s="55"/>
     </row>
-    <row r="186" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>179</v>
       </c>
@@ -21406,7 +21366,7 @@
       <c r="Q186" s="54"/>
       <c r="R186" s="55"/>
     </row>
-    <row r="187" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>180</v>
       </c>
@@ -21430,7 +21390,7 @@
       <c r="Q187" s="54"/>
       <c r="R187" s="55"/>
     </row>
-    <row r="188" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>181</v>
       </c>
@@ -21454,7 +21414,7 @@
       <c r="Q188" s="54"/>
       <c r="R188" s="55"/>
     </row>
-    <row r="189" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>182</v>
       </c>
@@ -21478,7 +21438,7 @@
       <c r="Q189" s="54"/>
       <c r="R189" s="55"/>
     </row>
-    <row r="190" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>183</v>
       </c>
@@ -21502,7 +21462,7 @@
       <c r="Q190" s="54"/>
       <c r="R190" s="55"/>
     </row>
-    <row r="191" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>184</v>
       </c>
@@ -21526,7 +21486,7 @@
       <c r="Q191" s="54"/>
       <c r="R191" s="55"/>
     </row>
-    <row r="192" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>185</v>
       </c>
@@ -21550,7 +21510,7 @@
       <c r="Q192" s="54"/>
       <c r="R192" s="55"/>
     </row>
-    <row r="193" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>186</v>
       </c>
@@ -21574,7 +21534,7 @@
       <c r="Q193" s="54"/>
       <c r="R193" s="55"/>
     </row>
-    <row r="194" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>187</v>
       </c>
@@ -21598,7 +21558,7 @@
       <c r="Q194" s="54"/>
       <c r="R194" s="55"/>
     </row>
-    <row r="195" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:18" ht="30" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>188</v>
       </c>
@@ -21622,7 +21582,7 @@
       <c r="Q195" s="54"/>
       <c r="R195" s="55"/>
     </row>
-    <row r="196" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>189</v>
       </c>
@@ -21646,7 +21606,7 @@
       <c r="Q196" s="54"/>
       <c r="R196" s="55"/>
     </row>
-    <row r="197" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>190</v>
       </c>
@@ -21670,7 +21630,7 @@
       <c r="Q197" s="54"/>
       <c r="R197" s="55"/>
     </row>
-    <row r="198" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>191</v>
       </c>
@@ -21694,7 +21654,7 @@
       <c r="Q198" s="54"/>
       <c r="R198" s="55"/>
     </row>
-    <row r="199" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>192</v>
       </c>
@@ -21718,7 +21678,7 @@
       <c r="Q199" s="54"/>
       <c r="R199" s="55"/>
     </row>
-    <row r="200" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>193</v>
       </c>
@@ -21742,7 +21702,7 @@
       <c r="Q200" s="54"/>
       <c r="R200" s="55"/>
     </row>
-    <row r="201" spans="1:18" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>194</v>
       </c>
@@ -21766,7 +21726,7 @@
       <c r="Q201" s="54"/>
       <c r="R201" s="61"/>
     </row>
-    <row r="202" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>195</v>
       </c>
@@ -21790,7 +21750,7 @@
       <c r="Q202" s="54"/>
       <c r="R202" s="55"/>
     </row>
-    <row r="203" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>196</v>
       </c>
@@ -21814,7 +21774,7 @@
       <c r="Q203" s="54"/>
       <c r="R203" s="55"/>
     </row>
-    <row r="204" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>197</v>
       </c>
@@ -21838,7 +21798,7 @@
       <c r="Q204" s="54"/>
       <c r="R204" s="76"/>
     </row>
-    <row r="205" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>198</v>
       </c>
@@ -21862,7 +21822,7 @@
       <c r="Q205" s="54"/>
       <c r="R205" s="269"/>
     </row>
-    <row r="206" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>199</v>
       </c>
@@ -21886,7 +21846,7 @@
       <c r="Q206" s="54"/>
       <c r="R206" s="55"/>
     </row>
-    <row r="207" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>200</v>
       </c>
@@ -21910,7 +21870,7 @@
       <c r="Q207" s="54"/>
       <c r="R207" s="55"/>
     </row>
-    <row r="208" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>201</v>
       </c>
@@ -21934,7 +21894,7 @@
       <c r="Q208" s="54"/>
       <c r="R208" s="61"/>
     </row>
-    <row r="209" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>202</v>
       </c>
@@ -21958,7 +21918,7 @@
       <c r="Q209" s="54"/>
       <c r="R209" s="56"/>
     </row>
-    <row r="210" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A210" s="67">
         <v>203</v>
       </c>
@@ -21982,7 +21942,7 @@
       <c r="Q210" s="135"/>
       <c r="R210" s="105"/>
     </row>
-    <row r="211" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A211" s="1"/>
       <c r="B211" s="73" t="s">
         <v>967</v>
@@ -22004,7 +21964,7 @@
       <c r="Q211" s="73"/>
       <c r="R211" s="73"/>
     </row>
-    <row r="212" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>205</v>
       </c>
@@ -22028,7 +21988,7 @@
       <c r="Q212" s="54"/>
       <c r="R212" s="61"/>
     </row>
-    <row r="213" spans="1:18" s="241" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:18" s="241" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>206</v>
       </c>
@@ -22052,7 +22012,7 @@
       <c r="Q213" s="54"/>
       <c r="R213" s="56"/>
     </row>
-    <row r="214" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>207</v>
       </c>
@@ -22076,7 +22036,7 @@
       <c r="Q214" s="54"/>
       <c r="R214" s="61"/>
     </row>
-    <row r="215" spans="1:18" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>208</v>
       </c>
@@ -22100,7 +22060,7 @@
       <c r="Q215" s="54"/>
       <c r="R215" s="61"/>
     </row>
-    <row r="216" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>209</v>
       </c>
@@ -22124,7 +22084,7 @@
       <c r="Q216" s="54"/>
       <c r="R216" s="87"/>
     </row>
-    <row r="217" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>210</v>
       </c>
@@ -22148,7 +22108,7 @@
       <c r="Q217" s="54"/>
       <c r="R217" s="130"/>
     </row>
-    <row r="218" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>211</v>
       </c>
@@ -22172,7 +22132,7 @@
       <c r="Q218" s="54"/>
       <c r="R218" s="73"/>
     </row>
-    <row r="219" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>212</v>
       </c>
@@ -22196,7 +22156,7 @@
       <c r="Q219" s="54"/>
       <c r="R219" s="270"/>
     </row>
-    <row r="220" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>213</v>
       </c>
@@ -22220,7 +22180,7 @@
       <c r="Q220" s="54"/>
       <c r="R220" s="61"/>
     </row>
-    <row r="221" spans="1:18" ht="37.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:18" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>214</v>
       </c>
@@ -22459,18 +22419,6 @@
       <c r="K1048576" s="129"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:R226" xr:uid="{00000000-0009-0000-0000-000005000000}">
-    <filterColumn colId="2" showButton="0">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="4" showButton="0"/>
-    <filterColumn colId="5" showButton="0"/>
-    <filterColumn colId="6" showButton="0"/>
-    <filterColumn colId="7" showButton="0"/>
-    <filterColumn colId="8" showButton="0"/>
-  </autoFilter>
   <mergeCells count="14">
     <mergeCell ref="C6:R6"/>
     <mergeCell ref="A2:R2"/>
@@ -22501,7 +22449,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor rgb="FF147216"/>
   </sheetPr>
   <dimension ref="A1:R172"/>
@@ -22533,24 +22481,24 @@
       </c>
     </row>
     <row r="2" spans="1:16" s="138" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="399" t="s">
+      <c r="A2" s="388" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="399"/>
-      <c r="C2" s="399"/>
-      <c r="D2" s="399"/>
-      <c r="E2" s="399"/>
-      <c r="F2" s="399"/>
-      <c r="G2" s="399"/>
-      <c r="H2" s="399"/>
-      <c r="I2" s="399"/>
-      <c r="J2" s="399"/>
-      <c r="K2" s="399"/>
-      <c r="L2" s="399"/>
-      <c r="M2" s="399"/>
-      <c r="N2" s="399"/>
-      <c r="O2" s="399"/>
-      <c r="P2" s="399"/>
+      <c r="B2" s="388"/>
+      <c r="C2" s="388"/>
+      <c r="D2" s="388"/>
+      <c r="E2" s="388"/>
+      <c r="F2" s="388"/>
+      <c r="G2" s="388"/>
+      <c r="H2" s="388"/>
+      <c r="I2" s="388"/>
+      <c r="J2" s="388"/>
+      <c r="K2" s="388"/>
+      <c r="L2" s="388"/>
+      <c r="M2" s="388"/>
+      <c r="N2" s="388"/>
+      <c r="O2" s="388"/>
+      <c r="P2" s="388"/>
     </row>
     <row r="3" spans="1:16" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="107" t="s">
@@ -22670,7 +22618,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="149">
         <v>1</v>
       </c>
@@ -22692,7 +22640,7 @@
       <c r="O6" s="150"/>
       <c r="P6" s="194"/>
     </row>
-    <row r="7" spans="1:16" s="34" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="153"/>
       <c r="B7" s="154" t="s">
         <v>1</v>
@@ -22714,7 +22662,7 @@
       <c r="O7" s="54"/>
       <c r="P7" s="64"/>
     </row>
-    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="153"/>
       <c r="B8" s="155" t="s">
         <v>2</v>
@@ -22736,7 +22684,7 @@
       <c r="O8" s="54"/>
       <c r="P8" s="64"/>
     </row>
-    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="153"/>
       <c r="B9" s="10" t="s">
         <v>3</v>
@@ -22758,7 +22706,7 @@
       <c r="O9" s="54"/>
       <c r="P9" s="70"/>
     </row>
-    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="153"/>
       <c r="B10" s="155" t="s">
         <v>4</v>
@@ -22780,7 +22728,7 @@
       <c r="O10" s="54"/>
       <c r="P10" s="70"/>
     </row>
-    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="157"/>
       <c r="B11" s="155" t="s">
         <v>5</v>
@@ -22802,7 +22750,7 @@
       <c r="O11" s="54"/>
       <c r="P11" s="70"/>
     </row>
-    <row r="12" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="149">
         <v>2</v>
       </c>
@@ -22824,7 +22772,7 @@
       <c r="O12" s="54"/>
       <c r="P12" s="119"/>
     </row>
-    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="153"/>
       <c r="B13" s="155" t="s">
         <v>1</v>
@@ -22845,7 +22793,7 @@
       <c r="N13" s="54"/>
       <c r="O13" s="54"/>
     </row>
-    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="153"/>
       <c r="B14" s="155" t="s">
         <v>2</v>
@@ -22867,7 +22815,7 @@
       <c r="O14" s="54"/>
       <c r="P14" s="195"/>
     </row>
-    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="157"/>
       <c r="B15" s="155" t="s">
         <v>3</v>
@@ -22889,7 +22837,7 @@
       <c r="O15" s="54"/>
       <c r="P15" s="195"/>
     </row>
-    <row r="16" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="149">
         <v>3</v>
       </c>
@@ -22911,7 +22859,7 @@
       <c r="O16" s="54"/>
       <c r="P16" s="194"/>
     </row>
-    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="153"/>
       <c r="B17" s="155" t="s">
         <v>1</v>
@@ -22933,7 +22881,7 @@
       <c r="O17" s="54"/>
       <c r="P17" s="195"/>
     </row>
-    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="153"/>
       <c r="B18" s="155" t="s">
         <v>2</v>
@@ -22955,7 +22903,7 @@
       <c r="O18" s="54"/>
       <c r="P18" s="70"/>
     </row>
-    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="153"/>
       <c r="B19" s="155" t="s">
         <v>3</v>
@@ -22977,7 +22925,7 @@
       <c r="O19" s="54"/>
       <c r="P19" s="70"/>
     </row>
-    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="153"/>
       <c r="B20" s="155" t="s">
         <v>4</v>
@@ -22999,7 +22947,7 @@
       <c r="O20" s="54"/>
       <c r="P20" s="196"/>
     </row>
-    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="157"/>
       <c r="B21" s="155" t="s">
         <v>4</v>
@@ -23021,7 +22969,7 @@
       <c r="O21" s="54"/>
       <c r="P21" s="196"/>
     </row>
-    <row r="22" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="149">
         <v>4</v>
       </c>
@@ -23043,7 +22991,7 @@
       <c r="O22" s="54"/>
       <c r="P22" s="119"/>
     </row>
-    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="153"/>
       <c r="B23" s="155" t="s">
         <v>1</v>
@@ -23065,7 +23013,7 @@
       <c r="O23" s="54"/>
       <c r="P23" s="70"/>
     </row>
-    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="153"/>
       <c r="B24" s="155" t="s">
         <v>2</v>
@@ -23087,7 +23035,7 @@
       <c r="O24" s="54"/>
       <c r="P24" s="70"/>
     </row>
-    <row r="25" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="153"/>
       <c r="B25" s="155" t="s">
         <v>3</v>
@@ -23109,7 +23057,7 @@
       <c r="O25" s="54"/>
       <c r="P25" s="70"/>
     </row>
-    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="157"/>
       <c r="B26" s="155" t="s">
         <v>4</v>
@@ -23131,7 +23079,7 @@
       <c r="O26" s="54"/>
       <c r="P26" s="70"/>
     </row>
-    <row r="27" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="149">
         <v>5</v>
       </c>
@@ -23153,7 +23101,7 @@
       <c r="O27" s="54"/>
       <c r="P27" s="119"/>
     </row>
-    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="153"/>
       <c r="B28" s="155" t="s">
         <v>1</v>
@@ -23175,7 +23123,7 @@
       <c r="O28" s="54"/>
       <c r="P28" s="70"/>
     </row>
-    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="157"/>
       <c r="B29" s="155" t="s">
         <v>2</v>
@@ -23197,7 +23145,7 @@
       <c r="O29" s="54"/>
       <c r="P29" s="70"/>
     </row>
-    <row r="30" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="149">
         <v>6</v>
       </c>
@@ -23219,7 +23167,7 @@
       <c r="O30" s="54"/>
       <c r="P30" s="119"/>
     </row>
-    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="153"/>
       <c r="B31" s="155" t="s">
         <v>1</v>
@@ -23241,7 +23189,7 @@
       <c r="O31" s="54"/>
       <c r="P31" s="70"/>
     </row>
-    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" s="153"/>
       <c r="B32" s="155" t="s">
         <v>2</v>
@@ -23263,7 +23211,7 @@
       <c r="O32" s="54"/>
       <c r="P32" s="70"/>
     </row>
-    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="153"/>
       <c r="B33" s="155" t="s">
         <v>3</v>
@@ -23285,7 +23233,7 @@
       <c r="O33" s="54"/>
       <c r="P33" s="70"/>
     </row>
-    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="153"/>
       <c r="B34" s="155" t="s">
         <v>4</v>
@@ -23307,7 +23255,7 @@
       <c r="O34" s="54"/>
       <c r="P34" s="70"/>
     </row>
-    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="157"/>
       <c r="B35" s="155" t="s">
         <v>5</v>
@@ -23329,7 +23277,7 @@
       <c r="O35" s="54"/>
       <c r="P35" s="70"/>
     </row>
-    <row r="36" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="149">
         <v>7</v>
       </c>
@@ -23351,7 +23299,7 @@
       <c r="O36" s="54"/>
       <c r="P36" s="119"/>
     </row>
-    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="153"/>
       <c r="B37" s="155" t="s">
         <v>1</v>
@@ -23373,7 +23321,7 @@
       <c r="O37" s="54"/>
       <c r="P37" s="70"/>
     </row>
-    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" s="153"/>
       <c r="B38" s="155" t="s">
         <v>2</v>
@@ -23395,7 +23343,7 @@
       <c r="O38" s="54"/>
       <c r="P38" s="70"/>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" s="153"/>
       <c r="B39" s="155" t="s">
         <v>3</v>
@@ -23417,7 +23365,7 @@
       <c r="O39" s="54"/>
       <c r="P39" s="70"/>
     </row>
-    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" s="157"/>
       <c r="B40" s="155" t="s">
         <v>4</v>
@@ -23439,7 +23387,7 @@
       <c r="O40" s="54"/>
       <c r="P40" s="70"/>
     </row>
-    <row r="41" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="149">
         <v>8</v>
       </c>
@@ -23461,7 +23409,7 @@
       <c r="O41" s="54"/>
       <c r="P41" s="119"/>
     </row>
-    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" s="153"/>
       <c r="B42" s="155" t="s">
         <v>1</v>
@@ -23483,7 +23431,7 @@
       <c r="O42" s="54"/>
       <c r="P42" s="70"/>
     </row>
-    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" s="157"/>
       <c r="B43" s="155" t="s">
         <v>2</v>
@@ -23505,7 +23453,7 @@
       <c r="O43" s="54"/>
       <c r="P43" s="70"/>
     </row>
-    <row r="44" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="149">
         <v>9</v>
       </c>
@@ -23527,7 +23475,7 @@
       <c r="O44" s="54"/>
       <c r="P44" s="119"/>
     </row>
-    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" s="153"/>
       <c r="B45" s="155" t="s">
         <v>1</v>
@@ -23549,7 +23497,7 @@
       <c r="O45" s="54"/>
       <c r="P45" s="70"/>
     </row>
-    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" s="153"/>
       <c r="B46" s="155" t="s">
         <v>2</v>
@@ -23571,7 +23519,7 @@
       <c r="O46" s="54"/>
       <c r="P46" s="70"/>
     </row>
-    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" s="153"/>
       <c r="B47" s="155" t="s">
         <v>3</v>
@@ -23593,7 +23541,7 @@
       <c r="O47" s="54"/>
       <c r="P47" s="70"/>
     </row>
-    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" s="157"/>
       <c r="B48" s="155" t="s">
         <v>4</v>
@@ -23615,7 +23563,7 @@
       <c r="O48" s="54"/>
       <c r="P48" s="70"/>
     </row>
-    <row r="49" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="149">
         <v>10</v>
       </c>
@@ -23637,7 +23585,7 @@
       <c r="O49" s="54"/>
       <c r="P49" s="119"/>
     </row>
-    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" s="153"/>
       <c r="B50" s="155" t="s">
         <v>1</v>
@@ -23659,7 +23607,7 @@
       <c r="O50" s="54"/>
       <c r="P50" s="70"/>
     </row>
-    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" s="153"/>
       <c r="B51" s="155" t="s">
         <v>2</v>
@@ -23681,7 +23629,7 @@
       <c r="O51" s="54"/>
       <c r="P51" s="70"/>
     </row>
-    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52" s="153"/>
       <c r="B52" s="155" t="s">
         <v>3</v>
@@ -23703,7 +23651,7 @@
       <c r="O52" s="54"/>
       <c r="P52" s="70"/>
     </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" s="157"/>
       <c r="B53" s="155" t="s">
         <v>4</v>
@@ -23725,7 +23673,7 @@
       <c r="O53" s="54"/>
       <c r="P53" s="70"/>
     </row>
-    <row r="54" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="149">
         <v>11</v>
       </c>
@@ -23747,7 +23695,7 @@
       <c r="O54" s="54"/>
       <c r="P54" s="119"/>
     </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" s="153"/>
       <c r="B55" s="155" t="s">
         <v>1</v>
@@ -23769,7 +23717,7 @@
       <c r="O55" s="54"/>
       <c r="P55" s="70"/>
     </row>
-    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" s="157"/>
       <c r="B56" s="155" t="s">
         <v>2</v>
@@ -23791,7 +23739,7 @@
       <c r="O56" s="54"/>
       <c r="P56" s="70"/>
     </row>
-    <row r="57" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="149">
         <v>12</v>
       </c>
@@ -23813,7 +23761,7 @@
       <c r="O57" s="54"/>
       <c r="P57" s="119"/>
     </row>
-    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" s="157"/>
       <c r="B58" s="155" t="s">
         <v>1</v>
@@ -23835,7 +23783,7 @@
       <c r="O58" s="54"/>
       <c r="P58" s="70"/>
     </row>
-    <row r="59" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="149">
         <v>13</v>
       </c>
@@ -23857,7 +23805,7 @@
       <c r="O59" s="54"/>
       <c r="P59" s="119"/>
     </row>
-    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" s="153"/>
       <c r="B60" s="155" t="s">
         <v>1</v>
@@ -23879,7 +23827,7 @@
       <c r="O60" s="54"/>
       <c r="P60" s="70"/>
     </row>
-    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" s="157"/>
       <c r="B61" s="155" t="s">
         <v>2</v>
@@ -23901,7 +23849,7 @@
       <c r="O61" s="54"/>
       <c r="P61" s="70"/>
     </row>
-    <row r="62" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="149">
         <v>14</v>
       </c>
@@ -23923,7 +23871,7 @@
       <c r="O62" s="54"/>
       <c r="P62" s="70"/>
     </row>
-    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" s="153"/>
       <c r="B63" s="155" t="s">
         <v>1</v>
@@ -23945,7 +23893,7 @@
       <c r="O63" s="54"/>
       <c r="P63" s="70"/>
     </row>
-    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" s="157"/>
       <c r="B64" s="155" t="s">
         <v>2</v>
@@ -23967,7 +23915,7 @@
       <c r="O64" s="54"/>
       <c r="P64" s="70"/>
     </row>
-    <row r="65" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="149">
         <v>15</v>
       </c>
@@ -23989,7 +23937,7 @@
       <c r="O65" s="54"/>
       <c r="P65" s="119"/>
     </row>
-    <row r="66" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66" s="153"/>
       <c r="B66" s="155" t="s">
         <v>1</v>
@@ -24011,7 +23959,7 @@
       <c r="O66" s="54"/>
       <c r="P66" s="70"/>
     </row>
-    <row r="67" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A67" s="157"/>
       <c r="B67" s="155" t="s">
         <v>2</v>
@@ -24033,7 +23981,7 @@
       <c r="O67" s="54"/>
       <c r="P67" s="70"/>
     </row>
-    <row r="68" spans="1:18" s="11" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="102" t="s">
         <v>214</v>
       </c>
@@ -24053,7 +24001,7 @@
       <c r="O68" s="54"/>
       <c r="P68" s="194"/>
     </row>
-    <row r="69" spans="1:18" s="34" customFormat="1" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" s="34" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>16</v>
       </c>
@@ -24078,7 +24026,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="70" spans="1:18" s="34" customFormat="1" ht="30.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" s="34" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>17</v>
       </c>
@@ -24100,7 +24048,7 @@
       <c r="O70" s="54"/>
       <c r="P70" s="49"/>
     </row>
-    <row r="71" spans="1:18" ht="36.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:18" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>18</v>
       </c>
@@ -24241,7 +24189,7 @@
       </c>
       <c r="P74" s="78"/>
     </row>
-    <row r="75" spans="1:18" s="34" customFormat="1" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:18" s="34" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>22</v>
       </c>
@@ -24263,7 +24211,7 @@
       <c r="O75" s="54"/>
       <c r="P75" s="76"/>
     </row>
-    <row r="76" spans="1:18" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="108">
         <v>23</v>
       </c>
@@ -24285,7 +24233,7 @@
       <c r="O76" s="54"/>
       <c r="P76" s="70"/>
     </row>
-    <row r="77" spans="1:18" s="34" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:18" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>24</v>
       </c>
@@ -24307,7 +24255,7 @@
       <c r="O77" s="54"/>
       <c r="P77" s="49"/>
     </row>
-    <row r="78" spans="1:18" s="34" customFormat="1" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:18" s="34" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>25</v>
       </c>
@@ -24329,7 +24277,7 @@
       <c r="O78" s="54"/>
       <c r="P78" s="56"/>
     </row>
-    <row r="79" spans="1:18" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="108">
         <v>26</v>
       </c>
@@ -24351,7 +24299,7 @@
       <c r="O79" s="54"/>
       <c r="P79" s="70"/>
     </row>
-    <row r="80" spans="1:18" s="34" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:18" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>27</v>
       </c>
@@ -24373,7 +24321,7 @@
       <c r="O80" s="54"/>
       <c r="P80" s="197"/>
     </row>
-    <row r="81" spans="1:16" s="11" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:16" s="11" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="102" t="s">
         <v>222</v>
       </c>
@@ -24433,7 +24381,7 @@
       </c>
       <c r="P82" s="273"/>
     </row>
-    <row r="83" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="108">
         <v>29</v>
       </c>
@@ -24455,7 +24403,7 @@
       <c r="O83" s="54"/>
       <c r="P83" s="70"/>
     </row>
-    <row r="84" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="108">
         <v>30</v>
       </c>
@@ -24477,14 +24425,14 @@
       <c r="O84" s="54"/>
       <c r="P84" s="70"/>
     </row>
-    <row r="85" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="108">
         <v>31</v>
       </c>
-      <c r="B85" s="407" t="s">
+      <c r="B85" s="396" t="s">
         <v>226</v>
       </c>
-      <c r="C85" s="408"/>
+      <c r="C85" s="397"/>
       <c r="D85" s="51"/>
       <c r="E85" s="51"/>
       <c r="F85" s="51"/>
@@ -24499,7 +24447,7 @@
       <c r="O85" s="54"/>
       <c r="P85" s="70"/>
     </row>
-    <row r="86" spans="1:16" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="108">
         <v>32</v>
       </c>
@@ -24521,7 +24469,7 @@
       <c r="O86" s="54"/>
       <c r="P86" s="197"/>
     </row>
-    <row r="87" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="108">
         <v>33</v>
       </c>
@@ -24543,7 +24491,7 @@
       <c r="O87" s="54"/>
       <c r="P87" s="70"/>
     </row>
-    <row r="88" spans="1:16" s="11" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:16" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="102" t="s">
         <v>229</v>
       </c>
@@ -24563,7 +24511,7 @@
       <c r="O88" s="103"/>
       <c r="P88" s="104"/>
     </row>
-    <row r="89" spans="1:16" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="108">
         <v>34</v>
       </c>
@@ -24705,7 +24653,7 @@
       </c>
       <c r="P92" s="329"/>
     </row>
-    <row r="93" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="108">
         <v>38</v>
       </c>
@@ -24727,7 +24675,7 @@
       <c r="O93" s="54"/>
       <c r="P93" s="197"/>
     </row>
-    <row r="94" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="108">
         <v>39</v>
       </c>
@@ -24749,7 +24697,7 @@
       <c r="O94" s="54"/>
       <c r="P94" s="70"/>
     </row>
-    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95" s="108">
         <v>40</v>
       </c>
@@ -24771,7 +24719,7 @@
       <c r="O95" s="54"/>
       <c r="P95" s="197"/>
     </row>
-    <row r="96" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="108">
         <v>41</v>
       </c>
@@ -24793,7 +24741,7 @@
       <c r="O96" s="54"/>
       <c r="P96" s="90"/>
     </row>
-    <row r="97" spans="1:16" s="34" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A97" s="108">
         <v>42</v>
       </c>
@@ -24815,7 +24763,7 @@
       <c r="O97" s="54"/>
       <c r="P97" s="197"/>
     </row>
-    <row r="98" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" s="108">
         <v>43</v>
       </c>
@@ -24837,7 +24785,7 @@
       <c r="O98" s="54"/>
       <c r="P98" s="61"/>
     </row>
-    <row r="99" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>44</v>
       </c>
@@ -24859,7 +24807,7 @@
       <c r="O99" s="54"/>
       <c r="P99" s="273"/>
     </row>
-    <row r="100" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100" s="108">
         <v>45</v>
       </c>
@@ -24881,7 +24829,7 @@
       <c r="O100" s="54"/>
       <c r="P100" s="197"/>
     </row>
-    <row r="101" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="108">
         <v>46</v>
       </c>
@@ -24903,7 +24851,7 @@
       <c r="O101" s="54"/>
       <c r="P101" s="70"/>
     </row>
-    <row r="102" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="108">
         <v>47</v>
       </c>
@@ -24925,7 +24873,7 @@
       <c r="O102" s="54"/>
       <c r="P102" s="70"/>
     </row>
-    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A103" s="108">
         <v>48</v>
       </c>
@@ -24947,7 +24895,7 @@
       <c r="O103" s="54"/>
       <c r="P103" s="197"/>
     </row>
-    <row r="104" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="108">
         <v>49</v>
       </c>
@@ -24969,7 +24917,7 @@
       <c r="O104" s="54"/>
       <c r="P104" s="198"/>
     </row>
-    <row r="105" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="108">
         <v>50</v>
       </c>
@@ -25031,7 +24979,7 @@
       </c>
       <c r="P106" s="273"/>
     </row>
-    <row r="107" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A107" s="108">
         <v>52</v>
       </c>
@@ -25053,7 +25001,7 @@
       <c r="O107" s="54"/>
       <c r="P107" s="197"/>
     </row>
-    <row r="108" spans="1:16" s="34" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:16" s="34" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="102" t="s">
         <v>246</v>
       </c>
@@ -25113,7 +25061,7 @@
       </c>
       <c r="P109" s="238"/>
     </row>
-    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>54</v>
       </c>
@@ -25135,7 +25083,7 @@
       <c r="O110" s="54"/>
       <c r="P110" s="197"/>
     </row>
-    <row r="111" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>55</v>
       </c>
@@ -25157,7 +25105,7 @@
       <c r="O111" s="54"/>
       <c r="P111" s="197"/>
     </row>
-    <row r="112" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>56</v>
       </c>
@@ -25179,7 +25127,7 @@
       <c r="O112" s="54"/>
       <c r="P112" s="56"/>
     </row>
-    <row r="113" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>57</v>
       </c>
@@ -25242,7 +25190,7 @@
       </c>
       <c r="P114" s="334"/>
     </row>
-    <row r="115" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>59</v>
       </c>
@@ -25264,7 +25212,7 @@
       <c r="O115" s="54"/>
       <c r="P115" s="197"/>
     </row>
-    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>60</v>
       </c>
@@ -25286,7 +25234,7 @@
       <c r="O116" s="54"/>
       <c r="P116" s="65"/>
     </row>
-    <row r="117" spans="1:16" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>61</v>
       </c>
@@ -25348,7 +25296,7 @@
       </c>
       <c r="P118" s="277"/>
     </row>
-    <row r="119" spans="1:16" s="34" customFormat="1" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:16" s="34" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>63</v>
       </c>
@@ -25370,7 +25318,7 @@
       <c r="O119" s="54"/>
       <c r="P119" s="197"/>
     </row>
-    <row r="120" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>64</v>
       </c>
@@ -25432,7 +25380,7 @@
       </c>
       <c r="P121" s="329"/>
     </row>
-    <row r="122" spans="1:16" s="34" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:16" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>66</v>
       </c>
@@ -25454,14 +25402,14 @@
       <c r="O122" s="54"/>
       <c r="P122" s="197"/>
     </row>
-    <row r="123" spans="1:16" s="34" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:16" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>67</v>
       </c>
-      <c r="B123" s="411" t="s">
+      <c r="B123" s="400" t="s">
         <v>257</v>
       </c>
-      <c r="C123" s="412"/>
+      <c r="C123" s="401"/>
       <c r="D123" s="51"/>
       <c r="E123" s="51"/>
       <c r="F123" s="51"/>
@@ -25476,7 +25424,7 @@
       <c r="O123" s="54"/>
       <c r="P123" s="197"/>
     </row>
-    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>68</v>
       </c>
@@ -25498,7 +25446,7 @@
       <c r="O124" s="54"/>
       <c r="P124" s="197"/>
     </row>
-    <row r="125" spans="1:16" s="34" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:16" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>69</v>
       </c>
@@ -25560,7 +25508,7 @@
       </c>
       <c r="P126" s="197"/>
     </row>
-    <row r="127" spans="1:16" s="34" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:16" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>71</v>
       </c>
@@ -25582,7 +25530,7 @@
       <c r="O127" s="54"/>
       <c r="P127" s="197"/>
     </row>
-    <row r="128" spans="1:16" s="34" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:16" s="34" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>72</v>
       </c>
@@ -25604,7 +25552,7 @@
       <c r="O128" s="54"/>
       <c r="P128" s="64"/>
     </row>
-    <row r="129" spans="1:16" s="34" customFormat="1" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:16" s="34" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>73</v>
       </c>
@@ -25626,7 +25574,7 @@
       <c r="O129" s="54"/>
       <c r="P129" s="273"/>
     </row>
-    <row r="130" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>74</v>
       </c>
@@ -25688,7 +25636,7 @@
       </c>
       <c r="P131" s="273"/>
     </row>
-    <row r="132" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>76</v>
       </c>
@@ -25710,7 +25658,7 @@
       <c r="O132" s="54"/>
       <c r="P132" s="70"/>
     </row>
-    <row r="133" spans="1:16" s="94" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:16" s="94" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>77</v>
       </c>
@@ -25732,7 +25680,7 @@
       <c r="O133" s="54"/>
       <c r="P133" s="197"/>
     </row>
-    <row r="134" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>78</v>
       </c>
@@ -25754,7 +25702,7 @@
       <c r="O134" s="54"/>
       <c r="P134" s="197"/>
     </row>
-    <row r="135" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>79</v>
       </c>
@@ -25776,7 +25724,7 @@
       <c r="O135" s="54"/>
       <c r="P135" s="90"/>
     </row>
-    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>80</v>
       </c>
@@ -25798,7 +25746,7 @@
       <c r="O136" s="54"/>
       <c r="P136" s="197"/>
     </row>
-    <row r="137" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>81</v>
       </c>
@@ -25820,7 +25768,7 @@
       <c r="O137" s="54"/>
       <c r="P137" s="197"/>
     </row>
-    <row r="138" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>82</v>
       </c>
@@ -25842,7 +25790,7 @@
       <c r="O138" s="54"/>
       <c r="P138" s="197"/>
     </row>
-    <row r="139" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>83</v>
       </c>
@@ -25864,7 +25812,7 @@
       <c r="O139" s="54"/>
       <c r="P139" s="200"/>
     </row>
-    <row r="140" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>84</v>
       </c>
@@ -25886,7 +25834,7 @@
       <c r="O140" s="54"/>
       <c r="P140" s="197"/>
     </row>
-    <row r="141" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>85</v>
       </c>
@@ -25908,7 +25856,7 @@
       <c r="O141" s="54"/>
       <c r="P141" s="200"/>
     </row>
-    <row r="142" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>86</v>
       </c>
@@ -25930,7 +25878,7 @@
       <c r="O142" s="54"/>
       <c r="P142" s="201"/>
     </row>
-    <row r="143" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>87</v>
       </c>
@@ -25952,7 +25900,7 @@
       <c r="O143" s="54"/>
       <c r="P143" s="201"/>
     </row>
-    <row r="144" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>88</v>
       </c>
@@ -25974,7 +25922,7 @@
       <c r="O144" s="54"/>
       <c r="P144" s="201"/>
     </row>
-    <row r="145" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>89</v>
       </c>
@@ -25996,7 +25944,7 @@
       <c r="O145" s="54"/>
       <c r="P145" s="201"/>
     </row>
-    <row r="146" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>90</v>
       </c>
@@ -26018,7 +25966,7 @@
       <c r="O146" s="54"/>
       <c r="P146" s="201"/>
     </row>
-    <row r="147" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>91</v>
       </c>
@@ -26040,7 +25988,7 @@
       <c r="O147" s="54"/>
       <c r="P147" s="274"/>
     </row>
-    <row r="148" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>92</v>
       </c>
@@ -26062,7 +26010,7 @@
       <c r="O148" s="54"/>
       <c r="P148" s="61"/>
     </row>
-    <row r="149" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>93</v>
       </c>
@@ -26084,7 +26032,7 @@
       <c r="O149" s="54"/>
       <c r="P149" s="197"/>
     </row>
-    <row r="150" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>94</v>
       </c>
@@ -26106,7 +26054,7 @@
       <c r="O150" s="54"/>
       <c r="P150" s="61"/>
     </row>
-    <row r="151" spans="1:16" s="3" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:16" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>95</v>
       </c>
@@ -26128,7 +26076,7 @@
       <c r="O151" s="54"/>
       <c r="P151" s="199"/>
     </row>
-    <row r="152" spans="1:16" s="34" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:16" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>96</v>
       </c>
@@ -26150,7 +26098,7 @@
       <c r="O152" s="54"/>
       <c r="P152" s="197"/>
     </row>
-    <row r="153" spans="1:16" s="34" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:16" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>97</v>
       </c>
@@ -26172,7 +26120,7 @@
       <c r="O153" s="54"/>
       <c r="P153" s="273"/>
     </row>
-    <row r="154" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>98</v>
       </c>
@@ -26194,7 +26142,7 @@
       <c r="O154" s="54"/>
       <c r="P154" s="238"/>
     </row>
-    <row r="155" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>99</v>
       </c>
@@ -26216,7 +26164,7 @@
       <c r="O155" s="54"/>
       <c r="P155" s="239"/>
     </row>
-    <row r="156" spans="1:16" s="34" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:16" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>100</v>
       </c>
@@ -26238,7 +26186,7 @@
       <c r="O156" s="54"/>
       <c r="P156" s="238"/>
     </row>
-    <row r="157" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>101</v>
       </c>
@@ -26260,7 +26208,7 @@
       <c r="O157" s="54"/>
       <c r="P157" s="69"/>
     </row>
-    <row r="158" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>102</v>
       </c>
@@ -26282,7 +26230,7 @@
       <c r="O158" s="54"/>
       <c r="P158" s="275"/>
     </row>
-    <row r="159" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>103</v>
       </c>
@@ -26304,14 +26252,14 @@
       <c r="O159" s="54"/>
       <c r="P159" s="275"/>
     </row>
-    <row r="160" spans="1:16" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>104</v>
       </c>
-      <c r="B160" s="409" t="s">
+      <c r="B160" s="398" t="s">
         <v>928</v>
       </c>
-      <c r="C160" s="410"/>
+      <c r="C160" s="399"/>
       <c r="D160" s="51"/>
       <c r="E160" s="51"/>
       <c r="F160" s="51"/>
@@ -26326,7 +26274,7 @@
       <c r="O160" s="54"/>
       <c r="P160" s="267"/>
     </row>
-    <row r="161" spans="1:16" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>105</v>
       </c>
@@ -26348,7 +26296,7 @@
       <c r="O161" s="54"/>
       <c r="P161" s="202"/>
     </row>
-    <row r="162" spans="1:16" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>106</v>
       </c>
@@ -26370,7 +26318,7 @@
       <c r="O162" s="54"/>
       <c r="P162" s="202"/>
     </row>
-    <row r="163" spans="1:16" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>107</v>
       </c>
@@ -26392,7 +26340,7 @@
       <c r="O163" s="54"/>
       <c r="P163" s="202"/>
     </row>
-    <row r="164" spans="1:16" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>108</v>
       </c>
@@ -26414,7 +26362,7 @@
       <c r="O164" s="54"/>
       <c r="P164" s="202"/>
     </row>
-    <row r="165" spans="1:16" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>109</v>
       </c>
@@ -26436,7 +26384,7 @@
       <c r="O165" s="54"/>
       <c r="P165" s="56"/>
     </row>
-    <row r="166" spans="1:16" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>110</v>
       </c>
@@ -26458,7 +26406,7 @@
       <c r="O166" s="54"/>
       <c r="P166" s="56"/>
     </row>
-    <row r="167" spans="1:16" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>111</v>
       </c>
@@ -26480,14 +26428,14 @@
       <c r="O167" s="54"/>
       <c r="P167" s="56"/>
     </row>
-    <row r="168" spans="1:16" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>112</v>
       </c>
-      <c r="B168" s="413" t="s">
+      <c r="B168" s="402" t="s">
         <v>957</v>
       </c>
-      <c r="C168" s="414"/>
+      <c r="C168" s="403"/>
       <c r="D168" s="52"/>
       <c r="E168" s="51"/>
       <c r="F168" s="51"/>
@@ -26502,14 +26450,14 @@
       <c r="O168" s="54"/>
       <c r="P168" s="56"/>
     </row>
-    <row r="169" spans="1:16" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="282">
         <v>113</v>
       </c>
-      <c r="B169" s="415" t="s">
+      <c r="B169" s="404" t="s">
         <v>960</v>
       </c>
-      <c r="C169" s="416"/>
+      <c r="C169" s="405"/>
       <c r="D169" s="52"/>
       <c r="E169" s="52"/>
       <c r="F169" s="51"/>
@@ -26524,14 +26472,14 @@
       <c r="O169" s="54"/>
       <c r="P169" s="267"/>
     </row>
-    <row r="170" spans="1:16" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="282">
         <v>114</v>
       </c>
-      <c r="B170" s="415" t="s">
+      <c r="B170" s="404" t="s">
         <v>959</v>
       </c>
-      <c r="C170" s="416"/>
+      <c r="C170" s="405"/>
       <c r="D170" s="52"/>
       <c r="E170" s="52"/>
       <c r="F170" s="51"/>
@@ -26547,11 +26495,11 @@
       <c r="P170" s="56"/>
     </row>
     <row r="171" spans="1:16" s="36" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="404" t="s">
+      <c r="A171" s="393" t="s">
         <v>596</v>
       </c>
-      <c r="B171" s="405"/>
-      <c r="C171" s="406"/>
+      <c r="B171" s="394"/>
+      <c r="C171" s="395"/>
       <c r="D171" s="217">
         <f>SUBTOTAL(9,D72:D131)</f>
         <v>103</v>
@@ -26591,13 +26539,6 @@
       <c r="C172" s="11"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:P171" xr:uid="{00000000-0009-0000-0000-000006000000}">
-    <filterColumn colId="4">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
   <mergeCells count="8">
     <mergeCell ref="A2:P2"/>
     <mergeCell ref="A171:C171"/>
@@ -26656,79 +26597,79 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2927" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="R1" s="419" t="s">
+      <c r="R1" s="408" t="s">
         <v>655</v>
       </c>
-      <c r="S1" s="419"/>
-      <c r="T1" s="419"/>
+      <c r="S1" s="408"/>
+      <c r="T1" s="408"/>
     </row>
     <row r="2" spans="1:2927" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="386" t="s">
+      <c r="A2" s="373" t="s">
         <v>660</v>
       </c>
-      <c r="B2" s="386"/>
-      <c r="C2" s="386"/>
-      <c r="D2" s="386"/>
-      <c r="E2" s="386"/>
-      <c r="F2" s="386"/>
-      <c r="G2" s="386"/>
-      <c r="H2" s="386"/>
-      <c r="I2" s="386"/>
-      <c r="J2" s="386"/>
-      <c r="K2" s="386"/>
-      <c r="L2" s="386"/>
-      <c r="M2" s="386"/>
-      <c r="N2" s="386"/>
-      <c r="O2" s="386"/>
-      <c r="P2" s="386"/>
-      <c r="Q2" s="386"/>
-      <c r="R2" s="386"/>
-      <c r="S2" s="386"/>
-      <c r="T2" s="386"/>
+      <c r="B2" s="373"/>
+      <c r="C2" s="373"/>
+      <c r="D2" s="373"/>
+      <c r="E2" s="373"/>
+      <c r="F2" s="373"/>
+      <c r="G2" s="373"/>
+      <c r="H2" s="373"/>
+      <c r="I2" s="373"/>
+      <c r="J2" s="373"/>
+      <c r="K2" s="373"/>
+      <c r="L2" s="373"/>
+      <c r="M2" s="373"/>
+      <c r="N2" s="373"/>
+      <c r="O2" s="373"/>
+      <c r="P2" s="373"/>
+      <c r="Q2" s="373"/>
+      <c r="R2" s="373"/>
+      <c r="S2" s="373"/>
+      <c r="T2" s="373"/>
     </row>
     <row r="3" spans="1:2927" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="398" t="s">
+      <c r="A3" s="387" t="s">
         <v>291</v>
       </c>
-      <c r="B3" s="420" t="s">
+      <c r="B3" s="409" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="380" t="s">
+      <c r="C3" s="367" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="380"/>
-      <c r="E3" s="380" t="s">
+      <c r="D3" s="367"/>
+      <c r="E3" s="367" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="380"/>
-      <c r="G3" s="380"/>
-      <c r="H3" s="380"/>
-      <c r="I3" s="380"/>
-      <c r="J3" s="380"/>
-      <c r="K3" s="380"/>
-      <c r="L3" s="380"/>
-      <c r="M3" s="421" t="s">
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
+      <c r="L3" s="367"/>
+      <c r="M3" s="410" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="421" t="s">
+      <c r="N3" s="410" t="s">
         <v>292</v>
       </c>
-      <c r="O3" s="380" t="s">
+      <c r="O3" s="367" t="s">
         <v>35</v>
       </c>
-      <c r="P3" s="423" t="s">
+      <c r="P3" s="412" t="s">
         <v>23</v>
       </c>
-      <c r="Q3" s="423" t="s">
+      <c r="Q3" s="412" t="s">
         <v>24</v>
       </c>
-      <c r="R3" s="423" t="s">
+      <c r="R3" s="412" t="s">
         <v>25</v>
       </c>
-      <c r="S3" s="423" t="s">
+      <c r="S3" s="412" t="s">
         <v>26</v>
       </c>
-      <c r="T3" s="398" t="s">
+      <c r="T3" s="387" t="s">
         <v>961</v>
       </c>
       <c r="U3" s="6"/>
@@ -29640,8 +29581,8 @@
       <c r="DHO3" s="6"/>
     </row>
     <row r="4" spans="1:2927" s="1" customFormat="1" ht="31.2" x14ac:dyDescent="0.25">
-      <c r="A4" s="398"/>
-      <c r="B4" s="420"/>
+      <c r="A4" s="387"/>
+      <c r="B4" s="409"/>
       <c r="C4" s="244" t="s">
         <v>27</v>
       </c>
@@ -29672,14 +29613,14 @@
       <c r="L4" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="M4" s="422"/>
-      <c r="N4" s="422"/>
-      <c r="O4" s="380"/>
-      <c r="P4" s="423"/>
-      <c r="Q4" s="423"/>
-      <c r="R4" s="423"/>
-      <c r="S4" s="423"/>
-      <c r="T4" s="380"/>
+      <c r="M4" s="411"/>
+      <c r="N4" s="411"/>
+      <c r="O4" s="367"/>
+      <c r="P4" s="412"/>
+      <c r="Q4" s="412"/>
+      <c r="R4" s="412"/>
+      <c r="S4" s="412"/>
+      <c r="T4" s="367"/>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
       <c r="W4" s="6"/>
@@ -35558,12 +35499,12 @@
       <c r="DHO5" s="6"/>
     </row>
     <row r="6" spans="1:2927" s="3" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="417" t="s">
+      <c r="A6" s="406" t="s">
         <v>627</v>
       </c>
-      <c r="B6" s="418"/>
-      <c r="C6" s="418"/>
-      <c r="D6" s="418"/>
+      <c r="B6" s="407"/>
+      <c r="C6" s="407"/>
+      <c r="D6" s="407"/>
       <c r="E6" s="205"/>
       <c r="F6" s="205"/>
       <c r="G6" s="205"/>
@@ -68365,10 +68306,10 @@
       <c r="T37" s="108"/>
     </row>
     <row r="38" spans="1:20" s="101" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="377" t="s">
+      <c r="A38" s="364" t="s">
         <v>289</v>
       </c>
-      <c r="B38" s="377"/>
+      <c r="B38" s="364"/>
       <c r="C38" s="164"/>
       <c r="D38" s="164"/>
       <c r="E38" s="164"/>
@@ -68430,7 +68371,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor rgb="FF147216"/>
   </sheetPr>
   <dimension ref="A1:J123"/>
@@ -68473,48 +68414,48 @@
       <c r="J2" s="222"/>
     </row>
     <row r="3" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="432" t="s">
+      <c r="A3" s="413" t="s">
         <v>939</v>
       </c>
-      <c r="B3" s="432"/>
-      <c r="C3" s="432"/>
-      <c r="D3" s="432"/>
-      <c r="E3" s="432"/>
-      <c r="F3" s="432"/>
-      <c r="G3" s="432"/>
-      <c r="H3" s="432"/>
-      <c r="I3" s="432"/>
-      <c r="J3" s="432"/>
+      <c r="B3" s="413"/>
+      <c r="C3" s="413"/>
+      <c r="D3" s="413"/>
+      <c r="E3" s="413"/>
+      <c r="F3" s="413"/>
+      <c r="G3" s="413"/>
+      <c r="H3" s="413"/>
+      <c r="I3" s="413"/>
+      <c r="J3" s="413"/>
     </row>
     <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="429" t="s">
+      <c r="A4" s="414" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="429" t="s">
+      <c r="B4" s="414" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="433" t="s">
+      <c r="C4" s="415" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="433"/>
-      <c r="E4" s="433" t="s">
+      <c r="D4" s="415"/>
+      <c r="E4" s="415" t="s">
         <v>940</v>
       </c>
-      <c r="F4" s="433"/>
-      <c r="G4" s="433"/>
-      <c r="H4" s="429" t="s">
+      <c r="F4" s="415"/>
+      <c r="G4" s="415"/>
+      <c r="H4" s="414" t="s">
         <v>941</v>
       </c>
-      <c r="I4" s="434" t="s">
+      <c r="I4" s="416" t="s">
         <v>942</v>
       </c>
-      <c r="J4" s="435" t="s">
+      <c r="J4" s="417" t="s">
         <v>962</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="429"/>
-      <c r="B5" s="429"/>
+      <c r="A5" s="414"/>
+      <c r="B5" s="414"/>
       <c r="C5" s="227" t="s">
         <v>27</v>
       </c>
@@ -68530,15 +68471,15 @@
       <c r="G5" s="226" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="429"/>
-      <c r="I5" s="434"/>
-      <c r="J5" s="435"/>
+      <c r="H5" s="414"/>
+      <c r="I5" s="416"/>
+      <c r="J5" s="417"/>
     </row>
     <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="425" t="s">
+      <c r="A6" s="419" t="s">
         <v>1049</v>
       </c>
-      <c r="B6" s="426"/>
+      <c r="B6" s="420"/>
       <c r="C6" s="227"/>
       <c r="D6" s="227"/>
       <c r="E6" s="226"/>
@@ -68570,7 +68511,7 @@
       <c r="I7" s="327"/>
       <c r="J7" s="328"/>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2</v>
       </c>
@@ -68586,7 +68527,7 @@
       <c r="I8" s="228"/>
       <c r="J8" s="229"/>
     </row>
-    <row r="9" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>3</v>
       </c>
@@ -68602,7 +68543,7 @@
       <c r="I9" s="272"/>
       <c r="J9" s="271"/>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>4</v>
       </c>
@@ -68618,7 +68559,7 @@
       <c r="I10" s="234"/>
       <c r="J10" s="297"/>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>5</v>
       </c>
@@ -68634,7 +68575,7 @@
       <c r="I11" s="228"/>
       <c r="J11" s="229"/>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>6</v>
       </c>
@@ -68650,7 +68591,7 @@
       <c r="I12" s="228"/>
       <c r="J12" s="229"/>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>7</v>
       </c>
@@ -68666,7 +68607,7 @@
       <c r="I13" s="228"/>
       <c r="J13" s="229"/>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>8</v>
       </c>
@@ -68682,7 +68623,7 @@
       <c r="I14" s="228"/>
       <c r="J14" s="229"/>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>9</v>
       </c>
@@ -68698,7 +68639,7 @@
       <c r="I15" s="228"/>
       <c r="J15" s="229"/>
     </row>
-    <row r="16" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>10</v>
       </c>
@@ -68714,7 +68655,7 @@
       <c r="I16" s="228"/>
       <c r="J16" s="229"/>
     </row>
-    <row r="17" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>11</v>
       </c>
@@ -68730,7 +68671,7 @@
       <c r="I17" s="228"/>
       <c r="J17" s="229"/>
     </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>12</v>
       </c>
@@ -68746,7 +68687,7 @@
       <c r="I18" s="228"/>
       <c r="J18" s="229"/>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>13</v>
       </c>
@@ -68762,7 +68703,7 @@
       <c r="I19" s="228"/>
       <c r="J19" s="229"/>
     </row>
-    <row r="20" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>14</v>
       </c>
@@ -68778,7 +68719,7 @@
       <c r="I20" s="228"/>
       <c r="J20" s="229"/>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>15</v>
       </c>
@@ -68794,7 +68735,7 @@
       <c r="I21" s="228"/>
       <c r="J21" s="229"/>
     </row>
-    <row r="22" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>16</v>
       </c>
@@ -68810,7 +68751,7 @@
       <c r="I22" s="229"/>
       <c r="J22" s="229"/>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>17</v>
       </c>
@@ -68826,7 +68767,7 @@
       <c r="I23" s="229"/>
       <c r="J23" s="229"/>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>18</v>
       </c>
@@ -68842,7 +68783,7 @@
       <c r="I24" s="229"/>
       <c r="J24" s="229"/>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>19</v>
       </c>
@@ -68858,7 +68799,7 @@
       <c r="I25" s="229"/>
       <c r="J25" s="229"/>
     </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>20</v>
       </c>
@@ -68874,7 +68815,7 @@
       <c r="I26" s="229"/>
       <c r="J26" s="229"/>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>21</v>
       </c>
@@ -68890,7 +68831,7 @@
       <c r="I27" s="229"/>
       <c r="J27" s="229"/>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>22</v>
       </c>
@@ -68906,7 +68847,7 @@
       <c r="I28" s="229"/>
       <c r="J28" s="229"/>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>23</v>
       </c>
@@ -68922,7 +68863,7 @@
       <c r="I29" s="229"/>
       <c r="J29" s="229"/>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24</v>
       </c>
@@ -68938,7 +68879,7 @@
       <c r="I30" s="229"/>
       <c r="J30" s="229"/>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>25</v>
       </c>
@@ -68954,7 +68895,7 @@
       <c r="I31" s="229"/>
       <c r="J31" s="229"/>
     </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>26</v>
       </c>
@@ -68970,7 +68911,7 @@
       <c r="I32" s="229"/>
       <c r="J32" s="229"/>
     </row>
-    <row r="33" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>27</v>
       </c>
@@ -68986,7 +68927,7 @@
       <c r="I33" s="229"/>
       <c r="J33" s="229"/>
     </row>
-    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>28</v>
       </c>
@@ -69002,7 +68943,7 @@
       <c r="I34" s="229"/>
       <c r="J34" s="229"/>
     </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>29</v>
       </c>
@@ -69018,7 +68959,7 @@
       <c r="I35" s="229"/>
       <c r="J35" s="229"/>
     </row>
-    <row r="36" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>30</v>
       </c>
@@ -69034,7 +68975,7 @@
       <c r="I36" s="229"/>
       <c r="J36" s="229"/>
     </row>
-    <row r="37" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>31</v>
       </c>
@@ -69050,7 +68991,7 @@
       <c r="I37" s="229"/>
       <c r="J37" s="229"/>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>32</v>
       </c>
@@ -69066,7 +69007,7 @@
       <c r="I38" s="229"/>
       <c r="J38" s="229"/>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>33</v>
       </c>
@@ -69082,7 +69023,7 @@
       <c r="I39" s="229"/>
       <c r="J39" s="229"/>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>34</v>
       </c>
@@ -69098,7 +69039,7 @@
       <c r="I40" s="229"/>
       <c r="J40" s="229"/>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>35</v>
       </c>
@@ -69114,7 +69055,7 @@
       <c r="I41" s="229"/>
       <c r="J41" s="229"/>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>36</v>
       </c>
@@ -69130,7 +69071,7 @@
       <c r="I42" s="229"/>
       <c r="J42" s="229"/>
     </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>37</v>
       </c>
@@ -69146,7 +69087,7 @@
       <c r="I43" s="229"/>
       <c r="J43" s="229"/>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>38</v>
       </c>
@@ -69162,7 +69103,7 @@
       <c r="I44" s="229"/>
       <c r="J44" s="229"/>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>39</v>
       </c>
@@ -69178,7 +69119,7 @@
       <c r="I45" s="229"/>
       <c r="J45" s="229"/>
     </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>40</v>
       </c>
@@ -69194,7 +69135,7 @@
       <c r="I46" s="229"/>
       <c r="J46" s="229"/>
     </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>41</v>
       </c>
@@ -69210,7 +69151,7 @@
       <c r="I47" s="229"/>
       <c r="J47" s="229"/>
     </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>42</v>
       </c>
@@ -69226,7 +69167,7 @@
       <c r="I48" s="229"/>
       <c r="J48" s="229"/>
     </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>43</v>
       </c>
@@ -69242,7 +69183,7 @@
       <c r="I49" s="229"/>
       <c r="J49" s="229"/>
     </row>
-    <row r="50" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>44</v>
       </c>
@@ -69258,7 +69199,7 @@
       <c r="I50" s="229"/>
       <c r="J50" s="229"/>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>45</v>
       </c>
@@ -69274,7 +69215,7 @@
       <c r="I51" s="229"/>
       <c r="J51" s="229"/>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>46</v>
       </c>
@@ -69312,7 +69253,7 @@
       <c r="I53" s="301"/>
       <c r="J53" s="301"/>
     </row>
-    <row r="54" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>48</v>
       </c>
@@ -69328,7 +69269,7 @@
       <c r="I54" s="229"/>
       <c r="J54" s="229"/>
     </row>
-    <row r="55" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>49</v>
       </c>
@@ -69344,7 +69285,7 @@
       <c r="I55" s="229"/>
       <c r="J55" s="229"/>
     </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>50</v>
       </c>
@@ -69360,7 +69301,7 @@
       <c r="I56" s="229"/>
       <c r="J56" s="229"/>
     </row>
-    <row r="57" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>51</v>
       </c>
@@ -69376,7 +69317,7 @@
       <c r="I57" s="229"/>
       <c r="J57" s="229"/>
     </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>52</v>
       </c>
@@ -69392,7 +69333,7 @@
       <c r="I58" s="229"/>
       <c r="J58" s="229"/>
     </row>
-    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>53</v>
       </c>
@@ -69408,7 +69349,7 @@
       <c r="I59" s="229"/>
       <c r="J59" s="229"/>
     </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>54</v>
       </c>
@@ -69424,7 +69365,7 @@
       <c r="I60" s="229"/>
       <c r="J60" s="229"/>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>55</v>
       </c>
@@ -69440,7 +69381,7 @@
       <c r="I61" s="229"/>
       <c r="J61" s="229"/>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>56</v>
       </c>
@@ -69456,7 +69397,7 @@
       <c r="I62" s="229"/>
       <c r="J62" s="229"/>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>57</v>
       </c>
@@ -69472,7 +69413,7 @@
       <c r="I63" s="229"/>
       <c r="J63" s="229"/>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>58</v>
       </c>
@@ -69488,7 +69429,7 @@
       <c r="I64" s="229"/>
       <c r="J64" s="229"/>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>59</v>
       </c>
@@ -69504,7 +69445,7 @@
       <c r="I65" s="229"/>
       <c r="J65" s="229"/>
     </row>
-    <row r="66" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>60</v>
       </c>
@@ -69520,7 +69461,7 @@
       <c r="I66" s="229"/>
       <c r="J66" s="229"/>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>61</v>
       </c>
@@ -69536,7 +69477,7 @@
       <c r="I67" s="229"/>
       <c r="J67" s="229"/>
     </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>62</v>
       </c>
@@ -69552,7 +69493,7 @@
       <c r="I68" s="229"/>
       <c r="J68" s="229"/>
     </row>
-    <row r="69" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>63</v>
       </c>
@@ -69568,7 +69509,7 @@
       <c r="I69" s="229"/>
       <c r="J69" s="229"/>
     </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>64</v>
       </c>
@@ -69584,7 +69525,7 @@
       <c r="I70" s="229"/>
       <c r="J70" s="229"/>
     </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>65</v>
       </c>
@@ -69600,7 +69541,7 @@
       <c r="I71" s="229"/>
       <c r="J71" s="229"/>
     </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>66</v>
       </c>
@@ -69616,7 +69557,7 @@
       <c r="I72" s="229"/>
       <c r="J72" s="229"/>
     </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>67</v>
       </c>
@@ -69632,7 +69573,7 @@
       <c r="I73" s="229"/>
       <c r="J73" s="229"/>
     </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>68</v>
       </c>
@@ -69648,7 +69589,7 @@
       <c r="I74" s="229"/>
       <c r="J74" s="229"/>
     </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>69</v>
       </c>
@@ -69664,7 +69605,7 @@
       <c r="I75" s="229"/>
       <c r="J75" s="229"/>
     </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>70</v>
       </c>
@@ -69680,7 +69621,7 @@
       <c r="I76" s="229"/>
       <c r="J76" s="229"/>
     </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>71</v>
       </c>
@@ -69696,7 +69637,7 @@
       <c r="I77" s="229"/>
       <c r="J77" s="229"/>
     </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>72</v>
       </c>
@@ -69712,7 +69653,7 @@
       <c r="I78" s="229"/>
       <c r="J78" s="229"/>
     </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>73</v>
       </c>
@@ -69728,7 +69669,7 @@
       <c r="I79" s="229"/>
       <c r="J79" s="229"/>
     </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>74</v>
       </c>
@@ -69744,7 +69685,7 @@
       <c r="I80" s="229"/>
       <c r="J80" s="229"/>
     </row>
-    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>75</v>
       </c>
@@ -69760,7 +69701,7 @@
       <c r="I81" s="229"/>
       <c r="J81" s="229"/>
     </row>
-    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>76</v>
       </c>
@@ -69776,7 +69717,7 @@
       <c r="I82" s="229"/>
       <c r="J82" s="229"/>
     </row>
-    <row r="83" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>77</v>
       </c>
@@ -69792,7 +69733,7 @@
       <c r="I83" s="229"/>
       <c r="J83" s="229"/>
     </row>
-    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>78</v>
       </c>
@@ -69808,7 +69749,7 @@
       <c r="I84" s="229"/>
       <c r="J84" s="229"/>
     </row>
-    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>79</v>
       </c>
@@ -69824,7 +69765,7 @@
       <c r="I85" s="229"/>
       <c r="J85" s="229"/>
     </row>
-    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>80</v>
       </c>
@@ -69840,7 +69781,7 @@
       <c r="I86" s="229"/>
       <c r="J86" s="229"/>
     </row>
-    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>81</v>
       </c>
@@ -69856,7 +69797,7 @@
       <c r="I87" s="229"/>
       <c r="J87" s="229"/>
     </row>
-    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>82</v>
       </c>
@@ -69872,7 +69813,7 @@
       <c r="I88" s="229"/>
       <c r="J88" s="229"/>
     </row>
-    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>83</v>
       </c>
@@ -69888,7 +69829,7 @@
       <c r="I89" s="229"/>
       <c r="J89" s="229"/>
     </row>
-    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>84</v>
       </c>
@@ -69904,7 +69845,7 @@
       <c r="I90" s="229"/>
       <c r="J90" s="229"/>
     </row>
-    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>85</v>
       </c>
@@ -69920,7 +69861,7 @@
       <c r="I91" s="229"/>
       <c r="J91" s="229"/>
     </row>
-    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>86</v>
       </c>
@@ -69958,11 +69899,11 @@
       <c r="I93" s="328"/>
       <c r="J93" s="328"/>
     </row>
-    <row r="94" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="429" t="s">
+    <row r="94" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="414" t="s">
         <v>1047</v>
       </c>
-      <c r="B94" s="429"/>
+      <c r="B94" s="414"/>
       <c r="C94" s="229"/>
       <c r="D94" s="229"/>
       <c r="E94" s="229"/>
@@ -69972,7 +69913,7 @@
       <c r="I94" s="229"/>
       <c r="J94" s="229"/>
     </row>
-    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="228">
         <v>1</v>
       </c>
@@ -69988,11 +69929,11 @@
       <c r="I95" s="229"/>
       <c r="J95" s="229"/>
     </row>
-    <row r="96" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="430" t="s">
+    <row r="96" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A96" s="423" t="s">
         <v>596</v>
       </c>
-      <c r="B96" s="431"/>
+      <c r="B96" s="424"/>
       <c r="C96" s="304"/>
       <c r="D96" s="304"/>
       <c r="E96" s="304"/>
@@ -70002,19 +69943,19 @@
       <c r="I96" s="304"/>
       <c r="J96" s="304"/>
     </row>
-    <row r="97" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="424" t="s">
+    <row r="97" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A97" s="418" t="s">
         <v>1050</v>
       </c>
-      <c r="B97" s="424"/>
-      <c r="C97" s="424"/>
-      <c r="D97" s="424"/>
-      <c r="E97" s="424"/>
-      <c r="F97" s="424"/>
-      <c r="G97" s="424"/>
-      <c r="H97" s="424"/>
-      <c r="I97" s="424"/>
-      <c r="J97" s="424"/>
+      <c r="B97" s="418"/>
+      <c r="C97" s="418"/>
+      <c r="D97" s="418"/>
+      <c r="E97" s="418"/>
+      <c r="F97" s="418"/>
+      <c r="G97" s="418"/>
+      <c r="H97" s="418"/>
+      <c r="I97" s="418"/>
+      <c r="J97" s="418"/>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="327">
@@ -70038,7 +69979,7 @@
       <c r="I98" s="328"/>
       <c r="J98" s="328"/>
     </row>
-    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="228">
         <v>2</v>
       </c>
@@ -70054,7 +69995,7 @@
       <c r="I99" s="229"/>
       <c r="J99" s="229"/>
     </row>
-    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="228">
         <v>3</v>
       </c>
@@ -70070,7 +70011,7 @@
       <c r="I100" s="229"/>
       <c r="J100" s="229"/>
     </row>
-    <row r="101" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A101" s="228">
         <v>4</v>
       </c>
@@ -70086,7 +70027,7 @@
       <c r="I101" s="229"/>
       <c r="J101" s="229"/>
     </row>
-    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="228">
         <v>5</v>
       </c>
@@ -70102,7 +70043,7 @@
       <c r="I102" s="229"/>
       <c r="J102" s="229"/>
     </row>
-    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="228">
         <v>6</v>
       </c>
@@ -70118,7 +70059,7 @@
       <c r="I103" s="229"/>
       <c r="J103" s="229"/>
     </row>
-    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="228">
         <v>7</v>
       </c>
@@ -70134,7 +70075,7 @@
       <c r="I104" s="229"/>
       <c r="J104" s="229"/>
     </row>
-    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="228">
         <v>8</v>
       </c>
@@ -70150,7 +70091,7 @@
       <c r="I105" s="229"/>
       <c r="J105" s="229"/>
     </row>
-    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="228">
         <v>9</v>
       </c>
@@ -70166,7 +70107,7 @@
       <c r="I106" s="229"/>
       <c r="J106" s="229"/>
     </row>
-    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="228">
         <v>10</v>
       </c>
@@ -70182,7 +70123,7 @@
       <c r="I107" s="229"/>
       <c r="J107" s="229"/>
     </row>
-    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="228">
         <v>11</v>
       </c>
@@ -70198,7 +70139,7 @@
       <c r="I108" s="229"/>
       <c r="J108" s="229"/>
     </row>
-    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="228">
         <v>12</v>
       </c>
@@ -70214,7 +70155,7 @@
       <c r="I109" s="229"/>
       <c r="J109" s="229"/>
     </row>
-    <row r="110" spans="1:10" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A110" s="228">
         <v>13</v>
       </c>
@@ -70230,7 +70171,7 @@
       <c r="I110" s="229"/>
       <c r="J110" s="229"/>
     </row>
-    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="228">
         <v>14</v>
       </c>
@@ -70246,7 +70187,7 @@
       <c r="I111" s="229"/>
       <c r="J111" s="229"/>
     </row>
-    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="228">
         <v>15</v>
       </c>
@@ -70262,7 +70203,7 @@
       <c r="I112" s="229"/>
       <c r="J112" s="229"/>
     </row>
-    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="228">
         <v>16</v>
       </c>
@@ -70278,7 +70219,7 @@
       <c r="I113" s="229"/>
       <c r="J113" s="229"/>
     </row>
-    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="228">
         <v>17</v>
       </c>
@@ -70294,7 +70235,7 @@
       <c r="I114" s="229"/>
       <c r="J114" s="229"/>
     </row>
-    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="228">
         <v>18</v>
       </c>
@@ -70310,7 +70251,7 @@
       <c r="I115" s="229"/>
       <c r="J115" s="229"/>
     </row>
-    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="228">
         <v>19</v>
       </c>
@@ -70326,7 +70267,7 @@
       <c r="I116" s="229"/>
       <c r="J116" s="229"/>
     </row>
-    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="228">
         <v>20</v>
       </c>
@@ -70342,7 +70283,7 @@
       <c r="I117" s="229"/>
       <c r="J117" s="229"/>
     </row>
-    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="228">
         <v>21</v>
       </c>
@@ -70358,7 +70299,7 @@
       <c r="I118" s="229"/>
       <c r="J118" s="229"/>
     </row>
-    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="228">
         <v>22</v>
       </c>
@@ -70374,7 +70315,7 @@
       <c r="I119" s="229"/>
       <c r="J119" s="229"/>
     </row>
-    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="228">
         <v>23</v>
       </c>
@@ -70390,7 +70331,7 @@
       <c r="I120" s="229"/>
       <c r="J120" s="229"/>
     </row>
-    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="228">
         <v>24</v>
       </c>
@@ -70406,7 +70347,7 @@
       <c r="I121" s="229"/>
       <c r="J121" s="229"/>
     </row>
-    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="228">
         <v>25</v>
       </c>
@@ -70422,11 +70363,11 @@
       <c r="I122" s="229"/>
       <c r="J122" s="229"/>
     </row>
-    <row r="123" spans="1:10" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="427" t="s">
+    <row r="123" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A123" s="421" t="s">
         <v>596</v>
       </c>
-      <c r="B123" s="428"/>
+      <c r="B123" s="422"/>
       <c r="C123" s="229"/>
       <c r="D123" s="229"/>
       <c r="E123" s="229"/>
@@ -70437,14 +70378,12 @@
       <c r="J123" s="229"/>
     </row>
   </sheetData>
-  <autoFilter ref="A7:J123" xr:uid="{00000000-0009-0000-0000-000008000000}">
-    <filterColumn colId="3">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
   <mergeCells count="13">
+    <mergeCell ref="A97:J97"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A123:B123"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="A96:B96"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B4:B5"/>
@@ -70453,11 +70392,6 @@
     <mergeCell ref="H4:H5"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
-    <mergeCell ref="A97:J97"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A123:B123"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="A96:B96"/>
   </mergeCells>
   <conditionalFormatting sqref="D1">
     <cfRule type="iconSet" priority="2">
